--- a/docs/Historias_Usuario.xlsx
+++ b/docs/Historias_Usuario.xlsx
@@ -720,6 +720,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="24" customHeight="1" s="26">
       <c r="A4" s="23" t="inlineStr">
         <is>
@@ -768,6 +769,8 @@
       </c>
       <c r="H5" s="24" t="n"/>
     </row>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8" ht="15.75" customHeight="1" s="26">
       <c r="A8" s="29" t="inlineStr">
         <is>
@@ -840,7 +843,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Cualquier rol</t>
+          <t>Cualquier usuario autenticado</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -1200,7 +1203,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Cualquier autorizado</t>
+          <t>Residente, supervisión o contratista</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -1440,7 +1443,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Supervisión + Residencia</t>
+          <t>Supervisión y residencia</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -1640,7 +1643,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Contratista + Finanzas</t>
+          <t>Contratista y finanzas</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -1937,8 +1940,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -2442,8 +2445,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -2685,8 +2688,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -3190,8 +3193,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -3433,8 +3436,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -3938,8 +3941,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -4181,8 +4184,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -4690,8 +4693,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -4933,8 +4936,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -5000,6 +5003,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="26">
       <c r="A5" s="30" t="inlineStr">
         <is>
@@ -5015,7 +5019,7 @@
       </c>
       <c r="B6" s="31" t="inlineStr">
         <is>
-          <t>contratista y Finanzas</t>
+          <t>contratista y finanzas</t>
         </is>
       </c>
       <c r="C6" s="32" t="n"/>
@@ -5049,6 +5053,7 @@
       <c r="C8" s="32" t="n"/>
       <c r="D8" s="24" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="26">
       <c r="A10" s="30" t="inlineStr">
         <is>
@@ -5128,6 +5133,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="24" customHeight="1" s="26">
       <c r="A16" s="30" t="inlineStr">
         <is>
@@ -5438,8 +5444,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -6336,8 +6342,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -6579,8 +6585,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -6822,8 +6828,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -7065,8 +7071,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -7308,8 +7314,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -7551,8 +7557,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>

--- a/docs/Historias_Usuario.xlsx
+++ b/docs/Historias_Usuario.xlsx
@@ -720,7 +720,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="24" customHeight="1" s="26">
       <c r="A4" s="23" t="inlineStr">
         <is>
@@ -769,8 +768,6 @@
       </c>
       <c r="H5" s="24" t="n"/>
     </row>
-    <row r="6"/>
-    <row r="7"/>
     <row r="8" ht="15.75" customHeight="1" s="26">
       <c r="A8" s="29" t="inlineStr">
         <is>
@@ -1940,8 +1937,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -2445,8 +2442,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -2688,8 +2685,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -2873,7 +2870,7 @@
       </c>
       <c r="B14" s="34" t="inlineStr">
         <is>
-          <t>El sistema bloquea la integración cuando una cantidad por concepto excede la cantidad contratada en el catálogo.</t>
+          <t>El sistema bloquea la integración cuando una cantidad por concepto excede la cantidad contratada en el catálogo (art. 118 RLOPSRM: los trabajos por mayor valor sin orden escrita no son pagables).</t>
         </is>
       </c>
       <c r="C14" s="24" t="n"/>
@@ -3193,8 +3190,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -3436,8 +3433,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -3546,7 +3543,7 @@
       </c>
       <c r="B8" s="31" t="inlineStr">
         <is>
-          <t>decidir sobre la estimación con evidencia completa y dentro de los plazos de los arts. 54 LOPSRM y 133 RLOPSRM</t>
+          <t>decidir sobre la estimación con evidencia completa, en ejercicio de la responsabilidad de la residencia sobre la revisión y aprobación (art. 53 LOPSRM), y dentro de los plazos de los arts. 54 LOPSRM y 133 RLOPSRM</t>
         </is>
       </c>
       <c r="C8" s="32" t="n"/>
@@ -3941,8 +3938,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -4184,8 +4181,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -4693,8 +4690,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -4936,8 +4933,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -5003,7 +5000,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="26">
       <c r="A5" s="30" t="inlineStr">
         <is>
@@ -5053,7 +5049,6 @@
       <c r="C8" s="32" t="n"/>
       <c r="D8" s="24" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="26">
       <c r="A10" s="30" t="inlineStr">
         <is>
@@ -5133,7 +5128,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16" ht="24" customHeight="1" s="26">
       <c r="A16" s="30" t="inlineStr">
         <is>
@@ -5444,8 +5438,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -6342,8 +6336,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -6585,8 +6579,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -6828,8 +6822,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -7071,8 +7065,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -7314,8 +7308,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -7557,8 +7551,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>

--- a/docs/Historias_Usuario.xlsx
+++ b/docs/Historias_Usuario.xlsx
@@ -1804,7 +1804,7 @@
       </c>
       <c r="B8" s="31" t="inlineStr">
         <is>
-          <t>habilitar el registro formal de eventos del contrato conforme al art. 46 último párrafo LOPSRM y al art. 122 RLOPSRM</t>
+          <t>habilitar el registro formal de eventos del contrato conforme al art. 46 último párrafo y al art. 52 Bis LOPSRM (bitácora electrónica obligatoria), reglamentados por el art. 122 RLOPSRM</t>
         </is>
       </c>
       <c r="C8" s="32" t="n"/>
@@ -1937,8 +1937,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -2442,8 +2442,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -2685,8 +2685,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>La carátula calcula automáticamente anticipo amortizado, retenciones legales (5 al millar) y deductivas por penalizaciones según el contrato.</t>
+          <t>La carátula calcula automáticamente el anticipo amortizado (proporcional, art. 143 RLOPSRM), las retenciones legales (5 al millar, art. 191 LFD) y las deductivas por penalizaciones según el contrato.</t>
         </is>
       </c>
       <c r="C13" s="24" t="n"/>
@@ -3190,8 +3190,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B8" s="31" t="inlineStr">
         <is>
-          <t>ver la trazabilidad completa del ciclo de cobro del contrato, incluyendo versiones rechazadas</t>
+          <t>ver la trazabilidad completa del ciclo de cobro del contrato, incluyendo versiones rechazadas, conforme a los tipos de estimación reconocidos en el art. 130 RLOPSRM</t>
         </is>
       </c>
       <c r="C8" s="32" t="n"/>
@@ -3433,8 +3433,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -3938,8 +3938,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -4181,8 +4181,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -4690,8 +4690,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -4933,8 +4933,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="B8" s="31" t="inlineStr">
         <is>
-          <t>no perder el plazo de pago y dejar evidencia de la suficiencia presupuestal verificada</t>
+          <t>no perder el plazo de pago y dejar evidencia de la suficiencia presupuestal verificada, considerando que el incumplimiento del plazo de pago genera gastos financieros a cargo de la dependencia (art. 55 LOPSRM)</t>
         </is>
       </c>
       <c r="C8" s="32" t="n"/>
@@ -5438,8 +5438,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -6336,8 +6336,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="B8" s="31" t="inlineStr">
         <is>
-          <t>documentar formalmente los cambios al contrato conforme al art. 59 LOPSRM y poder consultar qué cambió, cuándo y por qué</t>
+          <t>documentar formalmente los cambios al contrato conforme a los arts. 59 y 59 Bis LOPSRM (este último cuando la modificación supera el 50% del importe o del plazo) y poder consultar qué cambió, cuándo y por qué</t>
         </is>
       </c>
       <c r="C8" s="32" t="n"/>
@@ -6579,8 +6579,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -6822,8 +6822,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -7065,8 +7065,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -7308,8 +7308,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -7551,8 +7551,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>

--- a/docs/Historias_Usuario.xlsx
+++ b/docs/Historias_Usuario.xlsx
@@ -1937,8 +1937,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="B7" s="31" t="inlineStr">
         <is>
-          <t>emitir notas tipificadas según mi rol (instrucción, acuerdo, solicitud, confirmación, respuesta) conforme al art. 125 RLOPSRM, con folio automático y firma electrónica</t>
+          <t>emitir notas tipificadas según mi rol —el residente autoriza y aprueba, el superintendente solicita y avisa, y la supervisión registra el avance— conforme al art. 125 RLOPSRM, con folio automático y firma electrónica</t>
         </is>
       </c>
       <c r="C7" s="32" t="n"/>
@@ -2442,8 +2442,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -2685,8 +2685,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -3190,8 +3190,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -3433,8 +3433,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -3938,8 +3938,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -4181,8 +4181,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -4690,8 +4690,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -4933,8 +4933,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -5438,8 +5438,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -6336,8 +6336,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -6579,8 +6579,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -6822,8 +6822,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -7065,8 +7065,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -7308,8 +7308,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -7551,8 +7551,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>

--- a/docs/Historias_Usuario.xlsx
+++ b/docs/Historias_Usuario.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" tabRatio="600" firstSheet="6" activeTab="19" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="600" firstSheet="0" activeTab="9" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Índice" sheetId="1" state="visible" r:id="rId1"/>
@@ -220,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -284,6 +284,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -324,9 +330,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -695,87 +698,87 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="9" customWidth="1" style="26" min="1" max="1"/>
-    <col width="42" customWidth="1" style="26" min="2" max="2"/>
-    <col width="14" customWidth="1" style="26" min="3" max="3"/>
-    <col width="12" customWidth="1" style="26" min="4" max="4"/>
-    <col width="22" customWidth="1" style="26" min="5" max="5"/>
-    <col width="14" customWidth="1" style="26" min="6" max="7"/>
-    <col width="12" customWidth="1" style="26" min="8" max="8"/>
+    <col width="9" customWidth="1" style="28" min="1" max="1"/>
+    <col width="42" customWidth="1" style="28" min="2" max="2"/>
+    <col width="14" customWidth="1" style="28" min="3" max="3"/>
+    <col width="12" customWidth="1" style="28" min="4" max="4"/>
+    <col width="22" customWidth="1" style="28" min="5" max="5"/>
+    <col width="14" customWidth="1" style="28" min="6" max="7"/>
+    <col width="12" customWidth="1" style="28" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="26">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="28">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>SIGECOP — Historias de Usuario</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="39.95" customHeight="1" s="26">
-      <c r="A2" s="25" t="inlineStr">
+    <row r="2" ht="39.9" customHeight="1" s="28">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Sistema de Gestión Técnico-Administrativa de Contratos de Obra Pública. 22 historias siguiendo el formato dictado por el profesor.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1" s="26">
-      <c r="A4" s="23" t="inlineStr">
+    <row r="4" ht="24" customHeight="1" s="28">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Total historias</t>
         </is>
       </c>
-      <c r="B4" s="24" t="n"/>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="B4" s="26" t="n"/>
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>Total user points</t>
         </is>
       </c>
-      <c r="D4" s="24" t="n"/>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="D4" s="26" t="n"/>
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t>Total sprints planeados</t>
         </is>
       </c>
-      <c r="F4" s="24" t="n"/>
-      <c r="G4" s="23" t="inlineStr">
+      <c r="F4" s="26" t="n"/>
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t>Velocidad promedio del equipo</t>
         </is>
       </c>
-      <c r="H4" s="24" t="n"/>
-    </row>
-    <row r="5" ht="32.1" customHeight="1" s="26">
-      <c r="A5" s="27" t="n">
+      <c r="H4" s="26" t="n"/>
+    </row>
+    <row r="5" ht="32.1" customHeight="1" s="28">
+      <c r="A5" s="29" t="n">
         <v>22</v>
       </c>
-      <c r="B5" s="24" t="n"/>
-      <c r="C5" s="27" t="n">
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="29" t="n">
         <v>85</v>
       </c>
-      <c r="D5" s="24" t="n"/>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="29" t="inlineStr">
         <is>
           <t>1-9</t>
         </is>
       </c>
-      <c r="F5" s="24" t="n"/>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="29" t="inlineStr">
         <is>
           <t>9.4 pts/sprint</t>
         </is>
       </c>
-      <c r="H5" s="24" t="n"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1" s="26">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="H5" s="26" t="n"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" s="28">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>Tabla resumen de las 22 historias</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1" s="26">
+    <row r="9" ht="30" customHeight="1" s="28">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>HU_ID</t>
@@ -817,7 +820,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="27.95" customHeight="1" s="26">
+    <row r="10" ht="27.9" customHeight="1" s="28">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>HU-00</t>
@@ -857,7 +860,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="27.95" customHeight="1" s="26">
+    <row r="11" ht="27.9" customHeight="1" s="28">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>HU-01</t>
@@ -897,7 +900,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="27.95" customHeight="1" s="26">
+    <row r="12" ht="27.9" customHeight="1" s="28">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>HU-02</t>
@@ -937,7 +940,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="27.95" customHeight="1" s="26">
+    <row r="13" ht="27.9" customHeight="1" s="28">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>HU-03</t>
@@ -977,7 +980,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="27.95" customHeight="1" s="26">
+    <row r="14" ht="27.9" customHeight="1" s="28">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>HU-04</t>
@@ -1017,7 +1020,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="27.95" customHeight="1" s="26">
+    <row r="15" ht="27.9" customHeight="1" s="28">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>HU-05</t>
@@ -1057,7 +1060,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="27.95" customHeight="1" s="26">
+    <row r="16" ht="27.9" customHeight="1" s="28">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>HU-06</t>
@@ -1097,7 +1100,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="27.95" customHeight="1" s="26">
+    <row r="17" ht="27.9" customHeight="1" s="28">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t>HU-07</t>
@@ -1137,7 +1140,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="27.95" customHeight="1" s="26">
+    <row r="18" ht="27.9" customHeight="1" s="28">
       <c r="A18" s="3" t="inlineStr">
         <is>
           <t>HU-08</t>
@@ -1177,7 +1180,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="27.95" customHeight="1" s="26">
+    <row r="19" ht="27.9" customHeight="1" s="28">
       <c r="A19" s="3" t="inlineStr">
         <is>
           <t>HU-09</t>
@@ -1217,7 +1220,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="27.95" customHeight="1" s="26">
+    <row r="20" ht="27.9" customHeight="1" s="28">
       <c r="A20" s="3" t="inlineStr">
         <is>
           <t>HU-10</t>
@@ -1257,7 +1260,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="27.95" customHeight="1" s="26">
+    <row r="21" ht="27.9" customHeight="1" s="28">
       <c r="A21" s="3" t="inlineStr">
         <is>
           <t>HU-11</t>
@@ -1297,7 +1300,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="27.95" customHeight="1" s="26">
+    <row r="22" ht="27.9" customHeight="1" s="28">
       <c r="A22" s="3" t="inlineStr">
         <is>
           <t>HU-12</t>
@@ -1337,7 +1340,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="27.95" customHeight="1" s="26">
+    <row r="23" ht="27.9" customHeight="1" s="28">
       <c r="A23" s="3" t="inlineStr">
         <is>
           <t>HU-13</t>
@@ -1377,7 +1380,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="27.95" customHeight="1" s="26">
+    <row r="24" ht="27.9" customHeight="1" s="28">
       <c r="A24" s="3" t="inlineStr">
         <is>
           <t>HU-14</t>
@@ -1417,7 +1420,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="27.95" customHeight="1" s="26">
+    <row r="25" ht="27.9" customHeight="1" s="28">
       <c r="A25" s="3" t="inlineStr">
         <is>
           <t>HU-15</t>
@@ -1457,7 +1460,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="27.95" customHeight="1" s="26">
+    <row r="26" ht="27.9" customHeight="1" s="28">
       <c r="A26" s="3" t="inlineStr">
         <is>
           <t>HU-16</t>
@@ -1497,7 +1500,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="27.95" customHeight="1" s="26">
+    <row r="27" ht="27.9" customHeight="1" s="28">
       <c r="A27" s="3" t="inlineStr">
         <is>
           <t>HU-17</t>
@@ -1537,7 +1540,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="27.95" customHeight="1" s="26">
+    <row r="28" ht="27.9" customHeight="1" s="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
           <t>HU-18</t>
@@ -1577,7 +1580,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="27.95" customHeight="1" s="26">
+    <row r="29" ht="27.9" customHeight="1" s="28">
       <c r="A29" s="3" t="inlineStr">
         <is>
           <t>HU-19</t>
@@ -1617,7 +1620,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="27.95" customHeight="1" s="26">
+    <row r="30" ht="27.9" customHeight="1" s="28">
       <c r="A30" s="3" t="inlineStr">
         <is>
           <t>HU-20</t>
@@ -1657,7 +1660,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="27.95" customHeight="1" s="26">
+    <row r="31" ht="27.9" customHeight="1" s="28">
       <c r="A31" s="3" t="inlineStr">
         <is>
           <t>HU-21</t>
@@ -1722,223 +1725,226 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="26" min="1" max="1"/>
-    <col width="50" customWidth="1" style="26" min="2" max="2"/>
-    <col width="25" customWidth="1" style="26" min="3" max="3"/>
-    <col width="18" customWidth="1" style="26" min="4" max="4"/>
+    <col width="16" customWidth="1" style="28" min="1" max="1"/>
+    <col width="50" customWidth="1" style="28" min="2" max="2"/>
+    <col width="25" customWidth="1" style="28" min="3" max="3"/>
+    <col width="18" customWidth="1" style="28" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="26">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>HU-08 · Apertura formal de la bitácora del contrato</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="26">
-      <c r="A2" s="37" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="28">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-03-01</t>
         </is>
       </c>
-      <c r="C2" s="37" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>Módulo: MOD-03</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="26">
-      <c r="A3" s="37" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="28">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Sprint sugerido: 1</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="39" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="26">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="28">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.95" customHeight="1" s="26">
+    <row r="6" ht="27.9" customHeight="1" s="28">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="30" customHeight="1" s="26">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="26" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1" s="28">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
-        <is>
-          <t>abrir la bitácora electrónica del contrato ligando a las tres partes (contratante, supervisión, contratista) con sus responsables autorizados a firmar</t>
-        </is>
-      </c>
-      <c r="C7" s="32" t="n"/>
-      <c r="D7" s="24" t="n"/>
-    </row>
-    <row r="8" ht="27.95" customHeight="1" s="26">
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>aperturar la bitácora electrónica del contrato ligando a las tres partes (contratante, supervisión, contratista) con sus responsables autorizados a firmar</t>
+        </is>
+      </c>
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="26" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="28">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>habilitar el registro formal de eventos del contrato conforme al art. 46 último párrafo y al art. 52 Bis LOPSRM (bitácora electrónica obligatoria), reglamentados por el art. 122 RLOPSRM</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="24" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="26">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="26" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="24" customHeight="1" s="28">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
-        <is>
-          <t>Criterio (aseveración)</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>Criterios de aceptación</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="26">
+    <row r="12" ht="32.1" customHeight="1" s="28">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>Existe una bitácora única por contrato con las tres partes ligadas y sus firmantes autorizados.</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n"/>
+      <c r="C12" s="26" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="26">
+    <row r="13" ht="32.1" customHeight="1" s="28">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>La fecha y hora de apertura queda registrada como evento formal inalterable.</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n"/>
+      <c r="C13" s="26" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="26">
-      <c r="A15" s="30" t="inlineStr">
+    <row r="14"/>
+    <row r="15" ht="24" customHeight="1" s="28">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="26">
+    <row r="16" ht="24" customHeight="1" s="28">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B16" s="33" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" s="26">
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="26" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B17" s="33" t="n">
+      <c r="B17" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="26">
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="26">
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="24" t="n"/>
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -1965,233 +1971,236 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="26" min="1" max="1"/>
-    <col width="50" customWidth="1" style="26" min="2" max="2"/>
-    <col width="25" customWidth="1" style="26" min="3" max="3"/>
-    <col width="18" customWidth="1" style="26" min="4" max="4"/>
+    <col width="16" customWidth="1" style="28" min="1" max="1"/>
+    <col width="50" customWidth="1" style="28" min="2" max="2"/>
+    <col width="25" customWidth="1" style="28" min="3" max="3"/>
+    <col width="18" customWidth="1" style="28" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="26">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>HU-09 · Emisión y respuesta de notas tipificadas con firma</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="26">
-      <c r="A2" s="37" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="28">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-03-02</t>
         </is>
       </c>
-      <c r="C2" s="37" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>Módulo: MOD-03</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="26">
-      <c r="A3" s="37" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="28">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Sprint sugerido: 2</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="39" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="26">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="28">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.95" customHeight="1" s="26">
+    <row r="6" ht="27.9" customHeight="1" s="28">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>residente, supervisión o contratista (según rol autorizado)</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="30.95" customHeight="1" s="26">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="26" t="n"/>
+    </row>
+    <row r="7" ht="30.9" customHeight="1" s="28">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>emitir notas tipificadas según mi rol —el residente autoriza y aprueba, el superintendente solicita y avisa, y la supervisión registra el avance— conforme al art. 125 RLOPSRM, con folio automático y firma electrónica</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n"/>
-      <c r="D7" s="24" t="n"/>
-    </row>
-    <row r="8" ht="27.95" customHeight="1" s="26">
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="26" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="28">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>documentar formalmente los eventos del contrato de manera trazable e inmutable para auditoría</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="24" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="26">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="26" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="24" customHeight="1" s="28">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
-        <is>
-          <t>Criterio (aseveración)</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>Criterios de aceptación</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="26">
+    <row r="12" ht="32.1" customHeight="1" s="28">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>Solo aparecen disponibles los tipos de nota que corresponden al rol del usuario.</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n"/>
+      <c r="C12" s="26" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="26">
+    <row r="13" ht="32.1" customHeight="1" s="28">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>Una nota firmada queda inmutable y solo puede corregirse emitiendo una nueva nota vinculada.</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n"/>
+      <c r="C13" s="26" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32.1" customHeight="1" s="26">
+    <row r="14" ht="32.1" customHeight="1" s="28">
       <c r="A14" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>Cada nota queda registrada con folio, fecha, firmante y vínculo opcional a una nota previa.</t>
         </is>
       </c>
-      <c r="C14" s="24" t="n"/>
+      <c r="C14" s="26" t="n"/>
       <c r="D14" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="26">
-      <c r="A16" s="30" t="inlineStr">
+    <row r="15"/>
+    <row r="16" ht="24" customHeight="1" s="28">
+      <c r="A16" s="32" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" s="26">
+    <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B17" s="38" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="26">
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B18" s="38" t="n">
+      <c r="B18" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="26">
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="24" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" s="26">
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="26" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" s="28">
       <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="35" t="inlineStr">
+      <c r="B20" s="37" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="C20" s="32" t="n"/>
-      <c r="D20" s="24" t="n"/>
+      <c r="C20" s="34" t="n"/>
+      <c r="D20" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -2227,223 +2236,226 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="26" min="1" max="1"/>
-    <col width="50" customWidth="1" style="26" min="2" max="2"/>
-    <col width="25" customWidth="1" style="26" min="3" max="3"/>
-    <col width="18" customWidth="1" style="26" min="4" max="4"/>
+    <col width="16" customWidth="1" style="28" min="1" max="1"/>
+    <col width="50" customWidth="1" style="28" min="2" max="2"/>
+    <col width="25" customWidth="1" style="28" min="3" max="3"/>
+    <col width="18" customWidth="1" style="28" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="26">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>HU-10 · Consulta y búsqueda de notas de bitácora</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="26">
-      <c r="A2" s="37" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="28">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-03-03</t>
         </is>
       </c>
-      <c r="C2" s="37" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>Módulo: MOD-03</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="26">
-      <c r="A3" s="37" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="28">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Sprint sugerido: 3</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="39" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="26">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="28">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.95" customHeight="1" s="26">
+    <row r="6" ht="27.9" customHeight="1" s="28">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="27.95" customHeight="1" s="26">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="26" t="n"/>
+    </row>
+    <row r="7" ht="27.9" customHeight="1" s="28">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>buscar notas de la bitácora del contrato por tipo, fecha, firmante, estatus o tema, y seleccionar varias para adjuntarlas a una estimación</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n"/>
-      <c r="D7" s="24" t="n"/>
-    </row>
-    <row r="8" ht="27.95" customHeight="1" s="26">
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="26" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="28">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>encontrar rápido la nota que necesito y poder referenciarla en estimaciones o reportes</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="24" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="26">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="26" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="24" customHeight="1" s="28">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
-        <is>
-          <t>Criterio (aseveración)</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>Criterios de aceptación</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="26">
+    <row r="12" ht="32.1" customHeight="1" s="28">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>La búsqueda devuelve resultados que cumplen todos los filtros aplicados simultáneamente.</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n"/>
+      <c r="C12" s="26" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="26">
+    <row r="13" ht="32.1" customHeight="1" s="28">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>Se pueden seleccionar varias notas del resultado y exportarlas o adjuntarlas a una estimación.</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n"/>
+      <c r="C13" s="26" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="26">
-      <c r="A15" s="30" t="inlineStr">
+    <row r="14"/>
+    <row r="15" ht="24" customHeight="1" s="28">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="26">
+    <row r="16" ht="24" customHeight="1" s="28">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B16" s="33" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" s="26">
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="26" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B17" s="33" t="n">
+      <c r="B17" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="26">
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="26">
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="24" t="n"/>
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -2470,223 +2482,226 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="26" min="1" max="1"/>
-    <col width="50" customWidth="1" style="26" min="2" max="2"/>
-    <col width="25" customWidth="1" style="26" min="3" max="3"/>
-    <col width="18" customWidth="1" style="26" min="4" max="4"/>
+    <col width="16" customWidth="1" style="28" min="1" max="1"/>
+    <col width="50" customWidth="1" style="28" min="2" max="2"/>
+    <col width="25" customWidth="1" style="28" min="3" max="3"/>
+    <col width="18" customWidth="1" style="28" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="26">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>HU-11 · Registro de minutas, agenda de visitas y consulta de acuerdos</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="26">
-      <c r="A2" s="37" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="28">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-03-04</t>
         </is>
       </c>
-      <c r="C2" s="37" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>Módulo: MOD-03</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="26">
-      <c r="A3" s="37" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="28">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Sprint sugerido: 7</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="39" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="26">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="28">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.95" customHeight="1" s="26">
+    <row r="6" ht="27.9" customHeight="1" s="28">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="27.95" customHeight="1" s="26">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="26" t="n"/>
+    </row>
+    <row r="7" ht="27.9" customHeight="1" s="28">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>subir minutas de reuniones del contrato con sus metadatos, agendar visitas e inspecciones de campo, y consultar los acuerdos asentados</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n"/>
-      <c r="D7" s="24" t="n"/>
-    </row>
-    <row r="8" ht="27.95" customHeight="1" s="26">
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="26" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="28">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>tener concentradas todas las reuniones, visitas y compromisos del contrato en un solo lugar para consulta</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="24" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="26">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="26" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="24" customHeight="1" s="28">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
-        <is>
-          <t>Criterio (aseveración)</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>Criterios de aceptación</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="26">
+    <row r="12" ht="32.1" customHeight="1" s="28">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>Las minutas y visitas registradas son visibles para los usuarios autorizados del contrato.</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n"/>
+      <c r="C12" s="26" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="26">
+    <row r="13" ht="32.1" customHeight="1" s="28">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>Se pueden consultar los acuerdos y compromisos derivados, filtrados por contrato y periodo.</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n"/>
+      <c r="C13" s="26" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="26">
-      <c r="A15" s="30" t="inlineStr">
+    <row r="14"/>
+    <row r="15" ht="24" customHeight="1" s="28">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="26">
+    <row r="16" ht="24" customHeight="1" s="28">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B16" s="40" t="inlineStr">
+      <c r="B16" s="42" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" s="26">
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="26" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B17" s="40" t="n">
+      <c r="B17" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="26">
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>Sprint 7</t>
         </is>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="26">
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="24" t="n"/>
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -2713,233 +2728,236 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="26" min="1" max="1"/>
-    <col width="50" customWidth="1" style="26" min="2" max="2"/>
-    <col width="25" customWidth="1" style="26" min="3" max="3"/>
-    <col width="18" customWidth="1" style="26" min="4" max="4"/>
+    <col width="16" customWidth="1" style="28" min="1" max="1"/>
+    <col width="50" customWidth="1" style="28" min="2" max="2"/>
+    <col width="25" customWidth="1" style="28" min="3" max="3"/>
+    <col width="18" customWidth="1" style="28" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="26">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>HU-12 · Apertura del periodo e integración de la estimación</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="26">
-      <c r="A2" s="37" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="28">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-04-01</t>
         </is>
       </c>
-      <c r="C2" s="37" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>Módulo: MOD-04</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="26">
-      <c r="A3" s="37" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="28">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Sprint sugerido: 3</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="39" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="26">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="28">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.95" customHeight="1" s="26">
+    <row r="6" ht="27.9" customHeight="1" s="28">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>contratista</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="36" customHeight="1" s="26">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="26" t="n"/>
+    </row>
+    <row r="7" ht="36" customHeight="1" s="28">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>abrir el periodo de estimación e integrar como un solo bloque la carátula (con anticipos amortizados, retenciones y deductivas), números generadores, registro fotográfico, soportes y notas de bitácora del periodo</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n"/>
-      <c r="D7" s="24" t="n"/>
-    </row>
-    <row r="8" ht="27.95" customHeight="1" s="26">
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="26" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="28">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>presentar la estimación como un expediente completo conforme al art. 132 RLOPSRM para la revisión de supervisión y residencia</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="24" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="26">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="26" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="24" customHeight="1" s="28">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
-        <is>
-          <t>Criterio (aseveración)</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>Criterios de aceptación</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="33" customHeight="1" s="26">
+    <row r="12" ht="33" customHeight="1" s="28">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>La estimación se guarda como una sola entidad que contiene carátula, generadores, registro fotográfico, soportes y notas vinculadas.</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n"/>
+      <c r="C12" s="26" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="35.1" customHeight="1" s="26">
+    <row r="13" ht="35.1" customHeight="1" s="28">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>La carátula calcula automáticamente el anticipo amortizado (proporcional, art. 143 RLOPSRM), las retenciones legales (5 al millar, art. 191 LFD) y las deductivas por penalizaciones según el contrato.</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n"/>
+      <c r="C13" s="26" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32.1" customHeight="1" s="26">
+    <row r="14" ht="32.1" customHeight="1" s="28">
       <c r="A14" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>El sistema bloquea la integración cuando una cantidad por concepto excede la cantidad contratada en el catálogo (art. 118 RLOPSRM: los trabajos por mayor valor sin orden escrita no son pagables).</t>
         </is>
       </c>
-      <c r="C14" s="24" t="n"/>
+      <c r="C14" s="26" t="n"/>
       <c r="D14" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="26">
-      <c r="A16" s="30" t="inlineStr">
+    <row r="15"/>
+    <row r="16" ht="24" customHeight="1" s="28">
+      <c r="A16" s="32" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" s="26">
+    <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B17" s="38" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="26">
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B18" s="38" t="n">
+      <c r="B18" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="26">
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="24" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" s="26">
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="26" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" s="28">
       <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="35" t="inlineStr">
+      <c r="B20" s="37" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="C20" s="32" t="n"/>
-      <c r="D20" s="24" t="n"/>
+      <c r="C20" s="34" t="n"/>
+      <c r="D20" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -2975,223 +2993,226 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="26" min="1" max="1"/>
-    <col width="50" customWidth="1" style="26" min="2" max="2"/>
-    <col width="25" customWidth="1" style="26" min="3" max="3"/>
-    <col width="18" customWidth="1" style="26" min="4" max="4"/>
+    <col width="16" customWidth="1" style="28" min="1" max="1"/>
+    <col width="50" customWidth="1" style="28" min="2" max="2"/>
+    <col width="25" customWidth="1" style="28" min="3" max="3"/>
+    <col width="18" customWidth="1" style="28" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="26">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>HU-13 · Envío de la estimación</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="26">
-      <c r="A2" s="37" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="28">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-04-02</t>
         </is>
       </c>
-      <c r="C2" s="37" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>Módulo: MOD-04</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="26">
-      <c r="A3" s="37" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="28">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Sprint sugerido: 8</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="39" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="26">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="28">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.95" customHeight="1" s="26">
+    <row r="6" ht="27.9" customHeight="1" s="28">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>contratista</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="27.95" customHeight="1" s="26">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="26" t="n"/>
+    </row>
+    <row r="7" ht="27.9" customHeight="1" s="28">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>enviar formalmente una estimación integrada para que arranque el plazo de revisión del art. 54 LOPSRM</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n"/>
-      <c r="D7" s="24" t="n"/>
-    </row>
-    <row r="8" ht="27.95" customHeight="1" s="26">
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="26" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="28">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>dejar evidencia del momento exacto de entrega y disparar el plazo de revisión de la supervisión y residencia</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="24" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="26">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="26" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="24" customHeight="1" s="28">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
-        <is>
-          <t>Criterio (aseveración)</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>Criterios de aceptación</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="26">
+    <row r="12" ht="32.1" customHeight="1" s="28">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>Al enviar la estimación queda registrada la fecha y hora exacta, y se notifica a residencia y supervisión.</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n"/>
+      <c r="C12" s="26" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="26">
+    <row r="13" ht="32.1" customHeight="1" s="28">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>El botón Enviar se deshabilita cuando se vencen los 6 días naturales del periodo de presentación (art. 54 LOPSRM).</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n"/>
+      <c r="C13" s="26" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="26">
-      <c r="A15" s="30" t="inlineStr">
+    <row r="14"/>
+    <row r="15" ht="24" customHeight="1" s="28">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="26">
+    <row r="16" ht="24" customHeight="1" s="28">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B16" s="40" t="inlineStr">
+      <c r="B16" s="42" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" s="26">
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="26" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B17" s="40" t="n">
+      <c r="B17" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="26">
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>Sprint 8</t>
         </is>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="26">
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="24" t="n"/>
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -3218,223 +3239,226 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="26" min="1" max="1"/>
-    <col width="50" customWidth="1" style="26" min="2" max="2"/>
-    <col width="25" customWidth="1" style="26" min="3" max="3"/>
-    <col width="18" customWidth="1" style="26" min="4" max="4"/>
+    <col width="16" customWidth="1" style="28" min="1" max="1"/>
+    <col width="50" customWidth="1" style="28" min="2" max="2"/>
+    <col width="25" customWidth="1" style="28" min="3" max="3"/>
+    <col width="18" customWidth="1" style="28" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="26">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>HU-14 · Historial de estimaciones del contrato</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="26">
-      <c r="A2" s="37" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="28">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-04-03</t>
         </is>
       </c>
-      <c r="C2" s="37" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>Módulo: MOD-04</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="26">
-      <c r="A3" s="37" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="28">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Sprint sugerido: 5</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="39" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="26">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="28">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.95" customHeight="1" s="26">
+    <row r="6" ht="27.9" customHeight="1" s="28">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="29.1" customHeight="1" s="26">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="26" t="n"/>
+    </row>
+    <row r="7" ht="29.1" customHeight="1" s="28">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>consultar todas las estimaciones del contrato a lo largo del tiempo con sus estados (aceptadas, rechazadas, en proceso) y filtros por periodo</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n"/>
-      <c r="D7" s="24" t="n"/>
-    </row>
-    <row r="8" ht="27.95" customHeight="1" s="26">
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="26" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="28">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>ver la trazabilidad completa del ciclo de cobro del contrato, incluyendo versiones rechazadas, conforme a los tipos de estimación reconocidos en el art. 130 RLOPSRM</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="24" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="26">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="26" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="24" customHeight="1" s="28">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
-        <is>
-          <t>Criterio (aseveración)</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>Criterios de aceptación</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="26">
+    <row r="12" ht="32.1" customHeight="1" s="28">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>La lista incluye todas las versiones (incluyendo rechazadas) con su periodo, estado e importe.</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n"/>
+      <c r="C12" s="26" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="26">
+    <row r="13" ht="32.1" customHeight="1" s="28">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>Solo existe una estimación con estado 'aceptada' por periodo, mientras que pueden existir múltiples rechazadas.</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n"/>
+      <c r="C13" s="26" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="26">
-      <c r="A15" s="30" t="inlineStr">
+    <row r="14"/>
+    <row r="15" ht="24" customHeight="1" s="28">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="26">
+    <row r="16" ht="24" customHeight="1" s="28">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B16" s="33" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" s="26">
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="26" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B17" s="33" t="n">
+      <c r="B17" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="26">
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="26">
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="24" t="n"/>
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -3461,233 +3485,236 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="26" min="1" max="1"/>
-    <col width="50" customWidth="1" style="26" min="2" max="2"/>
-    <col width="25" customWidth="1" style="26" min="3" max="3"/>
-    <col width="18" customWidth="1" style="26" min="4" max="4"/>
+    <col width="16" customWidth="1" style="28" min="1" max="1"/>
+    <col width="50" customWidth="1" style="28" min="2" max="2"/>
+    <col width="25" customWidth="1" style="28" min="3" max="3"/>
+    <col width="18" customWidth="1" style="28" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="26">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>HU-15 · Recepción, revisión técnica y autorización de la estimación</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="26">
-      <c r="A2" s="37" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="28">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-05-01</t>
         </is>
       </c>
-      <c r="C2" s="37" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>Módulo: MOD-05</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="26">
-      <c r="A3" s="37" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="28">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Sprint sugerido: 4</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="39" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="26">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="28">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.95" customHeight="1" s="26">
+    <row r="6" ht="27.9" customHeight="1" s="28">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>supervisión y residencia (revisión secuencial)</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="36.95" customHeight="1" s="26">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="26" t="n"/>
+    </row>
+    <row r="7" ht="36.9" customHeight="1" s="28">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>revisar la estimación recibida sección por sección (carátula, números generadores, registro fotográfico, soportes, notas), registrar observaciones puntuales, turnar de supervisión a residencia y al final autorizar o rechazar</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n"/>
-      <c r="D7" s="24" t="n"/>
-    </row>
-    <row r="8" ht="27.95" customHeight="1" s="26">
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="26" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="28">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>decidir sobre la estimación con evidencia completa, en ejercicio de la responsabilidad de la residencia sobre la revisión y aprobación (art. 53 LOPSRM), y dentro de los plazos de los arts. 54 LOPSRM y 133 RLOPSRM</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="24" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="26">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="26" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="24" customHeight="1" s="28">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
-        <is>
-          <t>Criterio (aseveración)</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>Criterios de aceptación</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="33" customHeight="1" s="26">
+    <row r="12" ht="33" customHeight="1" s="28">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>La pantalla muestra todas las secciones de la estimación con posibilidad de registrar observaciones puntuales por sección.</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n"/>
+      <c r="C12" s="26" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="26">
+    <row r="13" ht="32.1" customHeight="1" s="28">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>El flujo obliga a la supervisión a turnar la estimación antes de que residencia pueda autorizar o rechazar.</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n"/>
+      <c r="C13" s="26" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="33" customHeight="1" s="26">
+    <row r="14" ht="33" customHeight="1" s="28">
       <c r="A14" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>El sistema emite alertas cuando una estimación permanece más del plazo configurado en un mismo estado (art. 54 LOPSRM).</t>
         </is>
       </c>
-      <c r="C14" s="24" t="n"/>
+      <c r="C14" s="26" t="n"/>
       <c r="D14" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="26">
-      <c r="A16" s="30" t="inlineStr">
+    <row r="15"/>
+    <row r="16" ht="24" customHeight="1" s="28">
+      <c r="A16" s="32" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" s="26">
+    <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B17" s="38" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="26">
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B18" s="38" t="n">
+      <c r="B18" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="26">
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="24" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" s="26">
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="26" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" s="28">
       <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="35" t="inlineStr">
+      <c r="B20" s="37" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="C20" s="32" t="n"/>
-      <c r="D20" s="24" t="n"/>
+      <c r="C20" s="34" t="n"/>
+      <c r="D20" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -3723,223 +3750,226 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="26" min="1" max="1"/>
-    <col width="50" customWidth="1" style="26" min="2" max="2"/>
-    <col width="25" customWidth="1" style="26" min="3" max="3"/>
-    <col width="18" customWidth="1" style="26" min="4" max="4"/>
+    <col width="16" customWidth="1" style="28" min="1" max="1"/>
+    <col width="50" customWidth="1" style="28" min="2" max="2"/>
+    <col width="25" customWidth="1" style="28" min="3" max="3"/>
+    <col width="18" customWidth="1" style="28" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="26">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>HU-16 · Reingreso de estimación tras rechazo</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="26">
-      <c r="A2" s="37" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="28">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-05-02</t>
         </is>
       </c>
-      <c r="C2" s="37" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>Módulo: MOD-05</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="26">
-      <c r="A3" s="37" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="28">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Sprint sugerido: 8</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="39" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="26">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="28">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.95" customHeight="1" s="26">
+    <row r="6" ht="27.9" customHeight="1" s="28">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>contratista</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="27.95" customHeight="1" s="26">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="26" t="n"/>
+    </row>
+    <row r="7" ht="27.9" customHeight="1" s="28">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>presentar una nueva versión completa de la estimación del mismo periodo después de un rechazo, atendiendo las observaciones recibidas</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n"/>
-      <c r="D7" s="24" t="n"/>
-    </row>
-    <row r="8" ht="27.95" customHeight="1" s="26">
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="26" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="28">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>que la estimación sea revisada nuevamente como un bloque completo sin perder trazabilidad de la versión anterior</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="24" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="26">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="26" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="24" customHeight="1" s="28">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
-        <is>
-          <t>Criterio (aseveración)</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>Criterios de aceptación</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="26">
+    <row r="12" ht="32.1" customHeight="1" s="28">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>La nueva versión se trata como bloque completo independiente y la versión rechazada queda como histórico vinculado.</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n"/>
+      <c r="C12" s="26" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="26">
+    <row r="13" ht="32.1" customHeight="1" s="28">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>El listado de observaciones de la versión rechazada está disponible para descarga en PDF o Excel.</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n"/>
+      <c r="C13" s="26" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="26">
-      <c r="A15" s="30" t="inlineStr">
+    <row r="14"/>
+    <row r="15" ht="24" customHeight="1" s="28">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="26">
+    <row r="16" ht="24" customHeight="1" s="28">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B16" s="40" t="inlineStr">
+      <c r="B16" s="42" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" s="26">
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="26" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B17" s="40" t="n">
+      <c r="B17" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="26">
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>Sprint 8</t>
         </is>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="26">
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="24" t="n"/>
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -3966,223 +3996,226 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="26" min="1" max="1"/>
-    <col width="50" customWidth="1" style="26" min="2" max="2"/>
-    <col width="25" customWidth="1" style="26" min="3" max="3"/>
-    <col width="18" customWidth="1" style="26" min="4" max="4"/>
+    <col width="16" customWidth="1" style="28" min="1" max="1"/>
+    <col width="50" customWidth="1" style="28" min="2" max="2"/>
+    <col width="25" customWidth="1" style="28" min="3" max="3"/>
+    <col width="18" customWidth="1" style="28" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="26">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>HU-17 · Tablero de estimaciones aceptadas y en proceso</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="26">
-      <c r="A2" s="37" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="28">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-06-01</t>
         </is>
       </c>
-      <c r="C2" s="37" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>Módulo: MOD-06</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="26">
-      <c r="A3" s="37" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="28">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Sprint sugerido: 8</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="39" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="26">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="28">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.95" customHeight="1" s="26">
+    <row r="6" ht="27.9" customHeight="1" s="28">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="35.1" customHeight="1" s="26">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="26" t="n"/>
+    </row>
+    <row r="7" ht="35.1" customHeight="1" s="28">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>ver en un tablero las estimaciones del contrato que están aceptadas y las que están en proceso (presentada, en revisión, autorizada, en pago, pagada), con su línea de tiempo y pendientes por solventar</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n"/>
-      <c r="D7" s="24" t="n"/>
-    </row>
-    <row r="8" ht="27.95" customHeight="1" s="26">
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="26" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="28">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>saber qué estimación está en qué estado y qué requiere mi acción inmediata</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="24" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="26">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="26" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="24" customHeight="1" s="28">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
-        <is>
-          <t>Criterio (aseveración)</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>Criterios de aceptación</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="26">
+    <row r="12" ht="32.1" customHeight="1" s="28">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>El tablero muestra solo estimaciones aceptadas y en proceso (no las rechazadas, que viven en el historial).</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n"/>
+      <c r="C12" s="26" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="26">
+    <row r="13" ht="32.1" customHeight="1" s="28">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>El panel 'Mis pendientes' filtra los pendientes según el rol del usuario autenticado.</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n"/>
+      <c r="C13" s="26" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="26">
-      <c r="A15" s="30" t="inlineStr">
+    <row r="14"/>
+    <row r="15" ht="24" customHeight="1" s="28">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="26">
+    <row r="16" ht="24" customHeight="1" s="28">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B16" s="40" t="inlineStr">
+      <c r="B16" s="42" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" s="26">
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="26" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B17" s="40" t="n">
+      <c r="B17" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="26">
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>Sprint 8</t>
         </is>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="26">
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="24" t="n"/>
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -4209,167 +4242,169 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="26" min="1" max="1"/>
-    <col width="50" customWidth="1" style="26" min="2" max="2"/>
-    <col width="25" customWidth="1" style="26" min="3" max="3"/>
-    <col width="18" customWidth="1" style="26" min="4" max="4"/>
+    <col width="16" customWidth="1" style="28" min="1" max="1"/>
+    <col width="50" customWidth="1" style="28" min="2" max="2"/>
+    <col width="25" customWidth="1" style="28" min="3" max="3"/>
+    <col width="18" customWidth="1" style="28" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="26">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>HU-00 · Inicio de sesión por rol</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="26">
-      <c r="A2" s="37" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="28">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Servicio implementado: —</t>
         </is>
       </c>
-      <c r="C2" s="37" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>Módulo: —</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="26">
-      <c r="A3" s="37" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="28">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Sprint sugerido: 1</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="39" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="26">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="28">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.95" customHeight="1" s="26">
+    <row r="6" ht="27.9" customHeight="1" s="28">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>usuario del sistema (residente, contratista, supervisión, dependencia o finanzas)</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="27.95" customHeight="1" s="26">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="26" t="n"/>
+    </row>
+    <row r="7" ht="69" customHeight="1" s="28">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>autenticarme con mi usuario y contraseña, sin tener que indicar mi rol explícitamente, para que el sistema reconozca internamente quién soy y me muestre únicamente las funciones que me corresponden</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n"/>
-      <c r="D7" s="24" t="n"/>
-    </row>
-    <row r="8" ht="27.95" customHeight="1" s="26">
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="26" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="28">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>proteger la información del contrato y que cada acción registrada quede asociada al usuario que la ejecuta</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="24" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="26">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="26" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="24" customHeight="1" s="28">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
-        <is>
-          <t>Criterio (aseveración)</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>Criterios de aceptación</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="26">
+    <row r="12" ht="32.1" customHeight="1" s="28">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>El sistema valida usuario y contraseña, bloquea el acceso cuando son inválidos y no permite continuar si los campos usuario o contraseña están vacíos.</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n"/>
+      <c r="C12" s="26" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="26">
+    <row r="13" ht="32.1" customHeight="1" s="28">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>El sistema deduce el rol del usuario a partir de su identificador, sin que este lo seleccione, y muestra únicamente las pantallas y opciones que corresponden a ese rol.</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n"/>
+      <c r="C13" s="26" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32.1" customHeight="1" s="26">
+    <row r="14" ht="32.1" customHeight="1" s="28">
       <c r="A14" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>Cada acción registrada por el usuario queda asociada a su nombre y fecha/hora en el sistema.</t>
         </is>
       </c>
-      <c r="C14" s="24" t="n"/>
+      <c r="C14" s="26" t="n"/>
       <c r="D14" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
@@ -4378,68 +4413,68 @@
     </row>
     <row r="15">
       <c r="A15" s="13" t="n"/>
-      <c r="B15" s="34" t="n"/>
-    </row>
-    <row r="16" ht="24" customHeight="1" s="26">
-      <c r="A16" s="30" t="inlineStr">
+      <c r="B15" s="36" t="n"/>
+    </row>
+    <row r="16" ht="24" customHeight="1" s="28">
+      <c r="A16" s="32" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" s="26">
+    <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B17" s="33" t="inlineStr">
+      <c r="B17" s="35" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="26">
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B18" s="33" t="n">
+      <c r="B18" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="26">
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="24" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" s="26">
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="26" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" s="28">
       <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="35" t="inlineStr">
+      <c r="B20" s="37" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="C20" s="32" t="n"/>
-      <c r="D20" s="24" t="n"/>
+      <c r="C20" s="34" t="n"/>
+      <c r="D20" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -4475,223 +4510,226 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="26" min="1" max="1"/>
-    <col width="50" customWidth="1" style="26" min="2" max="2"/>
-    <col width="25" customWidth="1" style="26" min="3" max="3"/>
-    <col width="18" customWidth="1" style="26" min="4" max="4"/>
+    <col width="16" customWidth="1" style="28" min="1" max="1"/>
+    <col width="50" customWidth="1" style="28" min="2" max="2"/>
+    <col width="25" customWidth="1" style="28" min="3" max="3"/>
+    <col width="18" customWidth="1" style="28" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="26">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>HU-18 · Vista ejecutiva del portafolio con semáforos</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="26">
-      <c r="A2" s="37" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="28">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-06-02</t>
         </is>
       </c>
-      <c r="C2" s="37" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>Módulo: MOD-06</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="26">
-      <c r="A3" s="37" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="28">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Sprint sugerido: 9</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="39" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="26">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="28">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.95" customHeight="1" s="26">
+    <row r="6" ht="27.9" customHeight="1" s="28">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>dependencia</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="32.1" customHeight="1" s="26">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="26" t="n"/>
+    </row>
+    <row r="7" ht="32.1" customHeight="1" s="28">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>ver mis contratos asignados como una lista con semáforo de tres colores (verde, ámbar, rojo) según avance físico, atrasos y pendientes, con drill-down al detalle del contrato</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n"/>
-      <c r="D7" s="24" t="n"/>
-    </row>
-    <row r="8" ht="27.95" customHeight="1" s="26">
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="26" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="28">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>tomar decisiones ejecutivas sobre cuáles contratos requieren mi atención</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="24" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="26">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="26" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="24" customHeight="1" s="28">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
-        <is>
-          <t>Criterio (aseveración)</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>Criterios de aceptación</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="26">
+    <row r="12" ht="32.1" customHeight="1" s="28">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>Cada contrato del portafolio muestra un semáforo de color calculado a partir de avance físico, atrasos y pendientes.</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n"/>
+      <c r="C12" s="26" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="26">
+    <row r="13" ht="32.1" customHeight="1" s="28">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>Al hacer doble clic sobre un contrato se abre su detalle con indicadores físicos, financieros y penalizaciones.</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n"/>
+      <c r="C13" s="26" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="26">
-      <c r="A15" s="30" t="inlineStr">
+    <row r="14"/>
+    <row r="15" ht="24" customHeight="1" s="28">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="26">
+    <row r="16" ht="24" customHeight="1" s="28">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B16" s="40" t="inlineStr">
+      <c r="B16" s="42" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" s="26">
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="26" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B17" s="39" t="n">
+      <c r="B17" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="26">
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>Sprint 9</t>
         </is>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="26">
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="24" t="n"/>
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -4718,223 +4756,226 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="26" min="1" max="1"/>
-    <col width="50" customWidth="1" style="26" min="2" max="2"/>
-    <col width="25" customWidth="1" style="26" min="3" max="3"/>
-    <col width="18" customWidth="1" style="26" min="4" max="4"/>
+    <col width="16" customWidth="1" style="28" min="1" max="1"/>
+    <col width="50" customWidth="1" style="28" min="2" max="2"/>
+    <col width="25" customWidth="1" style="28" min="3" max="3"/>
+    <col width="18" customWidth="1" style="28" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="26">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>HU-19 · Exportación de los 7 reportes definidos del contrato</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="26">
-      <c r="A2" s="37" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="28">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-06-03</t>
         </is>
       </c>
-      <c r="C2" s="37" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>Módulo: MOD-06</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="26">
-      <c r="A3" s="37" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="28">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Sprint sugerido: 9</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="39" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="26">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="28">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.95" customHeight="1" s="26">
+    <row r="6" ht="27.9" customHeight="1" s="28">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="35.1" customHeight="1" s="26">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="26" t="n"/>
+    </row>
+    <row r="7" ht="35.1" customHeight="1" s="28">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>descargar cualquiera de los 7 reportes definidos del contrato (avance físico, financiero, estimaciones, observaciones, bitácora, modificatorios, penalizaciones) en formato PDF o Excel según el reporte</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n"/>
-      <c r="D7" s="24" t="n"/>
-    </row>
-    <row r="8" ht="27.95" customHeight="1" s="26">
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="26" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="28">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>llevar la información del sistema a oficios, presentaciones o expedientes de auditoría</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="24" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="26">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="26" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="24" customHeight="1" s="28">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
-        <is>
-          <t>Criterio (aseveración)</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>Criterios de aceptación</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="26">
+    <row r="12" ht="32.1" customHeight="1" s="28">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>Cada uno de los 7 reportes definidos genera el archivo en el formato establecido (PDF, Excel o ambos).</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n"/>
+      <c r="C12" s="26" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="33" customHeight="1" s="26">
+    <row r="13" ht="33" customHeight="1" s="28">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>El usuario puede seleccionar el periodo (mensual, trimestral, acumulado) sin alterar el contenido predefinido del reporte.</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n"/>
+      <c r="C13" s="26" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="26">
-      <c r="A15" s="30" t="inlineStr">
+    <row r="14"/>
+    <row r="15" ht="24" customHeight="1" s="28">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="26">
+    <row r="16" ht="24" customHeight="1" s="28">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B16" s="40" t="inlineStr">
+      <c r="B16" s="42" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" s="26">
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="26" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B17" s="39" t="n">
+      <c r="B17" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="26">
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>Sprint 9</t>
         </is>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="26">
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="24" t="n"/>
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -4961,233 +5002,236 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="26" min="1" max="1"/>
-    <col width="50" customWidth="1" style="26" min="2" max="2"/>
-    <col width="25" customWidth="1" style="26" min="3" max="3"/>
-    <col width="18" customWidth="1" style="26" min="4" max="4"/>
+    <col width="16" customWidth="1" style="28" min="1" max="1"/>
+    <col width="50" customWidth="1" style="28" min="2" max="2"/>
+    <col width="25" customWidth="1" style="28" min="3" max="3"/>
+    <col width="18" customWidth="1" style="28" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="26">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>HU-20 · Tránsito a pago: carga de soportes y verificación de suficiencia presupuestal</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="26">
-      <c r="A2" s="37" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="28">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-07-01</t>
         </is>
       </c>
-      <c r="C2" s="37" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>Módulo: MOD-07</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="26">
-      <c r="A3" s="37" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="28">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Sprint sugerido: 5</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="39" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="26">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="28">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.95" customHeight="1" s="26">
+    <row r="6" ht="27.9" customHeight="1" s="28">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>contratista y finanzas</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="45" customHeight="1" s="26">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="26" t="n"/>
+    </row>
+    <row r="7" ht="45" customHeight="1" s="28">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>que al autorizarse una estimación el sistema verifique la suficiencia presupuestal (art. 24 LOPSRM), genere la instrucción de pago, permita cargar los soportes (factura, CFDI y fianza de cumplimiento cuando el contrato lo exija) y notifique a Finanzas con el plazo de 20 días naturales del art. 54 LOPSRM</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n"/>
-      <c r="D7" s="24" t="n"/>
-    </row>
-    <row r="8" ht="27.95" customHeight="1" s="26">
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="26" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="28">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>no perder el plazo de pago y dejar evidencia de la suficiencia presupuestal verificada, considerando que el incumplimiento del plazo de pago genera gastos financieros a cargo de la dependencia (art. 55 LOPSRM)</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="24" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="26">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="26" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="24" customHeight="1" s="28">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
-        <is>
-          <t>Criterio (aseveración)</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>Criterios de aceptación</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="26">
+    <row r="12" ht="32.1" customHeight="1" s="28">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>El sistema bloquea la instrucción de pago cuando la estimación excede el techo presupuestal disponible del contrato.</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n"/>
+      <c r="C12" s="26" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="33.95" customHeight="1" s="26">
+    <row r="13" ht="33.9" customHeight="1" s="28">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>El semáforo del plazo de pago (verde, ámbar, rojo) se calcula sobre los 20 días naturales y dispara alertas a Finanzas y Dependencia.</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n"/>
+      <c r="C13" s="26" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="36.95" customHeight="1" s="26">
+    <row r="14" ht="36.9" customHeight="1" s="28">
       <c r="A14" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>La instrucción de pago se genera solo cuando todos los soportes obligatorios (factura, CFDI y, cuando aplique, estado de cuenta de fianza) están cargados.</t>
         </is>
       </c>
-      <c r="C14" s="24" t="n"/>
+      <c r="C14" s="26" t="n"/>
       <c r="D14" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="26">
-      <c r="A16" s="30" t="inlineStr">
+    <row r="15"/>
+    <row r="16" ht="24" customHeight="1" s="28">
+      <c r="A16" s="32" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" s="26">
+    <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B17" s="38" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="26">
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B18" s="38" t="n">
+      <c r="B18" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="26">
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="24" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" s="26">
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="26" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" s="28">
       <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="35" t="inlineStr">
+      <c r="B20" s="37" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="C20" s="32" t="n"/>
-      <c r="D20" s="24" t="n"/>
+      <c r="C20" s="34" t="n"/>
+      <c r="D20" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -5223,223 +5267,226 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="26" min="1" max="1"/>
-    <col width="50" customWidth="1" style="26" min="2" max="2"/>
-    <col width="25" customWidth="1" style="26" min="3" max="3"/>
-    <col width="18" customWidth="1" style="26" min="4" max="4"/>
+    <col width="16" customWidth="1" style="28" min="1" max="1"/>
+    <col width="50" customWidth="1" style="28" min="2" max="2"/>
+    <col width="25" customWidth="1" style="28" min="3" max="3"/>
+    <col width="18" customWidth="1" style="28" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="26">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>HU-21 · Registro del pago efectuado</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="26">
-      <c r="A2" s="37" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="28">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-07-02</t>
         </is>
       </c>
-      <c r="C2" s="37" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>Módulo: MOD-07</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="26">
-      <c r="A3" s="37" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="28">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Sprint sugerido: 2</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="39" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="26">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="28">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.95" customHeight="1" s="26">
+    <row r="6" ht="27.9" customHeight="1" s="28">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>finanzas</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="27.95" customHeight="1" s="26">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="26" t="n"/>
+    </row>
+    <row r="7" ht="27.9" customHeight="1" s="28">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>registrar en el sistema el pago realizado de una estimación: fecha, importe, referencia bancaria y observaciones</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n"/>
-      <c r="D7" s="24" t="n"/>
-    </row>
-    <row r="8" ht="27.95" customHeight="1" s="26">
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="26" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="28">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>cerrar el ciclo de la estimación y actualizar el avance financiero del contrato</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="24" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="26">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="26" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="24" customHeight="1" s="28">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
-        <is>
-          <t>Criterio (aseveración)</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>Criterios de aceptación</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="26">
+    <row r="12" ht="32.1" customHeight="1" s="28">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>El registro del pago marca la estimación como pagada y actualiza el avance financiero del contrato.</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n"/>
+      <c r="C12" s="26" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="26">
+    <row r="13" ht="32.1" customHeight="1" s="28">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>Quedan capturados fecha, importe, referencia bancaria y usuario que realizó el registro.</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n"/>
+      <c r="C13" s="26" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="26">
-      <c r="A15" s="30" t="inlineStr">
+    <row r="14"/>
+    <row r="15" ht="24" customHeight="1" s="28">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="26">
+    <row r="16" ht="24" customHeight="1" s="28">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B16" s="33" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" s="26">
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="26" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B17" s="33" t="n">
+      <c r="B17" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="26">
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="26">
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="24" t="n"/>
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -5466,31 +5513,31 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="12" customWidth="1" style="26" min="1" max="1"/>
-    <col width="50" customWidth="1" style="26" min="2" max="2"/>
-    <col width="12" customWidth="1" style="26" min="3" max="3"/>
-    <col width="22" customWidth="1" style="26" min="4" max="4"/>
-    <col width="32" customWidth="1" style="26" min="5" max="5"/>
-    <col width="40" customWidth="1" style="26" min="6" max="6"/>
+    <col width="12" customWidth="1" style="28" min="1" max="1"/>
+    <col width="50" customWidth="1" style="28" min="2" max="2"/>
+    <col width="12" customWidth="1" style="28" min="3" max="3"/>
+    <col width="22" customWidth="1" style="28" min="4" max="4"/>
+    <col width="32" customWidth="1" style="28" min="5" max="5"/>
+    <col width="40" customWidth="1" style="28" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="26">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="28">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>Plan de iteraciones (Sprints)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="50.1" customHeight="1" s="26">
-      <c r="A2" s="25" t="inlineStr">
+    <row r="2" ht="50.1" customHeight="1" s="28">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Distribución de las 22 historias en 9 sprints. Velocidad objetivo: 9 puntos por sprint (3 integrantes × 3 días útiles × 1 punto por día-persona). Las historias complejas (8 user points): HU-09 emisión de notas, HU-12 integración de estimación, HU-15 revisión de estimación y HU-20 tránsito a pago, todas ubicadas en sprints 2-5 para mitigar el riesgo de retraso. Ningún sprint excede 10 puntos. Promedio: 9.4 pts/sprint.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32.1" customHeight="1" s="26">
+    <row r="4" ht="32.1" customHeight="1" s="28">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Sprint</t>
@@ -5522,20 +5569,20 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="66" customHeight="1" s="26">
-      <c r="A5" s="23" t="inlineStr">
+    <row r="5" ht="66" customHeight="1" s="28">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>• HU-00 Inicio de sesión por rol (1)
 • HU-01 Alta de contratos (5)
 • HU-08 Apertura formal de la bitácora del contrato (2)</t>
         </is>
       </c>
-      <c r="C5" s="38" t="n">
+      <c r="C5" s="40" t="n">
         <v>8</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -5554,19 +5601,19 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1" s="26">
-      <c r="A6" s="23" t="inlineStr">
+    <row r="6" ht="60" customHeight="1" s="28">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>• HU-09 Emisión y respuesta de notas tipificadas con firma (8)
 • HU-21 Registro del pago efectuado (2)</t>
         </is>
       </c>
-      <c r="C6" s="39" t="n">
+      <c r="C6" s="41" t="n">
         <v>10</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -5585,19 +5632,19 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1" s="26">
-      <c r="A7" s="23" t="inlineStr">
+    <row r="7" ht="60" customHeight="1" s="28">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>• HU-10 Consulta y búsqueda de notas de bitácora (2)
 • HU-12 Apertura del periodo e integración de la estimación (8)</t>
         </is>
       </c>
-      <c r="C7" s="39" t="n">
+      <c r="C7" s="41" t="n">
         <v>10</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -5616,19 +5663,19 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1" s="26">
-      <c r="A8" s="23" t="inlineStr">
+    <row r="8" ht="60" customHeight="1" s="28">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>• HU-04 Consulta integrada del expediente contractual (2)
 • HU-15 Recepción, revisión técnica y autorización de la estimación (8)</t>
         </is>
       </c>
-      <c r="C8" s="39" t="n">
+      <c r="C8" s="41" t="n">
         <v>10</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -5647,19 +5694,19 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1" s="26">
-      <c r="A9" s="23" t="inlineStr">
+    <row r="9" ht="60" customHeight="1" s="28">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="B9" s="31" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>• HU-14 Historial de estimaciones del contrato (2)
 • HU-20 Tránsito a pago: carga de soportes y verificación de suficiencia presupuestal (8)</t>
         </is>
       </c>
-      <c r="C9" s="39" t="n">
+      <c r="C9" s="41" t="n">
         <v>10</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -5678,20 +5725,20 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="66" customHeight="1" s="26">
-      <c r="A10" s="23" t="inlineStr">
+    <row r="10" ht="66" customHeight="1" s="28">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>Sprint 6</t>
         </is>
       </c>
-      <c r="B10" s="31" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>• HU-02 Registro de fianzas y garantías (2)
 • HU-03 Trámite y aplicación de convenios modificatorios (5)
 • HU-07 Configuración de alertas de atraso por concepto (2)</t>
         </is>
       </c>
-      <c r="C10" s="38" t="n">
+      <c r="C10" s="40" t="n">
         <v>9</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -5710,13 +5757,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="66" customHeight="1" s="26">
-      <c r="A11" s="23" t="inlineStr">
+    <row r="11" ht="66" customHeight="1" s="28">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>Sprint 7</t>
         </is>
       </c>
-      <c r="B11" s="31" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>• HU-05 Visualización del programa y curva de avance (3)
 • HU-06 Registro de trabajos terminados por periodo (3)
@@ -5742,20 +5789,20 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="66" customHeight="1" s="26">
-      <c r="A12" s="23" t="inlineStr">
+    <row r="12" ht="66" customHeight="1" s="28">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>Sprint 8</t>
         </is>
       </c>
-      <c r="B12" s="31" t="inlineStr">
+      <c r="B12" s="33" t="inlineStr">
         <is>
           <t>• HU-13 Envío de la estimación (3)
 • HU-16 Reingreso de estimación tras rechazo (3)
 • HU-17 Tablero de estimaciones aceptadas y en proceso (3)</t>
         </is>
       </c>
-      <c r="C12" s="39" t="n">
+      <c r="C12" s="41" t="n">
         <v>9</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -5774,19 +5821,19 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1" s="26">
-      <c r="A13" s="23" t="inlineStr">
+    <row r="13" ht="60" customHeight="1" s="28">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t>Sprint 9</t>
         </is>
       </c>
-      <c r="B13" s="31" t="inlineStr">
+      <c r="B13" s="33" t="inlineStr">
         <is>
           <t>• HU-18 Vista ejecutiva del portafolio con semáforos (5)
 • HU-19 Exportación de los 7 reportes definidos del contrato (5)</t>
         </is>
       </c>
-      <c r="C13" s="39" t="n">
+      <c r="C13" s="41" t="n">
         <v>10</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -5819,8 +5866,8 @@
       <c r="C14" s="20" t="n">
         <v>85</v>
       </c>
-      <c r="D14" s="22" t="inlineStr"/>
-      <c r="E14" s="22" t="inlineStr"/>
+      <c r="D14" s="22" t="n"/>
+      <c r="E14" s="22" t="n"/>
       <c r="F14" s="22" t="inlineStr">
         <is>
           <t>Velocidad objetivo: 9 pts/sprint (3 personas × 3 días útiles × 1 pt/día-persona)</t>
@@ -5844,233 +5891,236 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="26" min="1" max="1"/>
-    <col width="50" customWidth="1" style="26" min="2" max="2"/>
-    <col width="25" customWidth="1" style="26" min="3" max="3"/>
-    <col width="18" customWidth="1" style="26" min="4" max="4"/>
+    <col width="16" customWidth="1" style="28" min="1" max="1"/>
+    <col width="50" customWidth="1" style="28" min="2" max="2"/>
+    <col width="25" customWidth="1" style="28" min="3" max="3"/>
+    <col width="18" customWidth="1" style="28" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="26">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>HU-01 · Alta de contratos</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="26">
-      <c r="A2" s="37" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="28">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-01-01</t>
         </is>
       </c>
-      <c r="C2" s="37" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>Módulo: MOD-01</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="26">
-      <c r="A3" s="37" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="28">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Sprint sugerido: 1</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="39" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="26">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="28">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.95" customHeight="1" s="26">
+    <row r="6" ht="27.9" customHeight="1" s="28">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="33.95" customHeight="1" s="26">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="26" t="n"/>
+    </row>
+    <row r="7" ht="98.40000000000001" customHeight="1" s="28">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>dar de alta un contrato nuevo capturando en un solo flujo todos sus elementos: datos generales (folio, partes, monto, plazos, modalidad de pago), catálogo de conceptos, programa de obra mes a mes, elementos jurídicos del contrato, garantías (pólizas de anticipo, cumplimiento y vicios ocultos), penalizaciones aplicables (incluida la retención del 5 al millar conforme al art. 191 de la Ley Federal de Derechos), plan de amortización del anticipo otorgado, y el PDF firmado del contrato como respaldo documental</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n"/>
-      <c r="D7" s="24" t="n"/>
-    </row>
-    <row r="8" ht="27.95" customHeight="1" s="26">
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="26" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="28">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>tener el soporte documental del contrato en línea, disponible para los actores autorizados</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="24" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="26">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="26" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="24" customHeight="1" s="28">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
-        <is>
-          <t>Criterio (aseveración)</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>Criterios de aceptación</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="26">
+    <row r="12" ht="61.2" customHeight="1" s="28">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>Existe un contrato con folio único que contiene catálogo de conceptos, programa de obra, elementos jurídicos, garantías (anticipo, cumplimiento, vicios ocultos), penalizaciones aplicables, plan de amortización del anticipo y PDF firmado.</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n"/>
+      <c r="C12" s="26" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="26">
+    <row r="13" ht="32.1" customHeight="1" s="28">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>El sistema valida que los campos obligatorios estén llenos y el folio sea único antes de guardar; si falta alguno, no permite el guardado y señala el campo faltante.</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n"/>
+      <c r="C13" s="26" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32.1" customHeight="1" s="26">
+    <row r="14" ht="32.1" customHeight="1" s="28">
       <c r="A14" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>Existe un PDF firmado del contrato ligado al expediente, consultable por todos los actores autorizados.</t>
         </is>
       </c>
-      <c r="C14" s="24" t="n"/>
+      <c r="C14" s="26" t="n"/>
       <c r="D14" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="26">
-      <c r="A16" s="30" t="inlineStr">
+    <row r="15"/>
+    <row r="16" ht="24" customHeight="1" s="28">
+      <c r="A16" s="32" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" s="26">
+    <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B17" s="38" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="26">
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B18" s="39" t="n">
+      <c r="B18" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="26">
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="24" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" s="26">
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="26" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" s="28">
       <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="35" t="inlineStr">
+      <c r="B20" s="37" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="C20" s="32" t="n"/>
-      <c r="D20" s="24" t="n"/>
+      <c r="C20" s="34" t="n"/>
+      <c r="D20" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -6106,238 +6156,240 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="26" min="1" max="1"/>
-    <col width="50" customWidth="1" style="26" min="2" max="2"/>
-    <col width="25" customWidth="1" style="26" min="3" max="3"/>
-    <col width="18" customWidth="1" style="26" min="4" max="4"/>
+    <col width="16" customWidth="1" style="28" min="1" max="1"/>
+    <col width="50" customWidth="1" style="28" min="2" max="2"/>
+    <col width="25" customWidth="1" style="28" min="3" max="3"/>
+    <col width="18" customWidth="1" style="28" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="26">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>HU-02 · Registro de fianzas y garantías</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="26">
-      <c r="A2" s="37" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="28">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-01-02</t>
         </is>
       </c>
-      <c r="C2" s="37" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>Módulo: MOD-01</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="26">
-      <c r="A3" s="37" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="28">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Sprint sugerido: 6</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="39" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="26">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="28">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.95" customHeight="1" s="26">
+    <row r="6" ht="27.9" customHeight="1" s="28">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>dependencia</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="29.1" customHeight="1" s="26">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="26" t="n"/>
+    </row>
+    <row r="7" ht="29.1" customHeight="1" s="28">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>subir las pólizas de fianza del contrato (cumplimiento, vicios ocultos, anticipo) con sus metadatos: vigencia, afianzadora y monto afianzado</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n"/>
-      <c r="D7" s="24" t="n"/>
-    </row>
-    <row r="8" ht="27.95" customHeight="1" s="26">
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="26" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="28">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>contar con el respaldo documental de las garantías del contrato y ser notificado cuando una póliza esté por vencer</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="24" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="26">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="26" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="24" customHeight="1" s="28">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
-        <is>
-          <t>Criterio (aseveración)</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>Criterios de aceptación</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="26">
+    <row r="12" ht="32.1" customHeight="1" s="28">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>La póliza queda ligada al contrato con afianzadora, vigencia y monto registrados.</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n"/>
+      <c r="C12" s="26" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="26">
+    <row r="13" ht="32.1" customHeight="1" s="28">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>El sistema emite alerta cuando faltan N días configurables para el vencimiento de la póliza.</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n"/>
+      <c r="C13" s="26" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="27.6" customHeight="1" s="28">
       <c r="A14" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>La póliza registrada puede consultarse en formato PDF desde el listado de fianzas del contrato.</t>
         </is>
       </c>
-      <c r="D14" s="41" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="26">
-      <c r="A15" s="30" t="inlineStr">
+    <row r="15" ht="24" customHeight="1" s="28">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="26">
+    <row r="16" ht="24" customHeight="1" s="28">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B16" s="40" t="inlineStr">
+      <c r="B16" s="42" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" s="26">
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="26" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B17" s="33" t="n">
+      <c r="B17" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="26">
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>Sprint 6</t>
         </is>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="26">
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="24" t="n"/>
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -6364,223 +6416,226 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="26" min="1" max="1"/>
-    <col width="50" customWidth="1" style="26" min="2" max="2"/>
-    <col width="25" customWidth="1" style="26" min="3" max="3"/>
-    <col width="18" customWidth="1" style="26" min="4" max="4"/>
+    <col width="16" customWidth="1" style="28" min="1" max="1"/>
+    <col width="50" customWidth="1" style="28" min="2" max="2"/>
+    <col width="25" customWidth="1" style="28" min="3" max="3"/>
+    <col width="18" customWidth="1" style="28" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="26">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>HU-03 · Trámite y aplicación de convenios modificatorios</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="26">
-      <c r="A2" s="37" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="28">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-01-03</t>
         </is>
       </c>
-      <c r="C2" s="37" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>Módulo: MOD-01</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="26">
-      <c r="A3" s="37" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="28">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Sprint sugerido: 6</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="39" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="26">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="28">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.95" customHeight="1" s="26">
+    <row r="6" ht="27.9" customHeight="1" s="28">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>dependencia</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="33" customHeight="1" s="26">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="26" t="n"/>
+    </row>
+    <row r="7" ht="33" customHeight="1" s="28">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>registrar un convenio modificatorio del contrato (cambios al monto, plazo o conceptos) y aplicar las actualizaciones al catálogo, programa y fianzas, manteniendo el histórico de versiones</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n"/>
-      <c r="D7" s="24" t="n"/>
-    </row>
-    <row r="8" ht="27.95" customHeight="1" s="26">
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="26" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="28">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>documentar formalmente los cambios al contrato conforme a los arts. 59 y 59 Bis LOPSRM (este último cuando la modificación supera el 50% del importe o del plazo) y poder consultar qué cambió, cuándo y por qué</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="24" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="26">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="26" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="24" customHeight="1" s="28">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
-        <is>
-          <t>Criterio (aseveración)</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>Criterios de aceptación</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="33" customHeight="1" s="26">
+    <row r="12" ht="33" customHeight="1" s="28">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>Al autorizarse el modificatorio se generó una nueva versión del catálogo y del programa, sin alterar la versión anterior.</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n"/>
+      <c r="C12" s="26" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="26">
+    <row r="13" ht="32.1" customHeight="1" s="28">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>El histórico de versiones registra fecha, autor y motivo del cambio para cada modificatorio.</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n"/>
+      <c r="C13" s="26" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="26">
-      <c r="A15" s="30" t="inlineStr">
+    <row r="14"/>
+    <row r="15" ht="24" customHeight="1" s="28">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="26">
+    <row r="16" ht="24" customHeight="1" s="28">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B16" s="38" t="inlineStr">
+      <c r="B16" s="40" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" s="26">
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="26" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B17" s="39" t="n">
+      <c r="B17" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="26">
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>Sprint 6</t>
         </is>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="26">
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="24" t="n"/>
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -6607,223 +6662,226 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="26" min="1" max="1"/>
-    <col width="50" customWidth="1" style="26" min="2" max="2"/>
-    <col width="25" customWidth="1" style="26" min="3" max="3"/>
-    <col width="18" customWidth="1" style="26" min="4" max="4"/>
+    <col width="16" customWidth="1" style="28" min="1" max="1"/>
+    <col width="50" customWidth="1" style="28" min="2" max="2"/>
+    <col width="25" customWidth="1" style="28" min="3" max="3"/>
+    <col width="18" customWidth="1" style="28" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="26">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>HU-04 · Consulta integrada del expediente contractual</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="26">
-      <c r="A2" s="37" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="28">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-01-04</t>
         </is>
       </c>
-      <c r="C2" s="37" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>Módulo: MOD-01</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="26">
-      <c r="A3" s="37" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="28">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Sprint sugerido: 4</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="39" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="26">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="28">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.95" customHeight="1" s="26">
+    <row r="6" ht="27.9" customHeight="1" s="28">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="29.1" customHeight="1" s="26">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="26" t="n"/>
+    </row>
+    <row r="7" ht="29.1" customHeight="1" s="28">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>consultar en una sola vista todos los elementos vigentes del contrato (configuración, catálogo, programa, fianzas, elementos jurídicos) con buscador</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n"/>
-      <c r="D7" s="24" t="n"/>
-    </row>
-    <row r="8" ht="27.95" customHeight="1" s="26">
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="26" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="28">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>obtener información del contrato sin tener que ir a cada módulo individualmente</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="24" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="26">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="26" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="24" customHeight="1" s="28">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
-        <is>
-          <t>Criterio (aseveración)</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>Criterios de aceptación</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="26">
+    <row r="12" ht="32.1" customHeight="1" s="28">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>La pantalla muestra los cinco bloques (configuración, catálogo, programa, fianzas, jurídicos) en una sola vista.</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n"/>
+      <c r="C12" s="26" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="26">
+    <row r="13" ht="32.1" customHeight="1" s="28">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>El buscador permite filtrar por folio, contratista, objeto, periodo o tipo de documento.</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n"/>
+      <c r="C13" s="26" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="26">
-      <c r="A15" s="30" t="inlineStr">
+    <row r="14"/>
+    <row r="15" ht="24" customHeight="1" s="28">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="26">
+    <row r="16" ht="24" customHeight="1" s="28">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B16" s="33" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" s="26">
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="26" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B17" s="33" t="n">
+      <c r="B17" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="26">
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="26">
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="24" t="n"/>
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -6850,223 +6908,226 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="26" min="1" max="1"/>
-    <col width="50" customWidth="1" style="26" min="2" max="2"/>
-    <col width="25" customWidth="1" style="26" min="3" max="3"/>
-    <col width="18" customWidth="1" style="26" min="4" max="4"/>
+    <col width="16" customWidth="1" style="28" min="1" max="1"/>
+    <col width="50" customWidth="1" style="28" min="2" max="2"/>
+    <col width="25" customWidth="1" style="28" min="3" max="3"/>
+    <col width="18" customWidth="1" style="28" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="26">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>HU-05 · Visualización del programa y curva de avance</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="26">
-      <c r="A2" s="37" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="28">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-02-01</t>
         </is>
       </c>
-      <c r="C2" s="37" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>Módulo: MOD-02</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="26">
-      <c r="A3" s="37" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="28">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Sprint sugerido: 7</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="39" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="26">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="28">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.95" customHeight="1" s="26">
+    <row r="6" ht="27.9" customHeight="1" s="28">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="27.95" customHeight="1" s="26">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="26" t="n"/>
+    </row>
+    <row r="7" ht="27.9" customHeight="1" s="28">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>visualizar la curva S del contrato comparando avance programado, ejecutado y financiero, con filtros por concepto y periodo</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n"/>
-      <c r="D7" s="24" t="n"/>
-    </row>
-    <row r="8" ht="27.95" customHeight="1" s="26">
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="26" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="28">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>identificar desviaciones entre lo planeado, lo ejecutado y lo cobrado para tomar decisiones a tiempo</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="24" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="26">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="26" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="24" customHeight="1" s="28">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
-        <is>
-          <t>Criterio (aseveración)</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>Criterios de aceptación</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="26">
+    <row r="12" ht="32.1" customHeight="1" s="28">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>La pantalla grafica las tres curvas (programado, ejecutado, financiero) en un solo gráfico.</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n"/>
+      <c r="C12" s="26" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="26">
+    <row r="13" ht="32.1" customHeight="1" s="28">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>Los filtros por concepto y periodo modifican la gráfica y los porcentajes calculados.</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n"/>
+      <c r="C13" s="26" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="26">
-      <c r="A15" s="30" t="inlineStr">
+    <row r="14"/>
+    <row r="15" ht="24" customHeight="1" s="28">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="26">
+    <row r="16" ht="24" customHeight="1" s="28">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B16" s="40" t="inlineStr">
+      <c r="B16" s="42" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" s="26">
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="26" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B17" s="40" t="n">
+      <c r="B17" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="26">
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>Sprint 7</t>
         </is>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="26">
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="24" t="n"/>
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -7093,223 +7154,226 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="26" min="1" max="1"/>
-    <col width="50" customWidth="1" style="26" min="2" max="2"/>
-    <col width="25" customWidth="1" style="26" min="3" max="3"/>
-    <col width="18" customWidth="1" style="26" min="4" max="4"/>
+    <col width="16" customWidth="1" style="28" min="1" max="1"/>
+    <col width="50" customWidth="1" style="28" min="2" max="2"/>
+    <col width="25" customWidth="1" style="28" min="3" max="3"/>
+    <col width="18" customWidth="1" style="28" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="26">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>HU-06 · Registro de trabajos terminados por periodo</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="26">
-      <c r="A2" s="37" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="28">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-02-02</t>
         </is>
       </c>
-      <c r="C2" s="37" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>Módulo: MOD-02</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="26">
-      <c r="A3" s="37" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="28">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Sprint sugerido: 7</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="39" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="26">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="28">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.95" customHeight="1" s="26">
+    <row r="6" ht="27.9" customHeight="1" s="28">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>contratista</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="29.1" customHeight="1" s="26">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="26" t="n"/>
+    </row>
+    <row r="7" ht="29.1" customHeight="1" s="28">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>registrar por periodo las cantidades terminadas por cada concepto del catálogo, vinculando cada registro a su nota de bitácora del tipo Entrega</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n"/>
-      <c r="D7" s="24" t="n"/>
-    </row>
-    <row r="8" ht="27.95" customHeight="1" s="26">
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="26" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="28">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>alimentar la integración de la estimación con el avance real y dejar respaldo documental de cada cantidad reportada</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="24" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="26">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="26" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="24" customHeight="1" s="28">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
-        <is>
-          <t>Criterio (aseveración)</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>Criterios de aceptación</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="26">
+    <row r="12" ht="32.1" customHeight="1" s="28">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>Cada cantidad capturada queda ligada al concepto del catálogo correspondiente y a una nota de bitácora del periodo.</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n"/>
+      <c r="C12" s="26" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="26">
+    <row r="13" ht="32.1" customHeight="1" s="28">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>El sistema bloquea el registro cuando la cantidad acumulada excede la contratada.</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n"/>
+      <c r="C13" s="26" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="26">
-      <c r="A15" s="30" t="inlineStr">
+    <row r="14"/>
+    <row r="15" ht="24" customHeight="1" s="28">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="26">
+    <row r="16" ht="24" customHeight="1" s="28">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B16" s="40" t="inlineStr">
+      <c r="B16" s="42" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" s="26">
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="26" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B17" s="40" t="n">
+      <c r="B17" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="26">
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>Sprint 7</t>
         </is>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="26">
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="24" t="n"/>
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -7336,223 +7400,226 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="26" min="1" max="1"/>
-    <col width="50" customWidth="1" style="26" min="2" max="2"/>
-    <col width="25" customWidth="1" style="26" min="3" max="3"/>
-    <col width="18" customWidth="1" style="26" min="4" max="4"/>
+    <col width="16" customWidth="1" style="28" min="1" max="1"/>
+    <col width="50" customWidth="1" style="28" min="2" max="2"/>
+    <col width="25" customWidth="1" style="28" min="3" max="3"/>
+    <col width="18" customWidth="1" style="28" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="26">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>HU-07 · Configuración de alertas de atraso por concepto</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="26">
-      <c r="A2" s="37" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="28">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-02-03</t>
         </is>
       </c>
-      <c r="C2" s="37" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>Módulo: MOD-02</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="26">
-      <c r="A3" s="37" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="28">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Sprint sugerido: 6</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="39" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="26">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="28">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.95" customHeight="1" s="26">
+    <row r="6" ht="27.9" customHeight="1" s="28">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="29.1" customHeight="1" s="26">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="26" t="n"/>
+    </row>
+    <row r="7" ht="29.1" customHeight="1" s="28">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>configurar qué conceptos del contrato quiero vigilar, el umbral de atraso a partir del cual quiero ser notificado y el canal de notificación</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n"/>
-      <c r="D7" s="24" t="n"/>
-    </row>
-    <row r="8" ht="27.95" customHeight="1" s="26">
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="26" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="28">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>recibir alertas solo de lo que decidí vigilar, sin saturación de notificaciones</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="24" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="26">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="26" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="24" customHeight="1" s="28">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
-        <is>
-          <t>Criterio (aseveración)</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>Criterios de aceptación</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="26">
+    <row r="12" ht="32.1" customHeight="1" s="28">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>Se pueden crear, pausar y eliminar alertas por concepto sin alterar las del resto.</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n"/>
+      <c r="C12" s="26" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="26">
+    <row r="13" ht="32.1" customHeight="1" s="28">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>El sistema solo dispara alertas cuando el avance real es menor al umbral configurado por el usuario.</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n"/>
+      <c r="C13" s="26" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="26">
-      <c r="A15" s="30" t="inlineStr">
+    <row r="14"/>
+    <row r="15" ht="24" customHeight="1" s="28">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="26">
+    <row r="16" ht="24" customHeight="1" s="28">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B16" s="33" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" s="26">
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="26" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B17" s="33" t="n">
+      <c r="B17" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="26">
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>Sprint 6</t>
         </is>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="26">
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="24" t="n"/>
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>

--- a/docs/Historias_Usuario.xlsx
+++ b/docs/Historias_Usuario.xlsx
@@ -1932,7 +1932,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -1943,8 +1943,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="B12" s="36" t="inlineStr">
         <is>
-          <t>Solo aparecen disponibles los tipos de nota que corresponden al rol del usuario.</t>
+          <t>Solo aparecen los tipos de nota que corresponden al rol del usuario.</t>
         </is>
       </c>
       <c r="C12" s="26" t="n"/>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B14" s="36" t="inlineStr">
         <is>
-          <t>Cada nota queda registrada con folio, fecha, firmante y vínculo opcional a una nota previa.</t>
+          <t>Cada nota queda registrada con folio, fecha, firmante y vínculo opcional a nota previa.</t>
         </is>
       </c>
       <c r="C14" s="26" t="n"/>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="B20" s="37" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="C20" s="34" t="n"/>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -2454,8 +2454,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -2700,8 +2700,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="B13" s="36" t="inlineStr">
         <is>
-          <t>La carátula calcula automáticamente el anticipo amortizado (proporcional, art. 143 RLOPSRM), las retenciones legales (5 al millar, art. 191 LFD) y las deductivas por penalizaciones según el contrato.</t>
+          <t>La carátula calcula automáticamente anticipo amortizado, retenciones legales (5 al millar) y deductivas por penalizaciones según el contrato.</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="B14" s="36" t="inlineStr">
         <is>
-          <t>El sistema bloquea la integración cuando una cantidad por concepto excede la cantidad contratada en el catálogo (art. 118 RLOPSRM: los trabajos por mayor valor sin orden escrita no son pagables).</t>
+          <t>El sistema bloquea la integración cuando una cantidad por concepto excede la cantidad contratada en el catálogo (art. 118 RLOPSRM).</t>
         </is>
       </c>
       <c r="C14" s="26" t="n"/>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="B20" s="37" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="C20" s="34" t="n"/>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -3211,8 +3211,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B12" s="36" t="inlineStr">
         <is>
-          <t>La lista incluye todas las versiones (incluyendo rechazadas) con su periodo, estado e importe.</t>
+          <t>El historial muestra todas las estimaciones del contrato, incluyendo las versiones rechazadas.</t>
         </is>
       </c>
       <c r="C12" s="26" t="n"/>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="B13" s="36" t="inlineStr">
         <is>
-          <t>Solo existe una estimación con estado 'aceptada' por periodo, mientras que pueden existir múltiples rechazadas.</t>
+          <t>Por cada periodo solo puede haber una estimación aceptada; las versiones previas quedan marcadas como rechazadas.</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -3457,8 +3457,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="B12" s="36" t="inlineStr">
         <is>
-          <t>La pantalla muestra todas las secciones de la estimación con posibilidad de registrar observaciones puntuales por sección.</t>
+          <t>La revisión permite revisar sección por sección y dejar observaciones puntuales en cada una (carátula, generadores, registro fotográfico, soportes y notas).</t>
         </is>
       </c>
       <c r="C12" s="26" t="n"/>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B13" s="36" t="inlineStr">
         <is>
-          <t>El flujo obliga a la supervisión a turnar la estimación antes de que residencia pueda autorizar o rechazar.</t>
+          <t>La autorización queda condicionada al turnado secuencial: primero supervisión, luego residencia; residencia no puede resolver antes del turnado.</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="B14" s="36" t="inlineStr">
         <is>
-          <t>El sistema emite alertas cuando una estimación permanece más del plazo configurado en un mismo estado (art. 54 LOPSRM).</t>
+          <t>El sistema controla el plazo de 15 días naturales de revisión conforme al art. 54 LOPSRM mediante un semáforo visible para los actores.</t>
         </is>
       </c>
       <c r="C14" s="26" t="n"/>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="B20" s="37" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="C20" s="34" t="n"/>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -3968,8 +3968,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="B13" s="36" t="inlineStr">
         <is>
-          <t>El panel 'Mis pendientes' filtra los pendientes según el rol del usuario autenticado.</t>
+          <t>El panel "Mis pendientes" filtra los pendientes según el rol del usuario autenticado.</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -4214,8 +4214,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B20" s="37" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="C20" s="34" t="n"/>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -4728,8 +4728,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -4974,8 +4974,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -5125,7 +5125,7 @@
       </c>
       <c r="B12" s="36" t="inlineStr">
         <is>
-          <t>El sistema bloquea la instrucción de pago cuando la estimación excede el techo presupuestal disponible del contrato.</t>
+          <t>El sistema verifica suficiencia presupuestal contra el techo anual y bloquea la generación de la instrucción de pago si el monto excede lo disponible (art. 24 LOPSRM).</t>
         </is>
       </c>
       <c r="C12" s="26" t="n"/>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="B13" s="36" t="inlineStr">
         <is>
-          <t>El semáforo del plazo de pago (verde, ámbar, rojo) se calcula sobre los 20 días naturales y dispara alertas a Finanzas y Dependencia.</t>
+          <t>Un semáforo muestra el avance del plazo de 20 días naturales para pago (art. 54 LOPSRM) y emite alertas al entrar en amarillo.</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="B14" s="36" t="inlineStr">
         <is>
-          <t>La instrucción de pago se genera solo cuando todos los soportes obligatorios (factura, CFDI y, cuando aplique, estado de cuenta de fianza) están cargados.</t>
+          <t>La instrucción de pago solo puede generarse cuando todos los soportes obligatorios (factura, CFDI, estado de fianza) están cargados.</t>
         </is>
       </c>
       <c r="C14" s="26" t="n"/>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="B20" s="37" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="C20" s="34" t="n"/>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -5485,8 +5485,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="B12" s="36" t="inlineStr">
         <is>
-          <t>Existe un contrato con folio único que contiene catálogo de conceptos, programa de obra, elementos jurídicos, garantías (anticipo, cumplimiento, vicios ocultos), penalizaciones aplicables, plan de amortización del anticipo y PDF firmado.</t>
+          <t>Existe un contrato con folio único que contiene catálogo de conceptos, programa de obra, elementos jurídicos, garantías, penalizaciones, plan de amortización del anticipo y PDF firmado.</t>
         </is>
       </c>
       <c r="C12" s="26" t="n"/>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="B13" s="36" t="inlineStr">
         <is>
-          <t>El sistema valida que los campos obligatorios estén llenos y el folio sea único antes de guardar; si falta alguno, no permite el guardado y señala el campo faltante.</t>
+          <t>El sistema valida que los campos obligatorios estén llenos y el folio sea único antes de guardar.</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="B20" s="37" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="C20" s="34" t="n"/>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="B13" s="36" t="inlineStr">
         <is>
-          <t>El sistema emite alerta cuando faltan N días configurables para el vencimiento de la póliza.</t>
+          <t>El sistema emite alerta cuando faltan N días configurables para el vencimiento.</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -6388,8 +6388,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -6634,8 +6634,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="B12" s="36" t="inlineStr">
         <is>
-          <t>La pantalla muestra los cinco bloques (configuración, catálogo, programa, fianzas, jurídicos) en una sola vista.</t>
+          <t>El expediente muestra en una sola vista los 5 bloques: configuración, catálogo, programa, fianzas y documentos jurídicos.</t>
         </is>
       </c>
       <c r="C12" s="26" t="n"/>
@@ -6803,7 +6803,7 @@
       </c>
       <c r="B13" s="36" t="inlineStr">
         <is>
-          <t>El buscador permite filtrar por folio, contratista, objeto, periodo o tipo de documento.</t>
+          <t>El buscador filtra los bloques por folio, contratista, objeto, periodo o tipo de documento.</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -6880,8 +6880,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -7126,8 +7126,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -7372,8 +7372,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -7607,7 +7607,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -7618,8 +7618,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>

--- a/docs/Historias_Usuario.xlsx
+++ b/docs/Historias_Usuario.xlsx
@@ -1932,7 +1932,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Terminado</t>
+          <t>En desarrollo</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -1943,8 +1943,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="B20" s="37" t="inlineStr">
         <is>
-          <t>Terminado</t>
+          <t>En desarrollo</t>
         </is>
       </c>
       <c r="C20" s="34" t="n"/>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Terminado</t>
+          <t>En desarrollo</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -2454,8 +2454,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Terminado</t>
+          <t>En desarrollo</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -2700,8 +2700,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="B20" s="37" t="inlineStr">
         <is>
-          <t>Terminado</t>
+          <t>En desarrollo</t>
         </is>
       </c>
       <c r="C20" s="34" t="n"/>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Terminado</t>
+          <t>En desarrollo</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -3211,8 +3211,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Terminado</t>
+          <t>En desarrollo</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -3457,8 +3457,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="B20" s="37" t="inlineStr">
         <is>
-          <t>Terminado</t>
+          <t>En desarrollo</t>
         </is>
       </c>
       <c r="C20" s="34" t="n"/>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Terminado</t>
+          <t>En desarrollo</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -3968,8 +3968,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Terminado</t>
+          <t>En desarrollo</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -4214,8 +4214,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Terminado</t>
+          <t>En desarrollo</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -4728,8 +4728,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Terminado</t>
+          <t>En desarrollo</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -4974,8 +4974,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="B20" s="37" t="inlineStr">
         <is>
-          <t>Terminado</t>
+          <t>En desarrollo</t>
         </is>
       </c>
       <c r="C20" s="34" t="n"/>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Terminado</t>
+          <t>En desarrollo</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -5485,8 +5485,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Terminado</t>
+          <t>En desarrollo</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -6388,8 +6388,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Terminado</t>
+          <t>En desarrollo</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -6634,8 +6634,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Terminado</t>
+          <t>En desarrollo</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -6880,8 +6880,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Terminado</t>
+          <t>En desarrollo</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -7126,8 +7126,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Terminado</t>
+          <t>En desarrollo</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -7372,8 +7372,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -7607,7 +7607,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Terminado</t>
+          <t>En desarrollo</t>
         </is>
       </c>
       <c r="C19" s="34" t="n"/>
@@ -7618,8 +7618,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>

--- a/docs/Historias_Usuario.xlsx
+++ b/docs/Historias_Usuario.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="600" firstSheet="0" activeTab="9" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" tabRatio="600" firstSheet="8" activeTab="8" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Índice" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,11 +13,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HU-03" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HU-04" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HU-05" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HU-06" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HU-07" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HU-08" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HU-09" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HU-10" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HU-08" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HU-10" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HU-06" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HU-07" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HU-09" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HU-11" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HU-12" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HU-13" sheetId="15" state="visible" r:id="rId15"/>
@@ -30,6 +30,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HU-20" sheetId="22" state="visible" r:id="rId22"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HU-21" sheetId="23" state="visible" r:id="rId23"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan_Iteraciones" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -290,39 +291,39 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -710,39 +711,39 @@
   </cols>
   <sheetData>
     <row r="1" ht="23.25" customHeight="1" s="28">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>SIGECOP — Historias de Usuario</t>
         </is>
       </c>
     </row>
     <row r="2" ht="39.9" customHeight="1" s="28">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="37" t="inlineStr">
         <is>
           <t>Sistema de Gestión Técnico-Administrativa de Contratos de Obra Pública. 22 historias siguiendo el formato dictado por el profesor.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" s="28">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="36" t="inlineStr">
         <is>
           <t>Total historias</t>
         </is>
       </c>
       <c r="B4" s="26" t="n"/>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="36" t="inlineStr">
         <is>
           <t>Total user points</t>
         </is>
       </c>
       <c r="D4" s="26" t="n"/>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="36" t="inlineStr">
         <is>
           <t>Total sprints planeados</t>
         </is>
       </c>
       <c r="F4" s="26" t="n"/>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="36" t="inlineStr">
         <is>
           <t>Velocidad promedio del equipo</t>
         </is>
@@ -750,21 +751,21 @@
       <c r="H4" s="26" t="n"/>
     </row>
     <row r="5" ht="32.1" customHeight="1" s="28">
-      <c r="A5" s="29" t="n">
+      <c r="A5" s="38" t="n">
         <v>22</v>
       </c>
       <c r="B5" s="26" t="n"/>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="38" t="n">
         <v>85</v>
       </c>
       <c r="D5" s="26" t="n"/>
-      <c r="E5" s="29" t="inlineStr">
+      <c r="E5" s="38" t="inlineStr">
         <is>
           <t>1-9</t>
         </is>
       </c>
       <c r="F5" s="26" t="n"/>
-      <c r="G5" s="29" t="inlineStr">
+      <c r="G5" s="38" t="inlineStr">
         <is>
           <t>9.4 pts/sprint</t>
         </is>
@@ -772,7 +773,7 @@
       <c r="H5" s="26" t="n"/>
     </row>
     <row r="8" ht="15.75" customHeight="1" s="28">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>Tabla resumen de las 22 historias</t>
         </is>
@@ -1734,39 +1735,38 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="30" t="inlineStr">
-        <is>
-          <t>HU-08 · Apertura formal de la bitácora del contrato</t>
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>HU-06 · Registro de trabajos terminados por periodo</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="39" t="inlineStr">
-        <is>
-          <t>Servicio implementado: SRV-03-01</t>
-        </is>
-      </c>
-      <c r="C2" s="39" t="inlineStr">
-        <is>
-          <t>Módulo: MOD-03</t>
+      <c r="A2" s="32" t="inlineStr">
+        <is>
+          <t>Servicio implementado: SRV-02-02</t>
+        </is>
+      </c>
+      <c r="C2" s="32" t="inlineStr">
+        <is>
+          <t>Módulo: MOD-02</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="39" t="inlineStr">
-        <is>
-          <t>Sprint sugerido: 1</t>
-        </is>
-      </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
+        <is>
+          <t>Sprint sugerido: 7</t>
+        </is>
+      </c>
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
@@ -1778,26 +1778,26 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
-        <is>
-          <t>residente</t>
-        </is>
-      </c>
-      <c r="C6" s="34" t="n"/>
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>contratista</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="n"/>
       <c r="D6" s="26" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1" s="28">
+    <row r="7" ht="29.1" customHeight="1" s="28">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
-        <is>
-          <t>aperturar la bitácora electrónica del contrato ligando a las tres partes (contratante, supervisión, contratista) con sus responsables autorizados a firmar</t>
-        </is>
-      </c>
-      <c r="C7" s="34" t="n"/>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>registrar por periodo las cantidades terminadas por cada concepto del catálogo, vinculando cada registro a su nota de bitácora del tipo Entrega</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="n"/>
       <c r="D7" s="26" t="n"/>
     </row>
     <row r="8" ht="27.9" customHeight="1" s="28">
@@ -1806,35 +1806,34 @@
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
-        <is>
-          <t>habilitar el registro formal de eventos del contrato conforme al art. 46 último párrafo y al art. 52 Bis LOPSRM (bitácora electrónica obligatoria), reglamentados por el art. 122 RLOPSRM</t>
-        </is>
-      </c>
-      <c r="C8" s="34" t="n"/>
+      <c r="B8" s="34" t="inlineStr">
+        <is>
+          <t>alimentar la integración de la estimación con el avance real y dejar respaldo documental de cada cantidad reportada</t>
+        </is>
+      </c>
+      <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
       <c r="C11" s="26" t="n"/>
-      <c r="D11" s="38" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
@@ -1846,9 +1845,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
-        <is>
-          <t>Existe una bitácora única por contrato con las tres partes ligadas y sus firmantes autorizados.</t>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>Cada cantidad capturada queda ligada al concepto del catálogo correspondiente y a una nota de bitácora del periodo.</t>
         </is>
       </c>
       <c r="C12" s="26" t="n"/>
@@ -1864,9 +1863,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="36" t="inlineStr">
-        <is>
-          <t>La fecha y hora de apertura queda registrada como evento formal inalterable.</t>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>El sistema bloquea el registro cuando la cantidad acumulada excede la contratada.</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
@@ -1876,9 +1875,8 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
@@ -1890,12 +1888,12 @@
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B16" s="35" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="C16" s="34" t="n"/>
+      <c r="B16" s="42" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C16" s="31" t="n"/>
       <c r="D16" s="26" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="28">
@@ -1904,10 +1902,10 @@
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" s="34" t="n"/>
+      <c r="B17" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1" s="28">
@@ -1916,12 +1914,12 @@
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="37" t="inlineStr">
-        <is>
-          <t>Sprint 1</t>
-        </is>
-      </c>
-      <c r="C18" s="34" t="n"/>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1" s="28">
@@ -1930,12 +1928,12 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C19" s="34" t="n"/>
+      <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
@@ -1970,6 +1968,249 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="16" customWidth="1" style="28" min="1" max="1"/>
+    <col width="50" customWidth="1" style="28" min="2" max="2"/>
+    <col width="25" customWidth="1" style="28" min="3" max="3"/>
+    <col width="18" customWidth="1" style="28" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>HU-07 · Configuración de alertas de atraso por concepto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" s="28">
+      <c r="A2" s="32" t="inlineStr">
+        <is>
+          <t>Servicio implementado: SRV-02-03</t>
+        </is>
+      </c>
+      <c r="C2" s="32" t="inlineStr">
+        <is>
+          <t>Módulo: MOD-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1" s="28">
+      <c r="A3" s="32" t="inlineStr">
+        <is>
+          <t>Sprint sugerido: 6</t>
+        </is>
+      </c>
+      <c r="C3" s="32" t="inlineStr">
+        <is>
+          <t>Estado: Backlog</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" s="28">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>HISTORIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="27.9" customHeight="1" s="28">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>residente</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="n"/>
+      <c r="D6" s="26" t="n"/>
+    </row>
+    <row r="7" ht="29.1" customHeight="1" s="28">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Deseo</t>
+        </is>
+      </c>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>configurar qué conceptos del contrato quiero vigilar, el umbral de atraso a partir del cual quiero ser notificado y el canal de notificación</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="n"/>
+      <c r="D7" s="26" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="28">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>A fin de</t>
+        </is>
+      </c>
+      <c r="B8" s="34" t="inlineStr">
+        <is>
+          <t>recibir alertas solo de lo que decidí vigilar, sin saturación de notificaciones</t>
+        </is>
+      </c>
+      <c r="C8" s="31" t="n"/>
+      <c r="D8" s="26" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" s="28">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>CRITERIOS DE ACEPTACIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>Criterios de aceptación</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="33" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32.1" customHeight="1" s="28">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>Se pueden crear, pausar y eliminar alertas por concepto sin alterar las del resto.</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>☐ Sí   ☐ No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32.1" customHeight="1" s="28">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>El sistema solo dispara alertas cuando el avance real es menor al umbral configurado por el usuario.</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>☐ Sí   ☐ No</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" s="28">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>METADATOS DE PLANEACIÓN (Scrum)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" s="28">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Complejidad</t>
+        </is>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="C16" s="31" t="n"/>
+      <c r="D16" s="26" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="28">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
+        </is>
+      </c>
+      <c r="B17" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="28">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>Sprint propuesto</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="28">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>En desarrollo</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="26" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B12:C12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
@@ -1980,31 +2221,31 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>HU-09 · Emisión y respuesta de notas tipificadas con firma</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-03-02</t>
         </is>
       </c>
-      <c r="C2" s="39" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>Módulo: MOD-03</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Sprint sugerido: 2</t>
         </is>
       </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
@@ -2012,7 +2253,7 @@
     </row>
     <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
@@ -2024,12 +2265,12 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>residente, supervisión o contratista (según rol autorizado)</t>
         </is>
       </c>
-      <c r="C6" s="34" t="n"/>
+      <c r="C6" s="31" t="n"/>
       <c r="D6" s="26" t="n"/>
     </row>
     <row r="7" ht="30.9" customHeight="1" s="28">
@@ -2038,12 +2279,12 @@
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
-        <is>
-          <t>emitir notas tipificadas según mi rol —el residente autoriza y aprueba, el superintendente solicita y avisa, y la supervisión registra el avance— conforme al art. 125 RLOPSRM, con folio automático y firma electrónica</t>
-        </is>
-      </c>
-      <c r="C7" s="34" t="n"/>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>emitir notas en la bitácora del contrato —el residente autoriza y aprueba, el superintendente solicita y avisa, y la supervisión registra el avance—, conforme a los arts. 122 y 125 RLOPSRM, con folio correlativo automático y firma conjunta de los tres participantes</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="n"/>
       <c r="D7" s="26" t="n"/>
     </row>
     <row r="8" ht="27.9" customHeight="1" s="28">
@@ -2052,49 +2293,47 @@
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>documentar formalmente los eventos del contrato de manera trazable e inmutable para auditoría</t>
         </is>
       </c>
-      <c r="C8" s="34" t="n"/>
+      <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
     <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
       <c r="C11" s="26" t="n"/>
-      <c r="D11" s="38" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
     <row r="12" ht="32.1" customHeight="1" s="28">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B12" s="36" t="inlineStr">
-        <is>
-          <t>Solo aparecen los tipos de nota que corresponden al rol del usuario.</t>
+      <c r="A12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>Aparecen los tipos de nota que corresponden al rol del usuario, pudiendo incorporar también otro tipo de nota para eventos no tipificados.</t>
         </is>
       </c>
       <c r="C12" s="26" t="n"/>
@@ -2105,14 +2344,12 @@
       </c>
     </row>
     <row r="13" ht="32.1" customHeight="1" s="28">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B13" s="36" t="inlineStr">
-        <is>
-          <t>Una nota firmada queda inmutable y solo puede corregirse emitiendo una nueva nota vinculada.</t>
+      <c r="A13" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>Una nota firmada queda inmutable; las correcciones se hacen generando una nota vinculada (formato «dice / debe decir»), sin alterar la original.</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
@@ -2123,14 +2360,12 @@
       </c>
     </row>
     <row r="14" ht="32.1" customHeight="1" s="28">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B14" s="36" t="inlineStr">
-        <is>
-          <t>Cada nota queda registrada con folio, fecha, firmante y vínculo opcional a nota previa.</t>
+      <c r="A14" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>Cada nota queda registrada con folio correlativo, fecha, firma de los tres participantes y vínculo opcional a nota previa.</t>
         </is>
       </c>
       <c r="C14" s="26" t="n"/>
@@ -2142,7 +2377,7 @@
     </row>
     <row r="15"/>
     <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
@@ -2159,7 +2394,7 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="C17" s="34" t="n"/>
+      <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1" s="28">
@@ -2171,7 +2406,7 @@
       <c r="B18" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="34" t="n"/>
+      <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1" s="28">
@@ -2180,12 +2415,12 @@
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="C19" s="34" t="n"/>
+      <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1" s="28">
@@ -2194,12 +2429,12 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="37" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C20" s="34" t="n"/>
+      <c r="C20" s="31" t="n"/>
       <c r="D20" s="26" t="n"/>
     </row>
   </sheetData>
@@ -2229,252 +2464,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="16" customWidth="1" style="28" min="1" max="1"/>
-    <col width="50" customWidth="1" style="28" min="2" max="2"/>
-    <col width="25" customWidth="1" style="28" min="3" max="3"/>
-    <col width="18" customWidth="1" style="28" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="30" t="inlineStr">
-        <is>
-          <t>HU-10 · Consulta y búsqueda de notas de bitácora</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="39" t="inlineStr">
-        <is>
-          <t>Servicio implementado: SRV-03-03</t>
-        </is>
-      </c>
-      <c r="C2" s="39" t="inlineStr">
-        <is>
-          <t>Módulo: MOD-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="39" t="inlineStr">
-        <is>
-          <t>Sprint sugerido: 3</t>
-        </is>
-      </c>
-      <c r="C3" s="39" t="inlineStr">
-        <is>
-          <t>Estado: Backlog</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
-    <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="32" t="inlineStr">
-        <is>
-          <t>HISTORIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="27.9" customHeight="1" s="28">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>Como</t>
-        </is>
-      </c>
-      <c r="B6" s="33" t="inlineStr">
-        <is>
-          <t>residente</t>
-        </is>
-      </c>
-      <c r="C6" s="34" t="n"/>
-      <c r="D6" s="26" t="n"/>
-    </row>
-    <row r="7" ht="27.9" customHeight="1" s="28">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Deseo</t>
-        </is>
-      </c>
-      <c r="B7" s="33" t="inlineStr">
-        <is>
-          <t>buscar notas de la bitácora del contrato por tipo, fecha, firmante, estatus o tema, y seleccionar varias para adjuntarlas a una estimación</t>
-        </is>
-      </c>
-      <c r="C7" s="34" t="n"/>
-      <c r="D7" s="26" t="n"/>
-    </row>
-    <row r="8" ht="27.9" customHeight="1" s="28">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>A fin de</t>
-        </is>
-      </c>
-      <c r="B8" s="33" t="inlineStr">
-        <is>
-          <t>encontrar rápido la nota que necesito y poder referenciarla en estimaciones o reportes</t>
-        </is>
-      </c>
-      <c r="C8" s="34" t="n"/>
-      <c r="D8" s="26" t="n"/>
-    </row>
-    <row r="9"/>
-    <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="32" t="inlineStr">
-        <is>
-          <t>CRITERIOS DE ACEPTACIÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="38" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B11" s="38" t="inlineStr">
-        <is>
-          <t>Criterios de aceptación</t>
-        </is>
-      </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="38" t="inlineStr">
-        <is>
-          <t>Resultado</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32.1" customHeight="1" s="28">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B12" s="36" t="inlineStr">
-        <is>
-          <t>La búsqueda devuelve resultados que cumplen todos los filtros aplicados simultáneamente.</t>
-        </is>
-      </c>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>☐ Sí   ☐ No</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32.1" customHeight="1" s="28">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B13" s="36" t="inlineStr">
-        <is>
-          <t>Se pueden seleccionar varias notas del resultado y exportarlas o adjuntarlas a una estimación.</t>
-        </is>
-      </c>
-      <c r="C13" s="26" t="n"/>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>☐ Sí   ☐ No</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="32" t="inlineStr">
-        <is>
-          <t>METADATOS DE PLANEACIÓN (Scrum)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Complejidad</t>
-        </is>
-      </c>
-      <c r="B16" s="35" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="C16" s="34" t="n"/>
-      <c r="D16" s="26" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" s="28">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
-        </is>
-      </c>
-      <c r="B17" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" s="34" t="n"/>
-      <c r="D17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="28">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>Sprint propuesto</t>
-        </is>
-      </c>
-      <c r="B18" s="37" t="inlineStr">
-        <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="C18" s="34" t="n"/>
-      <c r="D18" s="26" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="28">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="B19" s="37" t="inlineStr">
-        <is>
-          <t>En desarrollo</t>
-        </is>
-      </c>
-      <c r="C19" s="34" t="n"/>
-      <c r="D19" s="26" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B12:C12"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2491,39 +2480,38 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>HU-11 · Registro de minutas, agenda de visitas y consulta de acuerdos</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-03-04</t>
         </is>
       </c>
-      <c r="C2" s="39" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>Módulo: MOD-03</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Sprint sugerido: 7</t>
         </is>
       </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
@@ -2535,12 +2523,12 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="34" t="n"/>
+      <c r="C6" s="31" t="n"/>
       <c r="D6" s="26" t="n"/>
     </row>
     <row r="7" ht="27.9" customHeight="1" s="28">
@@ -2549,12 +2537,12 @@
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>subir minutas de reuniones del contrato con sus metadatos, agendar visitas e inspecciones de campo, y consultar los acuerdos asentados</t>
         </is>
       </c>
-      <c r="C7" s="34" t="n"/>
+      <c r="C7" s="31" t="n"/>
       <c r="D7" s="26" t="n"/>
     </row>
     <row r="8" ht="27.9" customHeight="1" s="28">
@@ -2563,35 +2551,34 @@
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>tener concentradas todas las reuniones, visitas y compromisos del contrato en un solo lugar para consulta</t>
         </is>
       </c>
-      <c r="C8" s="34" t="n"/>
+      <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
       <c r="C11" s="26" t="n"/>
-      <c r="D11" s="38" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
@@ -2603,7 +2590,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Las minutas y visitas registradas son visibles para los usuarios autorizados del contrato.</t>
         </is>
@@ -2621,7 +2608,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>Se pueden consultar los acuerdos y compromisos derivados, filtrados por contrato y periodo.</t>
         </is>
@@ -2633,9 +2620,8 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
@@ -2652,7 +2638,7 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C16" s="34" t="n"/>
+      <c r="C16" s="31" t="n"/>
       <c r="D16" s="26" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="28">
@@ -2664,7 +2650,7 @@
       <c r="B17" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="34" t="n"/>
+      <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1" s="28">
@@ -2673,12 +2659,12 @@
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>Sprint 7</t>
         </is>
       </c>
-      <c r="C18" s="34" t="n"/>
+      <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1" s="28">
@@ -2687,12 +2673,12 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C19" s="34" t="n"/>
+      <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
@@ -2737,31 +2723,31 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>HU-12 · Apertura del periodo e integración de la estimación</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-04-01</t>
         </is>
       </c>
-      <c r="C2" s="39" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>Módulo: MOD-04</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Sprint sugerido: 3</t>
         </is>
       </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
@@ -2769,7 +2755,7 @@
     </row>
     <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
@@ -2781,12 +2767,12 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>contratista</t>
         </is>
       </c>
-      <c r="C6" s="34" t="n"/>
+      <c r="C6" s="31" t="n"/>
       <c r="D6" s="26" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1" s="28">
@@ -2795,12 +2781,12 @@
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
-        <is>
-          <t>abrir el periodo de estimación e integrar como un solo bloque la carátula (con anticipos amortizados, retenciones y deductivas), números generadores, registro fotográfico, soportes y notas de bitácora del periodo</t>
-        </is>
-      </c>
-      <c r="C7" s="34" t="n"/>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>abrir el periodo de estimación e integrar como un solo bloque la carátula (con anticipo amortizado, retenciones del 5 al millar y deductivas), los números generadores, el registro fotográfico, los soportes y las notas de bitácora del periodo seleccionadas desde el buscador de bitácora</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="n"/>
       <c r="D7" s="26" t="n"/>
     </row>
     <row r="8" ht="27.9" customHeight="1" s="28">
@@ -2809,49 +2795,47 @@
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>presentar la estimación como un expediente completo conforme al art. 132 RLOPSRM para la revisión de supervisión y residencia</t>
         </is>
       </c>
-      <c r="C8" s="34" t="n"/>
+      <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
     <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
       <c r="C11" s="26" t="n"/>
-      <c r="D11" s="38" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
     <row r="12" ht="33" customHeight="1" s="28">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B12" s="36" t="inlineStr">
-        <is>
-          <t>La estimación se guarda como una sola entidad que contiene carátula, generadores, registro fotográfico, soportes y notas vinculadas.</t>
+      <c r="A12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>La estimación se guarda como una sola entidad que contiene carátula, generadores, registro fotográfico, soportes y notas vinculadas seleccionadas del buscador de bitácora.</t>
         </is>
       </c>
       <c r="C12" s="26" t="n"/>
@@ -2862,14 +2846,12 @@
       </c>
     </row>
     <row r="13" ht="35.1" customHeight="1" s="28">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B13" s="36" t="inlineStr">
-        <is>
-          <t>La carátula calcula automáticamente anticipo amortizado, retenciones legales (5 al millar) y deductivas por penalizaciones según el contrato.</t>
+      <c r="A13" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>La carátula calcula automáticamente anticipo amortizado, retenciones legales (5 al millar, art. 191 LFD) y deductivas por penalizaciones según el contrato.</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
@@ -2880,12 +2862,10 @@
       </c>
     </row>
     <row r="14" ht="32.1" customHeight="1" s="28">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B14" s="36" t="inlineStr">
+      <c r="A14" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>El sistema bloquea la integración cuando una cantidad por concepto excede la cantidad contratada en el catálogo (art. 118 RLOPSRM).</t>
         </is>
@@ -2899,7 +2879,7 @@
     </row>
     <row r="15"/>
     <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
@@ -2916,7 +2896,7 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="C17" s="34" t="n"/>
+      <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1" s="28">
@@ -2928,7 +2908,7 @@
       <c r="B18" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="34" t="n"/>
+      <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1" s="28">
@@ -2937,12 +2917,12 @@
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="C19" s="34" t="n"/>
+      <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1" s="28">
@@ -2951,12 +2931,12 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="37" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C20" s="34" t="n"/>
+      <c r="C20" s="31" t="n"/>
       <c r="D20" s="26" t="n"/>
     </row>
   </sheetData>
@@ -3002,39 +2982,38 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>HU-13 · Envío de la estimación</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-04-02</t>
         </is>
       </c>
-      <c r="C2" s="39" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>Módulo: MOD-04</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Sprint sugerido: 8</t>
         </is>
       </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
@@ -3046,12 +3025,12 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>contratista</t>
         </is>
       </c>
-      <c r="C6" s="34" t="n"/>
+      <c r="C6" s="31" t="n"/>
       <c r="D6" s="26" t="n"/>
     </row>
     <row r="7" ht="27.9" customHeight="1" s="28">
@@ -3060,12 +3039,12 @@
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>enviar formalmente una estimación integrada para que arranque el plazo de revisión del art. 54 LOPSRM</t>
         </is>
       </c>
-      <c r="C7" s="34" t="n"/>
+      <c r="C7" s="31" t="n"/>
       <c r="D7" s="26" t="n"/>
     </row>
     <row r="8" ht="27.9" customHeight="1" s="28">
@@ -3074,35 +3053,34 @@
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>dejar evidencia del momento exacto de entrega y disparar el plazo de revisión de la supervisión y residencia</t>
         </is>
       </c>
-      <c r="C8" s="34" t="n"/>
+      <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
       <c r="C11" s="26" t="n"/>
-      <c r="D11" s="38" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
@@ -3114,7 +3092,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Al enviar la estimación queda registrada la fecha y hora exacta, y se notifica a residencia y supervisión.</t>
         </is>
@@ -3132,7 +3110,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>El botón Enviar se deshabilita cuando se vencen los 6 días naturales del periodo de presentación (art. 54 LOPSRM).</t>
         </is>
@@ -3144,9 +3122,8 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
@@ -3163,7 +3140,7 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C16" s="34" t="n"/>
+      <c r="C16" s="31" t="n"/>
       <c r="D16" s="26" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="28">
@@ -3175,7 +3152,7 @@
       <c r="B17" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="34" t="n"/>
+      <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1" s="28">
@@ -3184,12 +3161,12 @@
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>Sprint 8</t>
         </is>
       </c>
-      <c r="C18" s="34" t="n"/>
+      <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1" s="28">
@@ -3198,12 +3175,12 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C19" s="34" t="n"/>
+      <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
@@ -3248,39 +3225,38 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>HU-14 · Historial de estimaciones del contrato</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-04-03</t>
         </is>
       </c>
-      <c r="C2" s="39" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>Módulo: MOD-04</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Sprint sugerido: 5</t>
         </is>
       </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
@@ -3292,12 +3268,12 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="34" t="n"/>
+      <c r="C6" s="31" t="n"/>
       <c r="D6" s="26" t="n"/>
     </row>
     <row r="7" ht="29.1" customHeight="1" s="28">
@@ -3306,12 +3282,12 @@
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>consultar todas las estimaciones del contrato a lo largo del tiempo con sus estados (aceptadas, rechazadas, en proceso) y filtros por periodo</t>
         </is>
       </c>
-      <c r="C7" s="34" t="n"/>
+      <c r="C7" s="31" t="n"/>
       <c r="D7" s="26" t="n"/>
     </row>
     <row r="8" ht="27.9" customHeight="1" s="28">
@@ -3320,35 +3296,34 @@
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>ver la trazabilidad completa del ciclo de cobro del contrato, incluyendo versiones rechazadas, conforme a los tipos de estimación reconocidos en el art. 130 RLOPSRM</t>
         </is>
       </c>
-      <c r="C8" s="34" t="n"/>
+      <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
       <c r="C11" s="26" t="n"/>
-      <c r="D11" s="38" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
@@ -3360,7 +3335,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>El historial muestra todas las estimaciones del contrato, incluyendo las versiones rechazadas.</t>
         </is>
@@ -3378,7 +3353,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>Por cada periodo solo puede haber una estimación aceptada; las versiones previas quedan marcadas como rechazadas.</t>
         </is>
@@ -3390,9 +3365,8 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
@@ -3409,7 +3383,7 @@
           <t>Baja</t>
         </is>
       </c>
-      <c r="C16" s="34" t="n"/>
+      <c r="C16" s="31" t="n"/>
       <c r="D16" s="26" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="28">
@@ -3421,7 +3395,7 @@
       <c r="B17" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="34" t="n"/>
+      <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1" s="28">
@@ -3430,12 +3404,12 @@
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="C18" s="34" t="n"/>
+      <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1" s="28">
@@ -3444,12 +3418,12 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C19" s="34" t="n"/>
+      <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
@@ -3494,39 +3468,38 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>HU-15 · Recepción, revisión técnica y autorización de la estimación</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-05-01</t>
         </is>
       </c>
-      <c r="C2" s="39" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>Módulo: MOD-05</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Sprint sugerido: 4</t>
         </is>
       </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
@@ -3538,12 +3511,12 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>supervisión y residencia (revisión secuencial)</t>
         </is>
       </c>
-      <c r="C6" s="34" t="n"/>
+      <c r="C6" s="31" t="n"/>
       <c r="D6" s="26" t="n"/>
     </row>
     <row r="7" ht="36.9" customHeight="1" s="28">
@@ -3552,12 +3525,12 @@
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>revisar la estimación recibida sección por sección (carátula, números generadores, registro fotográfico, soportes, notas), registrar observaciones puntuales, turnar de supervisión a residencia y al final autorizar o rechazar</t>
         </is>
       </c>
-      <c r="C7" s="34" t="n"/>
+      <c r="C7" s="31" t="n"/>
       <c r="D7" s="26" t="n"/>
     </row>
     <row r="8" ht="27.9" customHeight="1" s="28">
@@ -3566,35 +3539,34 @@
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>decidir sobre la estimación con evidencia completa, en ejercicio de la responsabilidad de la residencia sobre la revisión y aprobación (art. 53 LOPSRM), y dentro de los plazos de los arts. 54 LOPSRM y 133 RLOPSRM</t>
         </is>
       </c>
-      <c r="C8" s="34" t="n"/>
+      <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
       <c r="C11" s="26" t="n"/>
-      <c r="D11" s="38" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
@@ -3606,7 +3578,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>La revisión permite revisar sección por sección y dejar observaciones puntuales en cada una (carátula, generadores, registro fotográfico, soportes y notas).</t>
         </is>
@@ -3624,7 +3596,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>La autorización queda condicionada al turnado secuencial: primero supervisión, luego residencia; residencia no puede resolver antes del turnado.</t>
         </is>
@@ -3642,7 +3614,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B14" s="36" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>El sistema controla el plazo de 15 días naturales de revisión conforme al art. 54 LOPSRM mediante un semáforo visible para los actores.</t>
         </is>
@@ -3654,9 +3626,8 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
@@ -3673,7 +3644,7 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="C17" s="34" t="n"/>
+      <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1" s="28">
@@ -3685,7 +3656,7 @@
       <c r="B18" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="34" t="n"/>
+      <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1" s="28">
@@ -3694,12 +3665,12 @@
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="C19" s="34" t="n"/>
+      <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1" s="28">
@@ -3708,12 +3679,12 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="37" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C20" s="34" t="n"/>
+      <c r="C20" s="31" t="n"/>
       <c r="D20" s="26" t="n"/>
     </row>
   </sheetData>
@@ -3759,39 +3730,38 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>HU-16 · Reingreso de estimación tras rechazo</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-05-02</t>
         </is>
       </c>
-      <c r="C2" s="39" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>Módulo: MOD-05</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Sprint sugerido: 8</t>
         </is>
       </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
@@ -3803,12 +3773,12 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>contratista</t>
         </is>
       </c>
-      <c r="C6" s="34" t="n"/>
+      <c r="C6" s="31" t="n"/>
       <c r="D6" s="26" t="n"/>
     </row>
     <row r="7" ht="27.9" customHeight="1" s="28">
@@ -3817,12 +3787,12 @@
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>presentar una nueva versión completa de la estimación del mismo periodo después de un rechazo, atendiendo las observaciones recibidas</t>
         </is>
       </c>
-      <c r="C7" s="34" t="n"/>
+      <c r="C7" s="31" t="n"/>
       <c r="D7" s="26" t="n"/>
     </row>
     <row r="8" ht="27.9" customHeight="1" s="28">
@@ -3831,35 +3801,34 @@
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>que la estimación sea revisada nuevamente como un bloque completo sin perder trazabilidad de la versión anterior</t>
         </is>
       </c>
-      <c r="C8" s="34" t="n"/>
+      <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
       <c r="C11" s="26" t="n"/>
-      <c r="D11" s="38" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
@@ -3871,7 +3840,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>La nueva versión se trata como bloque completo independiente y la versión rechazada queda como histórico vinculado.</t>
         </is>
@@ -3889,7 +3858,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>El listado de observaciones de la versión rechazada está disponible para descarga en PDF o Excel.</t>
         </is>
@@ -3901,9 +3870,8 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
@@ -3920,7 +3888,7 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C16" s="34" t="n"/>
+      <c r="C16" s="31" t="n"/>
       <c r="D16" s="26" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="28">
@@ -3932,7 +3900,7 @@
       <c r="B17" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="34" t="n"/>
+      <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1" s="28">
@@ -3941,12 +3909,12 @@
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>Sprint 8</t>
         </is>
       </c>
-      <c r="C18" s="34" t="n"/>
+      <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1" s="28">
@@ -3955,12 +3923,12 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C19" s="34" t="n"/>
+      <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
@@ -4005,39 +3973,38 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>HU-17 · Tablero de estimaciones aceptadas y en proceso</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-06-01</t>
         </is>
       </c>
-      <c r="C2" s="39" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>Módulo: MOD-06</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Sprint sugerido: 8</t>
         </is>
       </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
@@ -4049,12 +4016,12 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="34" t="n"/>
+      <c r="C6" s="31" t="n"/>
       <c r="D6" s="26" t="n"/>
     </row>
     <row r="7" ht="35.1" customHeight="1" s="28">
@@ -4063,12 +4030,12 @@
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>ver en un tablero las estimaciones del contrato que están aceptadas y las que están en proceso (presentada, en revisión, autorizada, en pago, pagada), con su línea de tiempo y pendientes por solventar</t>
         </is>
       </c>
-      <c r="C7" s="34" t="n"/>
+      <c r="C7" s="31" t="n"/>
       <c r="D7" s="26" t="n"/>
     </row>
     <row r="8" ht="27.9" customHeight="1" s="28">
@@ -4077,35 +4044,34 @@
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>saber qué estimación está en qué estado y qué requiere mi acción inmediata</t>
         </is>
       </c>
-      <c r="C8" s="34" t="n"/>
+      <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
       <c r="C11" s="26" t="n"/>
-      <c r="D11" s="38" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
@@ -4117,7 +4083,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>El tablero muestra solo estimaciones aceptadas y en proceso (no las rechazadas, que viven en el historial).</t>
         </is>
@@ -4135,7 +4101,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>El panel "Mis pendientes" filtra los pendientes según el rol del usuario autenticado.</t>
         </is>
@@ -4147,9 +4113,8 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
@@ -4166,7 +4131,7 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C16" s="34" t="n"/>
+      <c r="C16" s="31" t="n"/>
       <c r="D16" s="26" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="28">
@@ -4178,7 +4143,7 @@
       <c r="B17" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="34" t="n"/>
+      <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1" s="28">
@@ -4187,12 +4152,12 @@
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>Sprint 8</t>
         </is>
       </c>
-      <c r="C18" s="34" t="n"/>
+      <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1" s="28">
@@ -4201,12 +4166,12 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C19" s="34" t="n"/>
+      <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
@@ -4251,39 +4216,38 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>HU-00 · Inicio de sesión por rol</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>Servicio implementado: —</t>
         </is>
       </c>
-      <c r="C2" s="39" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>Módulo: —</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Sprint sugerido: 1</t>
         </is>
       </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
@@ -4295,12 +4259,12 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>usuario del sistema (residente, contratista, supervisión, dependencia o finanzas)</t>
         </is>
       </c>
-      <c r="C6" s="34" t="n"/>
+      <c r="C6" s="31" t="n"/>
       <c r="D6" s="26" t="n"/>
     </row>
     <row r="7" ht="69" customHeight="1" s="28">
@@ -4309,12 +4273,12 @@
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>autenticarme con mi usuario y contraseña, sin tener que indicar mi rol explícitamente, para que el sistema reconozca internamente quién soy y me muestre únicamente las funciones que me corresponden</t>
         </is>
       </c>
-      <c r="C7" s="34" t="n"/>
+      <c r="C7" s="31" t="n"/>
       <c r="D7" s="26" t="n"/>
     </row>
     <row r="8" ht="27.9" customHeight="1" s="28">
@@ -4323,35 +4287,34 @@
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>proteger la información del contrato y que cada acción registrada quede asociada al usuario que la ejecuta</t>
         </is>
       </c>
-      <c r="C8" s="34" t="n"/>
+      <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
       <c r="C11" s="26" t="n"/>
-      <c r="D11" s="38" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
@@ -4363,7 +4326,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>El sistema valida usuario y contraseña, bloquea el acceso cuando son inválidos y no permite continuar si los campos usuario o contraseña están vacíos.</t>
         </is>
@@ -4381,7 +4344,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>El sistema deduce el rol del usuario a partir de su identificador, sin que este lo seleccione, y muestra únicamente las pantallas y opciones que corresponden a ese rol.</t>
         </is>
@@ -4399,7 +4362,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B14" s="36" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>Cada acción registrada por el usuario queda asociada a su nombre y fecha/hora en el sistema.</t>
         </is>
@@ -4413,10 +4376,10 @@
     </row>
     <row r="15">
       <c r="A15" s="13" t="n"/>
-      <c r="B15" s="36" t="n"/>
+      <c r="B15" s="25" t="n"/>
     </row>
     <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
@@ -4433,7 +4396,7 @@
           <t>Baja</t>
         </is>
       </c>
-      <c r="C17" s="34" t="n"/>
+      <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1" s="28">
@@ -4445,7 +4408,7 @@
       <c r="B18" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="34" t="n"/>
+      <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1" s="28">
@@ -4454,12 +4417,12 @@
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="C19" s="34" t="n"/>
+      <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1" s="28">
@@ -4468,12 +4431,12 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="37" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>Terminado</t>
         </is>
       </c>
-      <c r="C20" s="34" t="n"/>
+      <c r="C20" s="31" t="n"/>
       <c r="D20" s="26" t="n"/>
     </row>
   </sheetData>
@@ -4519,39 +4482,38 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>HU-18 · Vista ejecutiva del portafolio con semáforos</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-06-02</t>
         </is>
       </c>
-      <c r="C2" s="39" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>Módulo: MOD-06</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Sprint sugerido: 9</t>
         </is>
       </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
@@ -4563,12 +4525,12 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>dependencia</t>
         </is>
       </c>
-      <c r="C6" s="34" t="n"/>
+      <c r="C6" s="31" t="n"/>
       <c r="D6" s="26" t="n"/>
     </row>
     <row r="7" ht="32.1" customHeight="1" s="28">
@@ -4577,12 +4539,12 @@
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>ver mis contratos asignados como una lista con semáforo de tres colores (verde, ámbar, rojo) según avance físico, atrasos y pendientes, con drill-down al detalle del contrato</t>
         </is>
       </c>
-      <c r="C7" s="34" t="n"/>
+      <c r="C7" s="31" t="n"/>
       <c r="D7" s="26" t="n"/>
     </row>
     <row r="8" ht="27.9" customHeight="1" s="28">
@@ -4591,35 +4553,34 @@
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>tomar decisiones ejecutivas sobre cuáles contratos requieren mi atención</t>
         </is>
       </c>
-      <c r="C8" s="34" t="n"/>
+      <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
       <c r="C11" s="26" t="n"/>
-      <c r="D11" s="38" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
@@ -4631,7 +4592,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Cada contrato del portafolio muestra un semáforo de color calculado a partir de avance físico, atrasos y pendientes.</t>
         </is>
@@ -4649,7 +4610,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>Al hacer doble clic sobre un contrato se abre su detalle con indicadores físicos, financieros y penalizaciones.</t>
         </is>
@@ -4661,9 +4622,8 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
@@ -4680,7 +4640,7 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C16" s="34" t="n"/>
+      <c r="C16" s="31" t="n"/>
       <c r="D16" s="26" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="28">
@@ -4692,7 +4652,7 @@
       <c r="B17" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="C17" s="34" t="n"/>
+      <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1" s="28">
@@ -4701,12 +4661,12 @@
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>Sprint 9</t>
         </is>
       </c>
-      <c r="C18" s="34" t="n"/>
+      <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1" s="28">
@@ -4715,12 +4675,12 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C19" s="34" t="n"/>
+      <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
@@ -4765,39 +4725,38 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>HU-19 · Exportación de los 7 reportes definidos del contrato</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-06-03</t>
         </is>
       </c>
-      <c r="C2" s="39" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>Módulo: MOD-06</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Sprint sugerido: 9</t>
         </is>
       </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
@@ -4809,12 +4768,12 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="34" t="n"/>
+      <c r="C6" s="31" t="n"/>
       <c r="D6" s="26" t="n"/>
     </row>
     <row r="7" ht="35.1" customHeight="1" s="28">
@@ -4823,12 +4782,12 @@
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>descargar cualquiera de los 7 reportes definidos del contrato (avance físico, financiero, estimaciones, observaciones, bitácora, modificatorios, penalizaciones) en formato PDF o Excel según el reporte</t>
         </is>
       </c>
-      <c r="C7" s="34" t="n"/>
+      <c r="C7" s="31" t="n"/>
       <c r="D7" s="26" t="n"/>
     </row>
     <row r="8" ht="27.9" customHeight="1" s="28">
@@ -4837,35 +4796,34 @@
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>llevar la información del sistema a oficios, presentaciones o expedientes de auditoría</t>
         </is>
       </c>
-      <c r="C8" s="34" t="n"/>
+      <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
       <c r="C11" s="26" t="n"/>
-      <c r="D11" s="38" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
@@ -4877,7 +4835,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Cada uno de los 7 reportes definidos genera el archivo en el formato establecido (PDF, Excel o ambos).</t>
         </is>
@@ -4895,7 +4853,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>El usuario puede seleccionar el periodo (mensual, trimestral, acumulado) sin alterar el contenido predefinido del reporte.</t>
         </is>
@@ -4907,9 +4865,8 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
@@ -4926,7 +4883,7 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C16" s="34" t="n"/>
+      <c r="C16" s="31" t="n"/>
       <c r="D16" s="26" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="28">
@@ -4938,7 +4895,7 @@
       <c r="B17" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="C17" s="34" t="n"/>
+      <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1" s="28">
@@ -4947,12 +4904,12 @@
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>Sprint 9</t>
         </is>
       </c>
-      <c r="C18" s="34" t="n"/>
+      <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1" s="28">
@@ -4961,12 +4918,12 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C19" s="34" t="n"/>
+      <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
@@ -5011,39 +4968,38 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>HU-20 · Tránsito a pago: carga de soportes y verificación de suficiencia presupuestal</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-07-01</t>
         </is>
       </c>
-      <c r="C2" s="39" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>Módulo: MOD-07</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Sprint sugerido: 5</t>
         </is>
       </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
@@ -5055,12 +5011,12 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>contratista y finanzas</t>
         </is>
       </c>
-      <c r="C6" s="34" t="n"/>
+      <c r="C6" s="31" t="n"/>
       <c r="D6" s="26" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1" s="28">
@@ -5069,12 +5025,12 @@
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>que al autorizarse una estimación el sistema verifique la suficiencia presupuestal (art. 24 LOPSRM), genere la instrucción de pago, permita cargar los soportes (factura, CFDI y fianza de cumplimiento cuando el contrato lo exija) y notifique a Finanzas con el plazo de 20 días naturales del art. 54 LOPSRM</t>
         </is>
       </c>
-      <c r="C7" s="34" t="n"/>
+      <c r="C7" s="31" t="n"/>
       <c r="D7" s="26" t="n"/>
     </row>
     <row r="8" ht="27.9" customHeight="1" s="28">
@@ -5083,35 +5039,34 @@
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>no perder el plazo de pago y dejar evidencia de la suficiencia presupuestal verificada, considerando que el incumplimiento del plazo de pago genera gastos financieros a cargo de la dependencia (art. 55 LOPSRM)</t>
         </is>
       </c>
-      <c r="C8" s="34" t="n"/>
+      <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
       <c r="C11" s="26" t="n"/>
-      <c r="D11" s="38" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
@@ -5123,7 +5078,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>El sistema verifica suficiencia presupuestal contra el techo anual y bloquea la generación de la instrucción de pago si el monto excede lo disponible (art. 24 LOPSRM).</t>
         </is>
@@ -5141,7 +5096,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>Un semáforo muestra el avance del plazo de 20 días naturales para pago (art. 54 LOPSRM) y emite alertas al entrar en amarillo.</t>
         </is>
@@ -5159,7 +5114,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B14" s="36" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>La instrucción de pago solo puede generarse cuando todos los soportes obligatorios (factura, CFDI, estado de fianza) están cargados.</t>
         </is>
@@ -5171,9 +5126,8 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
@@ -5190,7 +5144,7 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="C17" s="34" t="n"/>
+      <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1" s="28">
@@ -5202,7 +5156,7 @@
       <c r="B18" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="34" t="n"/>
+      <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1" s="28">
@@ -5211,12 +5165,12 @@
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="C19" s="34" t="n"/>
+      <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1" s="28">
@@ -5225,12 +5179,12 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="37" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C20" s="34" t="n"/>
+      <c r="C20" s="31" t="n"/>
       <c r="D20" s="26" t="n"/>
     </row>
   </sheetData>
@@ -5276,39 +5230,38 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>HU-21 · Registro del pago efectuado</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-07-02</t>
         </is>
       </c>
-      <c r="C2" s="39" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>Módulo: MOD-07</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Sprint sugerido: 2</t>
         </is>
       </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
@@ -5320,12 +5273,12 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>finanzas</t>
         </is>
       </c>
-      <c r="C6" s="34" t="n"/>
+      <c r="C6" s="31" t="n"/>
       <c r="D6" s="26" t="n"/>
     </row>
     <row r="7" ht="27.9" customHeight="1" s="28">
@@ -5334,12 +5287,12 @@
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>registrar en el sistema el pago realizado de una estimación: fecha, importe, referencia bancaria y observaciones</t>
         </is>
       </c>
-      <c r="C7" s="34" t="n"/>
+      <c r="C7" s="31" t="n"/>
       <c r="D7" s="26" t="n"/>
     </row>
     <row r="8" ht="27.9" customHeight="1" s="28">
@@ -5348,35 +5301,34 @@
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>cerrar el ciclo de la estimación y actualizar el avance financiero del contrato</t>
         </is>
       </c>
-      <c r="C8" s="34" t="n"/>
+      <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
       <c r="C11" s="26" t="n"/>
-      <c r="D11" s="38" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
@@ -5388,7 +5340,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>El registro del pago marca la estimación como pagada y actualiza el avance financiero del contrato.</t>
         </is>
@@ -5406,9 +5358,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="36" t="inlineStr">
-        <is>
-          <t>Quedan capturados fecha, importe, referencia bancaria y usuario que realizó el registro.</t>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>se encuentran todos o se encuentran los siguientes datos: fecha, importe, referencia bancaria y usuario que realizó el registro.</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
@@ -5418,9 +5370,8 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
@@ -5437,7 +5388,7 @@
           <t>Baja</t>
         </is>
       </c>
-      <c r="C16" s="34" t="n"/>
+      <c r="C16" s="31" t="n"/>
       <c r="D16" s="26" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="28">
@@ -5449,7 +5400,7 @@
       <c r="B17" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="34" t="n"/>
+      <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1" s="28">
@@ -5458,12 +5409,12 @@
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="C18" s="34" t="n"/>
+      <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1" s="28">
@@ -5472,12 +5423,12 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C19" s="34" t="n"/>
+      <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
@@ -5524,14 +5475,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="23.25" customHeight="1" s="28">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>Plan de iteraciones (Sprints)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="50.1" customHeight="1" s="28">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="37" t="inlineStr">
         <is>
           <t>Distribución de las 22 historias en 9 sprints. Velocidad objetivo: 9 puntos por sprint (3 integrantes × 3 días útiles × 1 punto por día-persona). Las historias complejas (8 user points): HU-09 emisión de notas, HU-12 integración de estimación, HU-15 revisión de estimación y HU-20 tránsito a pago, todas ubicadas en sprints 2-5 para mitigar el riesgo de retraso. Ningún sprint excede 10 puntos. Promedio: 9.4 pts/sprint.</t>
         </is>
@@ -5570,12 +5521,12 @@
       </c>
     </row>
     <row r="5" ht="66" customHeight="1" s="28">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>• HU-00 Inicio de sesión por rol (1)
 • HU-01 Alta de contratos (5)
@@ -5602,12 +5553,12 @@
       </c>
     </row>
     <row r="6" ht="60" customHeight="1" s="28">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>• HU-09 Emisión y respuesta de notas tipificadas con firma (8)
 • HU-21 Registro del pago efectuado (2)</t>
@@ -5633,12 +5584,12 @@
       </c>
     </row>
     <row r="7" ht="60" customHeight="1" s="28">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>• HU-10 Consulta y búsqueda de notas de bitácora (2)
 • HU-12 Apertura del periodo e integración de la estimación (8)</t>
@@ -5664,12 +5615,12 @@
       </c>
     </row>
     <row r="8" ht="60" customHeight="1" s="28">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>• HU-04 Consulta integrada del expediente contractual (2)
 • HU-15 Recepción, revisión técnica y autorización de la estimación (8)</t>
@@ -5695,12 +5646,12 @@
       </c>
     </row>
     <row r="9" ht="60" customHeight="1" s="28">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="B9" s="33" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>• HU-14 Historial de estimaciones del contrato (2)
 • HU-20 Tránsito a pago: carga de soportes y verificación de suficiencia presupuestal (8)</t>
@@ -5726,12 +5677,12 @@
       </c>
     </row>
     <row r="10" ht="66" customHeight="1" s="28">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>Sprint 6</t>
         </is>
       </c>
-      <c r="B10" s="33" t="inlineStr">
+      <c r="B10" s="34" t="inlineStr">
         <is>
           <t>• HU-02 Registro de fianzas y garantías (2)
 • HU-03 Trámite y aplicación de convenios modificatorios (5)
@@ -5758,12 +5709,12 @@
       </c>
     </row>
     <row r="11" ht="66" customHeight="1" s="28">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>Sprint 7</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>• HU-05 Visualización del programa y curva de avance (3)
 • HU-06 Registro de trabajos terminados por periodo (3)
@@ -5790,12 +5741,12 @@
       </c>
     </row>
     <row r="12" ht="66" customHeight="1" s="28">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>Sprint 8</t>
         </is>
       </c>
-      <c r="B12" s="33" t="inlineStr">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>• HU-13 Envío de la estimación (3)
 • HU-16 Reingreso de estimación tras rechazo (3)
@@ -5822,12 +5773,12 @@
       </c>
     </row>
     <row r="13" ht="60" customHeight="1" s="28">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>Sprint 9</t>
         </is>
       </c>
-      <c r="B13" s="33" t="inlineStr">
+      <c r="B13" s="34" t="inlineStr">
         <is>
           <t>• HU-18 Vista ejecutiva del portafolio con semáforos (5)
 • HU-19 Exportación de los 7 reportes definidos del contrato (5)</t>
@@ -5881,6 +5832,19 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -5900,31 +5864,31 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>HU-01 · Alta de contratos</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-01-01</t>
         </is>
       </c>
-      <c r="C2" s="39" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>Módulo: MOD-01</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Sprint sugerido: 1</t>
         </is>
       </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
@@ -5932,7 +5896,7 @@
     </row>
     <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
@@ -5944,12 +5908,12 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="34" t="n"/>
+      <c r="C6" s="31" t="n"/>
       <c r="D6" s="26" t="n"/>
     </row>
     <row r="7" ht="98.40000000000001" customHeight="1" s="28">
@@ -5958,12 +5922,12 @@
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
-        <is>
-          <t>dar de alta un contrato nuevo capturando en un solo flujo todos sus elementos: datos generales (folio, partes, monto, plazos, modalidad de pago), catálogo de conceptos, programa de obra mes a mes, elementos jurídicos del contrato, garantías (pólizas de anticipo, cumplimiento y vicios ocultos), penalizaciones aplicables (incluida la retención del 5 al millar conforme al art. 191 de la Ley Federal de Derechos), plan de amortización del anticipo otorgado, y el PDF firmado del contrato como respaldo documental</t>
-        </is>
-      </c>
-      <c r="C7" s="34" t="n"/>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>dar de alta un contrato nuevo capturando en un solo flujo: datos generales (folio, partes, monto, plazos, modalidad de pago), catálogo de conceptos (clave, descripción, unidad, precio, cantidad), programa de obra mes a mes, elementos jurídicos separados por dependencia y contratista, garantías (anticipo, cumplimiento y vicios ocultos), plan de amortización del anticipo, penalizaciones aplicables (incluida la retención del 5 al millar, art. 191 LFD) y el PDF firmado del contrato como respaldo</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="n"/>
       <c r="D7" s="26" t="n"/>
     </row>
     <row r="8" ht="27.9" customHeight="1" s="28">
@@ -5972,49 +5936,47 @@
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>tener el soporte documental del contrato en línea, disponible para los actores autorizados</t>
         </is>
       </c>
-      <c r="C8" s="34" t="n"/>
+      <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
     <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
       <c r="C11" s="26" t="n"/>
-      <c r="D11" s="38" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
     <row r="12" ht="61.2" customHeight="1" s="28">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B12" s="36" t="inlineStr">
-        <is>
-          <t>Existe un contrato con folio único que contiene catálogo de conceptos, programa de obra, elementos jurídicos, garantías, penalizaciones, plan de amortización del anticipo y PDF firmado.</t>
+      <c r="A12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>Existe un contrato con folio único que contiene, en una sola entidad, los siguientes bloques: datos generales, catálogo de conceptos, programa de obra, elementos jurídicos (dependencia y contratista por separado), garantías (anticipo, cumplimiento, vicios ocultos), plan de amortización, penalizaciones y PDF firmado.</t>
         </is>
       </c>
       <c r="C12" s="26" t="n"/>
@@ -6025,14 +5987,12 @@
       </c>
     </row>
     <row r="13" ht="32.1" customHeight="1" s="28">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B13" s="36" t="inlineStr">
-        <is>
-          <t>El sistema valida que los campos obligatorios estén llenos y el folio sea único antes de guardar.</t>
+      <c r="A13" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>El sistema no permite guardar el contrato hasta que todos los campos obligatorios estén llenos y el folio sea único.</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
@@ -6043,14 +6003,12 @@
       </c>
     </row>
     <row r="14" ht="32.1" customHeight="1" s="28">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B14" s="36" t="inlineStr">
-        <is>
-          <t>Existe un PDF firmado del contrato ligado al expediente, consultable por todos los actores autorizados.</t>
+      <c r="A14" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>El sistema contempla el PDF firmado como parte del expediente del contrato, ligado cuando se cargue, consultable por los actores autorizados.</t>
         </is>
       </c>
       <c r="C14" s="26" t="n"/>
@@ -6062,7 +6020,7 @@
     </row>
     <row r="15"/>
     <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
@@ -6079,7 +6037,7 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="C17" s="34" t="n"/>
+      <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1" s="28">
@@ -6091,7 +6049,7 @@
       <c r="B18" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="C18" s="34" t="n"/>
+      <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1" s="28">
@@ -6100,12 +6058,12 @@
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="C19" s="34" t="n"/>
+      <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1" s="28">
@@ -6114,12 +6072,12 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="37" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>Terminado</t>
         </is>
       </c>
-      <c r="C20" s="34" t="n"/>
+      <c r="C20" s="31" t="n"/>
       <c r="D20" s="26" t="n"/>
     </row>
   </sheetData>
@@ -6165,39 +6123,38 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>HU-02 · Registro de fianzas y garantías</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-01-02</t>
         </is>
       </c>
-      <c r="C2" s="39" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>Módulo: MOD-01</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Sprint sugerido: 6</t>
         </is>
       </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
@@ -6209,12 +6166,12 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>dependencia</t>
         </is>
       </c>
-      <c r="C6" s="34" t="n"/>
+      <c r="C6" s="31" t="n"/>
       <c r="D6" s="26" t="n"/>
     </row>
     <row r="7" ht="29.1" customHeight="1" s="28">
@@ -6223,12 +6180,12 @@
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>subir las pólizas de fianza del contrato (cumplimiento, vicios ocultos, anticipo) con sus metadatos: vigencia, afianzadora y monto afianzado</t>
         </is>
       </c>
-      <c r="C7" s="34" t="n"/>
+      <c r="C7" s="31" t="n"/>
       <c r="D7" s="26" t="n"/>
     </row>
     <row r="8" ht="27.9" customHeight="1" s="28">
@@ -6237,35 +6194,34 @@
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>contar con el respaldo documental de las garantías del contrato y ser notificado cuando una póliza esté por vencer</t>
         </is>
       </c>
-      <c r="C8" s="34" t="n"/>
+      <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
       <c r="C11" s="26" t="n"/>
-      <c r="D11" s="38" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
@@ -6277,7 +6233,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>La póliza queda ligada al contrato con afianzadora, vigencia y monto registrados.</t>
         </is>
@@ -6295,7 +6251,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>El sistema emite alerta cuando faltan N días configurables para el vencimiento.</t>
         </is>
@@ -6311,7 +6267,7 @@
       <c r="A14" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="36" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>La póliza registrada puede consultarse en formato PDF desde el listado de fianzas del contrato.</t>
         </is>
@@ -6323,7 +6279,7 @@
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
@@ -6340,7 +6296,7 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C16" s="34" t="n"/>
+      <c r="C16" s="31" t="n"/>
       <c r="D16" s="26" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="28">
@@ -6352,7 +6308,7 @@
       <c r="B17" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="34" t="n"/>
+      <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1" s="28">
@@ -6361,12 +6317,12 @@
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>Sprint 6</t>
         </is>
       </c>
-      <c r="C18" s="34" t="n"/>
+      <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1" s="28">
@@ -6375,12 +6331,12 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C19" s="34" t="n"/>
+      <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
@@ -6425,39 +6381,38 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>HU-03 · Trámite y aplicación de convenios modificatorios</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-01-03</t>
         </is>
       </c>
-      <c r="C2" s="39" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>Módulo: MOD-01</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Sprint sugerido: 6</t>
         </is>
       </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
@@ -6469,12 +6424,12 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>dependencia</t>
         </is>
       </c>
-      <c r="C6" s="34" t="n"/>
+      <c r="C6" s="31" t="n"/>
       <c r="D6" s="26" t="n"/>
     </row>
     <row r="7" ht="33" customHeight="1" s="28">
@@ -6483,12 +6438,12 @@
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>registrar un convenio modificatorio del contrato (cambios al monto, plazo o conceptos) y aplicar las actualizaciones al catálogo, programa y fianzas, manteniendo el histórico de versiones</t>
         </is>
       </c>
-      <c r="C7" s="34" t="n"/>
+      <c r="C7" s="31" t="n"/>
       <c r="D7" s="26" t="n"/>
     </row>
     <row r="8" ht="27.9" customHeight="1" s="28">
@@ -6497,35 +6452,34 @@
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>documentar formalmente los cambios al contrato conforme a los arts. 59 y 59 Bis LOPSRM (este último cuando la modificación supera el 50% del importe o del plazo) y poder consultar qué cambió, cuándo y por qué</t>
         </is>
       </c>
-      <c r="C8" s="34" t="n"/>
+      <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
       <c r="C11" s="26" t="n"/>
-      <c r="D11" s="38" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
@@ -6537,7 +6491,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Al autorizarse el modificatorio se generó una nueva versión del catálogo y del programa, sin alterar la versión anterior.</t>
         </is>
@@ -6555,7 +6509,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>El histórico de versiones registra fecha, autor y motivo del cambio para cada modificatorio.</t>
         </is>
@@ -6567,9 +6521,8 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
@@ -6586,7 +6539,7 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="C16" s="34" t="n"/>
+      <c r="C16" s="31" t="n"/>
       <c r="D16" s="26" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="28">
@@ -6598,7 +6551,7 @@
       <c r="B17" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="C17" s="34" t="n"/>
+      <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1" s="28">
@@ -6607,12 +6560,12 @@
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>Sprint 6</t>
         </is>
       </c>
-      <c r="C18" s="34" t="n"/>
+      <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1" s="28">
@@ -6621,12 +6574,12 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C19" s="34" t="n"/>
+      <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
@@ -6671,39 +6624,38 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>HU-04 · Consulta integrada del expediente contractual</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-01-04</t>
         </is>
       </c>
-      <c r="C2" s="39" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>Módulo: MOD-01</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Sprint sugerido: 4</t>
         </is>
       </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
@@ -6715,12 +6667,12 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="34" t="n"/>
+      <c r="C6" s="31" t="n"/>
       <c r="D6" s="26" t="n"/>
     </row>
     <row r="7" ht="29.1" customHeight="1" s="28">
@@ -6729,12 +6681,12 @@
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>consultar en una sola vista todos los elementos vigentes del contrato (configuración, catálogo, programa, fianzas, elementos jurídicos) con buscador</t>
         </is>
       </c>
-      <c r="C7" s="34" t="n"/>
+      <c r="C7" s="31" t="n"/>
       <c r="D7" s="26" t="n"/>
     </row>
     <row r="8" ht="27.9" customHeight="1" s="28">
@@ -6743,35 +6695,34 @@
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>obtener información del contrato sin tener que ir a cada módulo individualmente</t>
         </is>
       </c>
-      <c r="C8" s="34" t="n"/>
+      <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
       <c r="C11" s="26" t="n"/>
-      <c r="D11" s="38" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
@@ -6783,7 +6734,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>El expediente muestra en una sola vista los 5 bloques: configuración, catálogo, programa, fianzas y documentos jurídicos.</t>
         </is>
@@ -6801,7 +6752,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>El buscador filtra los bloques por folio, contratista, objeto, periodo o tipo de documento.</t>
         </is>
@@ -6813,9 +6764,8 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
@@ -6832,7 +6782,7 @@
           <t>Baja</t>
         </is>
       </c>
-      <c r="C16" s="34" t="n"/>
+      <c r="C16" s="31" t="n"/>
       <c r="D16" s="26" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="28">
@@ -6844,7 +6794,7 @@
       <c r="B17" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="34" t="n"/>
+      <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1" s="28">
@@ -6853,12 +6803,12 @@
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="C18" s="34" t="n"/>
+      <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1" s="28">
@@ -6867,12 +6817,12 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C19" s="34" t="n"/>
+      <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>
@@ -6907,7 +6857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" style="28" min="1" max="1"/>
@@ -6917,31 +6867,31 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>HU-05 · Visualización del programa y curva de avance</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-02-01</t>
         </is>
       </c>
-      <c r="C2" s="39" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>Módulo: MOD-02</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Sprint sugerido: 7</t>
         </is>
       </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
@@ -6949,7 +6899,7 @@
     </row>
     <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
@@ -6961,12 +6911,12 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="34" t="n"/>
+      <c r="C6" s="31" t="n"/>
       <c r="D6" s="26" t="n"/>
     </row>
     <row r="7" ht="27.9" customHeight="1" s="28">
@@ -6975,12 +6925,12 @@
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
-        <is>
-          <t>visualizar la curva S del contrato comparando avance programado, ejecutado y financiero, con filtros por concepto y periodo</t>
-        </is>
-      </c>
-      <c r="C7" s="34" t="n"/>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>visualizar el programa de obra (catálogo de conceptos y su calendario tipo Gantt, marcando lo ejecutado) y las curvas de avance (programado vs ejecutado vs financiero), con filtros por concepto y periodo</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="n"/>
       <c r="D7" s="26" t="n"/>
     </row>
     <row r="8" ht="27.9" customHeight="1" s="28">
@@ -6989,49 +6939,47 @@
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>identificar desviaciones entre lo planeado, lo ejecutado y lo cobrado para tomar decisiones a tiempo</t>
         </is>
       </c>
-      <c r="C8" s="34" t="n"/>
+      <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
     <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
       <c r="C11" s="26" t="n"/>
-      <c r="D11" s="38" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
     <row r="12" ht="32.1" customHeight="1" s="28">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B12" s="36" t="inlineStr">
-        <is>
-          <t>La pantalla grafica las tres curvas (programado, ejecutado, financiero) en un solo gráfico.</t>
+      <c r="A12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>La vista muestra el programa de obra como matriz concepto × periodo (tipo Gantt), con el catálogo de conceptos y un código de color que distingue lo ejecutado de lo no ejecutado.</t>
         </is>
       </c>
       <c r="C12" s="26" t="n"/>
@@ -7042,14 +6990,12 @@
       </c>
     </row>
     <row r="13" ht="32.1" customHeight="1" s="28">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B13" s="36" t="inlineStr">
-        <is>
-          <t>Los filtros por concepto y periodo modifican la gráfica y los porcentajes calculados.</t>
+      <c r="A13" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>La vista grafica las tres curvas (programado, ejecutado, financiero) y los filtros por concepto y periodo recalculan tanto la matriz como las curvas.</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
@@ -7059,67 +7005,77 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="32" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>El sistema calcula y muestra el porcentaje de avance global y por concepto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" s="28"/>
+    <row r="16" ht="24" customHeight="1" s="28">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Complejidad</t>
-        </is>
-      </c>
-      <c r="B16" s="42" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C16" s="34" t="n"/>
-      <c r="D16" s="26" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
-        </is>
-      </c>
-      <c r="B17" s="42" t="n">
-        <v>3</v>
-      </c>
-      <c r="C17" s="34" t="n"/>
+          <t>Complejidad</t>
+        </is>
+      </c>
+      <c r="B17" s="42" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>Sprint propuesto</t>
-        </is>
-      </c>
-      <c r="B18" s="37" t="inlineStr">
-        <is>
-          <t>Sprint 7</t>
-        </is>
-      </c>
-      <c r="C18" s="34" t="n"/>
+          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
+        </is>
+      </c>
+      <c r="B18" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
+          <t>Sprint propuesto</t>
+        </is>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="26" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C19" s="34" t="n"/>
-      <c r="D19" s="26" t="n"/>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -7153,7 +7109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" style="28" min="1" max="1"/>
@@ -7163,31 +7119,31 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="30" t="inlineStr">
-        <is>
-          <t>HU-06 · Registro de trabajos terminados por periodo</t>
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>HU-08 · Apertura formal de la bitácora del contrato</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="39" t="inlineStr">
-        <is>
-          <t>Servicio implementado: SRV-02-02</t>
-        </is>
-      </c>
-      <c r="C2" s="39" t="inlineStr">
-        <is>
-          <t>Módulo: MOD-02</t>
+      <c r="A2" s="32" t="inlineStr">
+        <is>
+          <t>Servicio implementado: SRV-03-01</t>
+        </is>
+      </c>
+      <c r="C2" s="32" t="inlineStr">
+        <is>
+          <t>Módulo: MOD-03</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="39" t="inlineStr">
-        <is>
-          <t>Sprint sugerido: 7</t>
-        </is>
-      </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
+        <is>
+          <t>Sprint sugerido: 1</t>
+        </is>
+      </c>
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
@@ -7195,7 +7151,7 @@
     </row>
     <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
@@ -7207,26 +7163,26 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
-        <is>
-          <t>contratista</t>
-        </is>
-      </c>
-      <c r="C6" s="34" t="n"/>
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>residente</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="n"/>
       <c r="D6" s="26" t="n"/>
     </row>
-    <row r="7" ht="29.1" customHeight="1" s="28">
+    <row r="7" ht="30" customHeight="1" s="28">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
-        <is>
-          <t>registrar por periodo las cantidades terminadas por cada concepto del catálogo, vinculando cada registro a su nota de bitácora del tipo Entrega</t>
-        </is>
-      </c>
-      <c r="C7" s="34" t="n"/>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>aperturar la bitácora electrónica del contrato en la fecha de entrega del sitio de los trabajos, ligando a las tres partes (dependencia, supervisión y contratista) con sus representantes autorizados a firmar, y registrando la primera nota con los datos obligatorios</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="n"/>
       <c r="D7" s="26" t="n"/>
     </row>
     <row r="8" ht="27.9" customHeight="1" s="28">
@@ -7235,49 +7191,47 @@
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
-        <is>
-          <t>alimentar la integración de la estimación con el avance real y dejar respaldo documental de cada cantidad reportada</t>
-        </is>
-      </c>
-      <c r="C8" s="34" t="n"/>
+      <c r="B8" s="34" t="inlineStr">
+        <is>
+          <t>habilitar el registro formal de eventos del contrato conforme al art. 46 último párrafo y al art. 52 Bis LOPSRM (bitácora electrónica obligatoria), reglamentados por el art. 122 RLOPSRM</t>
+        </is>
+      </c>
+      <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
     <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
       <c r="C11" s="26" t="n"/>
-      <c r="D11" s="38" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
     <row r="12" ht="32.1" customHeight="1" s="28">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B12" s="36" t="inlineStr">
-        <is>
-          <t>Cada cantidad capturada queda ligada al concepto del catálogo correspondiente y a una nota de bitácora del periodo.</t>
+      <c r="A12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>Existe una bitácora única por contrato con las tres partes ligadas y sus firmantes autorizados (residente, supervisor externo si existe, superintendente).</t>
         </is>
       </c>
       <c r="C12" s="26" t="n"/>
@@ -7288,14 +7242,12 @@
       </c>
     </row>
     <row r="13" ht="32.1" customHeight="1" s="28">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B13" s="36" t="inlineStr">
-        <is>
-          <t>El sistema bloquea el registro cuando la cantidad acumulada excede la contratada.</t>
+      <c r="A13" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>La fecha y hora de apertura (fecha de entrega del sitio) queda registrada como evento formal inalterable, con la firma conjunta de los tres autorizados.</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
@@ -7305,67 +7257,77 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="32" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>La primera nota registra los datos obligatorios: identificación del contrato, objeto, datos financieros, cronograma contractual y registro de firmas (art. 122 RLOPSRM).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" s="28"/>
+    <row r="16" ht="24" customHeight="1" s="28">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Complejidad</t>
-        </is>
-      </c>
-      <c r="B16" s="42" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C16" s="34" t="n"/>
-      <c r="D16" s="26" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
-        </is>
-      </c>
-      <c r="B17" s="42" t="n">
-        <v>3</v>
-      </c>
-      <c r="C17" s="34" t="n"/>
+          <t>Complejidad</t>
+        </is>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>Sprint propuesto</t>
-        </is>
-      </c>
-      <c r="B18" s="37" t="inlineStr">
-        <is>
-          <t>Sprint 7</t>
-        </is>
-      </c>
-      <c r="C18" s="34" t="n"/>
+          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
+          <t>Sprint propuesto</t>
+        </is>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="26" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C19" s="34" t="n"/>
-      <c r="D19" s="26" t="n"/>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -7409,31 +7371,31 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="30" t="inlineStr">
-        <is>
-          <t>HU-07 · Configuración de alertas de atraso por concepto</t>
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>HU-10 · Consulta y búsqueda de notas de bitácora</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="39" t="inlineStr">
-        <is>
-          <t>Servicio implementado: SRV-02-03</t>
-        </is>
-      </c>
-      <c r="C2" s="39" t="inlineStr">
-        <is>
-          <t>Módulo: MOD-02</t>
+      <c r="A2" s="32" t="inlineStr">
+        <is>
+          <t>Servicio implementado: SRV-03-03</t>
+        </is>
+      </c>
+      <c r="C2" s="32" t="inlineStr">
+        <is>
+          <t>Módulo: MOD-03</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="39" t="inlineStr">
-        <is>
-          <t>Sprint sugerido: 6</t>
-        </is>
-      </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
+        <is>
+          <t>Sprint sugerido: 3</t>
+        </is>
+      </c>
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
@@ -7441,7 +7403,7 @@
     </row>
     <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
@@ -7453,26 +7415,26 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="34" t="n"/>
+      <c r="C6" s="31" t="n"/>
       <c r="D6" s="26" t="n"/>
     </row>
-    <row r="7" ht="29.1" customHeight="1" s="28">
+    <row r="7" ht="27.9" customHeight="1" s="28">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
-        <is>
-          <t>configurar qué conceptos del contrato quiero vigilar, el umbral de atraso a partir del cual quiero ser notificado y el canal de notificación</t>
-        </is>
-      </c>
-      <c r="C7" s="34" t="n"/>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>buscar notas de la bitácora del contrato combinando los filtros tipo, rango de fechas, firmante, vínculo y palabra clave, todos aplicados con lógica Y (AND), y exportar las notas seleccionadas en formato Excel</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="n"/>
       <c r="D7" s="26" t="n"/>
     </row>
     <row r="8" ht="27.9" customHeight="1" s="28">
@@ -7481,49 +7443,47 @@
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
-        <is>
-          <t>recibir alertas solo de lo que decidí vigilar, sin saturación de notificaciones</t>
-        </is>
-      </c>
-      <c r="C8" s="34" t="n"/>
+      <c r="B8" s="34" t="inlineStr">
+        <is>
+          <t>encontrar rápido la nota que necesito y poder referenciarla en estimaciones o reportes</t>
+        </is>
+      </c>
+      <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
     <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
       <c r="C11" s="26" t="n"/>
-      <c r="D11" s="38" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
     <row r="12" ht="32.1" customHeight="1" s="28">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B12" s="36" t="inlineStr">
-        <is>
-          <t>Se pueden crear, pausar y eliminar alertas por concepto sin alterar las del resto.</t>
+      <c r="A12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>La búsqueda devuelve solo las notas que cumplen simultáneamente todos los filtros aplicados (tipo, fecha, firmante, vínculo y palabra clave).</t>
         </is>
       </c>
       <c r="C12" s="26" t="n"/>
@@ -7534,14 +7494,12 @@
       </c>
     </row>
     <row r="13" ht="32.1" customHeight="1" s="28">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B13" s="36" t="inlineStr">
-        <is>
-          <t>El sistema solo dispara alertas cuando el avance real es menor al umbral configurado por el usuario.</t>
+      <c r="A13" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>Se pueden seleccionar varias notas del resultado y exportarlas en formato Excel.</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
@@ -7553,7 +7511,7 @@
     </row>
     <row r="14"/>
     <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
@@ -7570,7 +7528,7 @@
           <t>Baja</t>
         </is>
       </c>
-      <c r="C16" s="34" t="n"/>
+      <c r="C16" s="31" t="n"/>
       <c r="D16" s="26" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="28">
@@ -7582,7 +7540,7 @@
       <c r="B17" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="34" t="n"/>
+      <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1" s="28">
@@ -7591,12 +7549,12 @@
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="37" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="C18" s="34" t="n"/>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1" s="28">
@@ -7605,12 +7563,12 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C19" s="34" t="n"/>
+      <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
     </row>
   </sheetData>

--- a/docs/Historias_Usuario.xlsx
+++ b/docs/Historias_Usuario.xlsx
@@ -1725,7 +1725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" style="28" min="1" max="1"/>
@@ -1765,6 +1765,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -1794,7 +1795,7 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>registrar por periodo las cantidades terminadas por cada concepto del catálogo, vinculando cada registro a su nota de bitácora del tipo Entrega</t>
+          <t>registrar por periodo las cantidades terminadas por cada concepto del catálogo, vinculando cada registro a su nota de bitácora del periodo, viendo el avance acumulado contra lo contratado en vivo</t>
         </is>
       </c>
       <c r="C7" s="31" t="n"/>
@@ -1814,6 +1815,7 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -1840,14 +1842,12 @@
       </c>
     </row>
     <row r="12" ht="32.1" customHeight="1" s="28">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A12" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>Cada cantidad capturada queda ligada al concepto del catálogo correspondiente y a una nota de bitácora del periodo.</t>
+          <t>Cada cantidad capturada queda ligada al concepto del catálogo correspondiente y a una nota de bitácora del periodo (tipo entrega de obra o avance).</t>
         </is>
       </c>
       <c r="C12" s="26" t="n"/>
@@ -1858,14 +1858,12 @@
       </c>
     </row>
     <row r="13" ht="32.1" customHeight="1" s="28">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A13" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>El sistema bloquea el registro cuando la cantidad acumulada excede la contratada.</t>
+          <t>El sistema acumula el avance ejecutado por concepto y muestra el porcentaje de avance contra lo contratado en vivo, periodo a periodo.</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
@@ -1875,35 +1873,34 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="29" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>El sistema bloquea el registro cuando la cantidad acumulada excede la contratada (art. 118 RLOPSRM).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" s="28"/>
+    <row r="16" ht="24" customHeight="1" s="28">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Complejidad</t>
-        </is>
-      </c>
-      <c r="B16" s="42" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C16" s="31" t="n"/>
-      <c r="D16" s="26" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
-        </is>
-      </c>
-      <c r="B17" s="42" t="n">
-        <v>3</v>
+          <t>Complejidad</t>
+        </is>
+      </c>
+      <c r="B17" s="42" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
       </c>
       <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
@@ -1911,13 +1908,11 @@
     <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>Sprint propuesto</t>
-        </is>
-      </c>
-      <c r="B18" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 7</t>
-        </is>
+          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
+        </is>
+      </c>
+      <c r="B18" s="42" t="n">
+        <v>3</v>
       </c>
       <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
@@ -1925,24 +1920,38 @@
     <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Sprint propuesto</t>
         </is>
       </c>
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>En desarrollo</t>
+          <t>Sprint 7</t>
         </is>
       </c>
       <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>En desarrollo</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -1968,7 +1977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" style="28" min="1" max="1"/>
@@ -2008,6 +2017,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -2037,7 +2047,7 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>configurar qué conceptos del contrato quiero vigilar, el umbral de atraso a partir del cual quiero ser notificado y el canal de notificación</t>
+          <t>configurar qué conceptos del contrato quiero vigilar, el umbral de atraso a partir del cual quiero ser notificado y el canal de notificación (sistema o correo)</t>
         </is>
       </c>
       <c r="C7" s="31" t="n"/>
@@ -2057,6 +2067,7 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -2083,10 +2094,8 @@
       </c>
     </row>
     <row r="12" ht="32.1" customHeight="1" s="28">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A12" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
@@ -2101,14 +2110,12 @@
       </c>
     </row>
     <row r="13" ht="32.1" customHeight="1" s="28">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A13" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>El sistema solo dispara alertas cuando el avance real es menor al umbral configurado por el usuario.</t>
+          <t>La alerta solo dispara cuando el avance real es menor al umbral configurado por el usuario.</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
@@ -2118,35 +2125,34 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="29" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>La notificación se entrega por el canal elegido al configurar la alerta (sistema o correo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" s="28"/>
+    <row r="16" ht="24" customHeight="1" s="28">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Complejidad</t>
-        </is>
-      </c>
-      <c r="B16" s="35" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="C16" s="31" t="n"/>
-      <c r="D16" s="26" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
-        </is>
-      </c>
-      <c r="B17" s="35" t="n">
-        <v>2</v>
+          <t>Complejidad</t>
+        </is>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
       </c>
       <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
@@ -2154,13 +2160,11 @@
     <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>Sprint propuesto</t>
-        </is>
-      </c>
-      <c r="B18" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
+          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="n">
+        <v>2</v>
       </c>
       <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
@@ -2168,24 +2172,38 @@
     <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Sprint propuesto</t>
         </is>
       </c>
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>En desarrollo</t>
+          <t>Sprint 6</t>
         </is>
       </c>
       <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>En desarrollo</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -2251,7 +2269,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -2301,7 +2318,6 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -2375,7 +2391,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16" ht="24" customHeight="1" s="28">
       <c r="A16" s="29" t="inlineStr">
         <is>
@@ -2470,7 +2485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" style="28" min="1" max="1"/>
@@ -2510,6 +2525,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -2539,7 +2555,7 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>subir minutas de reuniones del contrato con sus metadatos, agendar visitas e inspecciones de campo, y consultar los acuerdos asentados</t>
+          <t>subir el PDF de las minutas de reuniones del contrato con sus metadatos, agendar visitas e inspecciones de campo, y consultar los acuerdos asentados, pudiendo adjuntar una minuta como referencia en una nota de bitácora</t>
         </is>
       </c>
       <c r="C7" s="31" t="n"/>
@@ -2559,6 +2575,7 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -2585,14 +2602,12 @@
       </c>
     </row>
     <row r="12" ht="32.1" customHeight="1" s="28">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A12" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>Las minutas y visitas registradas son visibles para los usuarios autorizados del contrato.</t>
+          <t>Las minutas (con su PDF y metadatos) y las visitas registradas son visibles para los usuarios autorizados del contrato.</t>
         </is>
       </c>
       <c r="C12" s="26" t="n"/>
@@ -2603,10 +2618,8 @@
       </c>
     </row>
     <row r="13" ht="32.1" customHeight="1" s="28">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A13" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
@@ -2620,35 +2633,34 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="29" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Una minuta o registro de visita puede adjuntarse como referencia en una nota de bitácora (HU-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" s="28"/>
+    <row r="16" ht="24" customHeight="1" s="28">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Complejidad</t>
-        </is>
-      </c>
-      <c r="B16" s="42" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C16" s="31" t="n"/>
-      <c r="D16" s="26" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
-        </is>
-      </c>
-      <c r="B17" s="42" t="n">
-        <v>3</v>
+          <t>Complejidad</t>
+        </is>
+      </c>
+      <c r="B17" s="42" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
       </c>
       <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
@@ -2656,13 +2668,11 @@
     <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>Sprint propuesto</t>
-        </is>
-      </c>
-      <c r="B18" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 7</t>
-        </is>
+          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
+        </is>
+      </c>
+      <c r="B18" s="42" t="n">
+        <v>3</v>
       </c>
       <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
@@ -2670,24 +2680,38 @@
     <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Sprint propuesto</t>
         </is>
       </c>
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>En desarrollo</t>
+          <t>Sprint 7</t>
         </is>
       </c>
       <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>En desarrollo</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -2753,7 +2777,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -2803,7 +2826,6 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -2877,7 +2899,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16" ht="24" customHeight="1" s="28">
       <c r="A16" s="29" t="inlineStr">
         <is>
@@ -2972,7 +2993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" style="28" min="1" max="1"/>
@@ -3012,6 +3033,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -3041,7 +3063,7 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>enviar formalmente una estimación integrada para que arranque el plazo de revisión del art. 54 LOPSRM</t>
+          <t>enviar formalmente una estimación integrada para que arranque el plazo de revisión del art. 54 LOPSRM, dentro de los 6 días naturales del periodo de presentación</t>
         </is>
       </c>
       <c r="C7" s="31" t="n"/>
@@ -3061,6 +3083,7 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -3087,14 +3110,12 @@
       </c>
     </row>
     <row r="12" ht="32.1" customHeight="1" s="28">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A12" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>Al enviar la estimación queda registrada la fecha y hora exacta, y se notifica a residencia y supervisión.</t>
+          <t>Al enviar la estimación quedan registradas la fecha y hora exacta de recepción, y queda notificación formal a residencia y supervisión.</t>
         </is>
       </c>
       <c r="C12" s="26" t="n"/>
@@ -3105,10 +3126,8 @@
       </c>
     </row>
     <row r="13" ht="32.1" customHeight="1" s="28">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A13" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
@@ -3122,35 +3141,34 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="29" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Al enviarse, inicia automáticamente el plazo de revisión de 15 días naturales (supervisión, art. 54 LOPSRM).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" s="28"/>
+    <row r="16" ht="24" customHeight="1" s="28">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Complejidad</t>
-        </is>
-      </c>
-      <c r="B16" s="42" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C16" s="31" t="n"/>
-      <c r="D16" s="26" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
-        </is>
-      </c>
-      <c r="B17" s="42" t="n">
-        <v>3</v>
+          <t>Complejidad</t>
+        </is>
+      </c>
+      <c r="B17" s="42" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
       </c>
       <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
@@ -3158,13 +3176,11 @@
     <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>Sprint propuesto</t>
-        </is>
-      </c>
-      <c r="B18" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 8</t>
-        </is>
+          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
+        </is>
+      </c>
+      <c r="B18" s="42" t="n">
+        <v>3</v>
       </c>
       <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
@@ -3172,24 +3188,38 @@
     <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Sprint propuesto</t>
         </is>
       </c>
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>En desarrollo</t>
+          <t>Sprint 8</t>
         </is>
       </c>
       <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>En desarrollo</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -3215,7 +3245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" style="28" min="1" max="1"/>
@@ -3255,6 +3285,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -3284,7 +3315,7 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>consultar todas las estimaciones del contrato a lo largo del tiempo con sus estados (aceptadas, rechazadas, en proceso) y filtros por periodo</t>
+          <t>consultar todas las estimaciones del contrato a lo largo del tiempo con sus estados (aceptadas, rechazadas, en proceso) y filtros por periodo, pudiendo abrir cada una para ver su expediente</t>
         </is>
       </c>
       <c r="C7" s="31" t="n"/>
@@ -3304,6 +3335,7 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -3330,14 +3362,12 @@
       </c>
     </row>
     <row r="12" ht="32.1" customHeight="1" s="28">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A12" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>El historial muestra todas las estimaciones del contrato, incluyendo las versiones rechazadas.</t>
+          <t>El historial muestra todas las estimaciones del contrato en orden cronológico, incluyendo las versiones rechazadas.</t>
         </is>
       </c>
       <c r="C12" s="26" t="n"/>
@@ -3348,14 +3378,12 @@
       </c>
     </row>
     <row r="13" ht="32.1" customHeight="1" s="28">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A13" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>Por cada periodo solo puede haber una estimación aceptada; las versiones previas quedan marcadas como rechazadas.</t>
+          <t>Los filtros permiten consultar por periodo, estado o ambos combinados (lógica Y).</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
@@ -3365,35 +3393,34 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="29" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cada estimación del historial puede abrirse para ver su expediente completo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" s="28"/>
+    <row r="16" ht="24" customHeight="1" s="28">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Complejidad</t>
-        </is>
-      </c>
-      <c r="B16" s="35" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="C16" s="31" t="n"/>
-      <c r="D16" s="26" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
-        </is>
-      </c>
-      <c r="B17" s="35" t="n">
-        <v>2</v>
+          <t>Complejidad</t>
+        </is>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
       </c>
       <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
@@ -3401,13 +3428,11 @@
     <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>Sprint propuesto</t>
-        </is>
-      </c>
-      <c r="B18" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
+          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="n">
+        <v>2</v>
       </c>
       <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
@@ -3415,24 +3440,38 @@
     <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Sprint propuesto</t>
         </is>
       </c>
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>En desarrollo</t>
+          <t>Sprint 5</t>
         </is>
       </c>
       <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>En desarrollo</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -3498,6 +3537,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -3527,7 +3567,7 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>revisar la estimación recibida sección por sección (carátula, números generadores, registro fotográfico, soportes, notas), registrar observaciones puntuales, turnar de supervisión a residencia y al final autorizar o rechazar</t>
+          <t>revisar la estimación recibida sección por sección (carátula, números generadores, registro fotográfico, soportes, notas), registrar observaciones con tipo y severidad, turnar de supervisión a residencia y al final autorizar o rechazar</t>
         </is>
       </c>
       <c r="C7" s="31" t="n"/>
@@ -3547,6 +3587,7 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -3573,14 +3614,12 @@
       </c>
     </row>
     <row r="12" ht="33" customHeight="1" s="28">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A12" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>La revisión permite revisar sección por sección y dejar observaciones puntuales en cada una (carátula, generadores, registro fotográfico, soportes y notas).</t>
+          <t>La revisión permite ir sección por sección (carátula, generadores, registro fotográfico, soportes y notas) y registrar observaciones con tipo y severidad por concepto.</t>
         </is>
       </c>
       <c r="C12" s="26" t="n"/>
@@ -3591,10 +3630,8 @@
       </c>
     </row>
     <row r="13" ht="32.1" customHeight="1" s="28">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A13" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
@@ -3609,14 +3646,12 @@
       </c>
     </row>
     <row r="14" ht="33" customHeight="1" s="28">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="A14" s="13" t="n">
+        <v>3</v>
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>El sistema controla el plazo de 15 días naturales de revisión conforme al art. 54 LOPSRM mediante un semáforo visible para los actores.</t>
+          <t>El sistema controla el plazo de 15 días naturales de revisión conforme al art. 54 LOPSRM mediante un semáforo basado en la fecha real de recepción.</t>
         </is>
       </c>
       <c r="C14" s="26" t="n"/>
@@ -3626,6 +3661,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="24" customHeight="1" s="28">
       <c r="A16" s="29" t="inlineStr">
         <is>
@@ -3720,7 +3756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" style="28" min="1" max="1"/>
@@ -3760,6 +3796,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -3809,6 +3846,7 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -3835,10 +3873,8 @@
       </c>
     </row>
     <row r="12" ht="32.1" customHeight="1" s="28">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A12" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
@@ -3853,10 +3889,8 @@
       </c>
     </row>
     <row r="13" ht="32.1" customHeight="1" s="28">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A13" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
@@ -3870,35 +3904,34 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="29" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>La nueva versión queda vinculada con la rechazada para trazabilidad, sin reiniciar el plazo de presentación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" s="28"/>
+    <row r="16" ht="24" customHeight="1" s="28">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Complejidad</t>
-        </is>
-      </c>
-      <c r="B16" s="42" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C16" s="31" t="n"/>
-      <c r="D16" s="26" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
-        </is>
-      </c>
-      <c r="B17" s="42" t="n">
-        <v>3</v>
+          <t>Complejidad</t>
+        </is>
+      </c>
+      <c r="B17" s="42" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
       </c>
       <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
@@ -3906,13 +3939,11 @@
     <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>Sprint propuesto</t>
-        </is>
-      </c>
-      <c r="B18" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 8</t>
-        </is>
+          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
+        </is>
+      </c>
+      <c r="B18" s="42" t="n">
+        <v>3</v>
       </c>
       <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
@@ -3920,24 +3951,38 @@
     <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Sprint propuesto</t>
         </is>
       </c>
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>En desarrollo</t>
+          <t>Sprint 8</t>
         </is>
       </c>
       <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>En desarrollo</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -3963,7 +4008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" style="28" min="1" max="1"/>
@@ -4003,6 +4048,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -4032,7 +4078,7 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>ver en un tablero las estimaciones del contrato que están aceptadas y las que están en proceso (presentada, en revisión, autorizada, en pago, pagada), con su línea de tiempo y pendientes por solventar</t>
+          <t>ver en un tablero las estimaciones del contrato aceptadas y en proceso (presentada, en revisión, autorizada, en pago, pagada), con su línea de tiempo, indicadores y pendientes por solventar</t>
         </is>
       </c>
       <c r="C7" s="31" t="n"/>
@@ -4052,6 +4098,7 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -4078,10 +4125,8 @@
       </c>
     </row>
     <row r="12" ht="32.1" customHeight="1" s="28">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A12" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
@@ -4096,14 +4141,12 @@
       </c>
     </row>
     <row r="13" ht="32.1" customHeight="1" s="28">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A13" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>El panel "Mis pendientes" filtra los pendientes según el rol del usuario autenticado.</t>
+          <t>Cada estimación muestra su línea de tiempo de estado, y el tablero da indicadores agregados del contrato (avance, montos, días en cada estado).</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
@@ -4113,35 +4156,34 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="29" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>El panel «Mis pendientes» filtra los pendientes según el rol del usuario autenticado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" s="28"/>
+    <row r="16" ht="24" customHeight="1" s="28">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Complejidad</t>
-        </is>
-      </c>
-      <c r="B16" s="42" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C16" s="31" t="n"/>
-      <c r="D16" s="26" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
-        </is>
-      </c>
-      <c r="B17" s="42" t="n">
-        <v>3</v>
+          <t>Complejidad</t>
+        </is>
+      </c>
+      <c r="B17" s="42" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
       </c>
       <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
@@ -4149,13 +4191,11 @@
     <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>Sprint propuesto</t>
-        </is>
-      </c>
-      <c r="B18" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 8</t>
-        </is>
+          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
+        </is>
+      </c>
+      <c r="B18" s="42" t="n">
+        <v>3</v>
       </c>
       <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
@@ -4163,24 +4203,38 @@
     <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Sprint propuesto</t>
         </is>
       </c>
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>En desarrollo</t>
+          <t>Sprint 8</t>
         </is>
       </c>
       <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>En desarrollo</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -4472,7 +4526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" style="28" min="1" max="1"/>
@@ -4512,6 +4566,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -4561,6 +4616,7 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -4587,14 +4643,12 @@
       </c>
     </row>
     <row r="12" ht="32.1" customHeight="1" s="28">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A12" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>Cada contrato del portafolio muestra un semáforo de color calculado a partir de avance físico, atrasos y pendientes.</t>
+          <t>Cada contrato del portafolio muestra un semáforo de color calculado a partir de tres factores: avance físico vs programado, atrasos en plazos legales y pendientes sin atender.</t>
         </is>
       </c>
       <c r="C12" s="26" t="n"/>
@@ -4605,14 +4659,12 @@
       </c>
     </row>
     <row r="13" ht="32.1" customHeight="1" s="28">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A13" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>Al hacer doble clic sobre un contrato se abre su detalle con indicadores físicos, financieros y penalizaciones.</t>
+          <t>Al hacer doble clic sobre un contrato se abre su detalle con indicadores físicos, financieros, atrasos y penalizaciones.</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
@@ -4622,35 +4674,34 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="29" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>El portafolio puede agruparse (por contratista, ejercicio fiscal o tipo de contratación) y comparar el periodo actual contra el anterior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" s="28"/>
+    <row r="16" ht="24" customHeight="1" s="28">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Complejidad</t>
-        </is>
-      </c>
-      <c r="B16" s="42" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C16" s="31" t="n"/>
-      <c r="D16" s="26" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
-        </is>
-      </c>
-      <c r="B17" s="41" t="n">
-        <v>5</v>
+          <t>Complejidad</t>
+        </is>
+      </c>
+      <c r="B17" s="42" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
       </c>
       <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
@@ -4658,13 +4709,11 @@
     <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>Sprint propuesto</t>
-        </is>
-      </c>
-      <c r="B18" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 9</t>
-        </is>
+          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
+        </is>
+      </c>
+      <c r="B18" s="41" t="n">
+        <v>5</v>
       </c>
       <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
@@ -4672,24 +4721,38 @@
     <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Sprint propuesto</t>
         </is>
       </c>
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>En desarrollo</t>
+          <t>Sprint 9</t>
         </is>
       </c>
       <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>En desarrollo</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -4755,6 +4818,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -4804,6 +4868,7 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -4830,14 +4895,12 @@
       </c>
     </row>
     <row r="12" ht="32.1" customHeight="1" s="28">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A12" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>Cada uno de los 7 reportes definidos genera el archivo en el formato establecido (PDF, Excel o ambos).</t>
+          <t>Cada uno de los 7 reportes definidos genera un archivo descargable en el formato establecido (PDF, Excel o ambos según el reporte).</t>
         </is>
       </c>
       <c r="C12" s="26" t="n"/>
@@ -4848,10 +4911,8 @@
       </c>
     </row>
     <row r="13" ht="33" customHeight="1" s="28">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A13" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
@@ -4865,6 +4926,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="24" customHeight="1" s="28">
       <c r="A15" s="29" t="inlineStr">
         <is>
@@ -4931,8 +4993,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -4998,6 +5060,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -5047,6 +5110,7 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -5073,10 +5137,8 @@
       </c>
     </row>
     <row r="12" ht="32.1" customHeight="1" s="28">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A12" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
@@ -5091,14 +5153,12 @@
       </c>
     </row>
     <row r="13" ht="33.9" customHeight="1" s="28">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A13" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>Un semáforo muestra el avance del plazo de 20 días naturales para pago (art. 54 LOPSRM) y emite alertas al entrar en amarillo.</t>
+          <t>Un semáforo muestra el avance del plazo de 20 días naturales para pago (art. 54 LOPSRM), basado en la fecha de autorización, y avisa al entrar en amarillo.</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
@@ -5109,14 +5169,12 @@
       </c>
     </row>
     <row r="14" ht="36.9" customHeight="1" s="28">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="A14" s="13" t="n">
+        <v>3</v>
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>La instrucción de pago solo puede generarse cuando todos los soportes obligatorios (factura, CFDI, estado de fianza) están cargados.</t>
+          <t>La instrucción de pago solo puede generarse cuando todos los soportes obligatorios (factura, CFDI, estado de fianza de cumplimiento cuando el contrato lo exija) están cargados.</t>
         </is>
       </c>
       <c r="C14" s="26" t="n"/>
@@ -5126,6 +5184,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="24" customHeight="1" s="28">
       <c r="A16" s="29" t="inlineStr">
         <is>
@@ -5436,8 +5495,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -5894,7 +5953,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -5944,7 +6002,6 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -6018,7 +6075,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16" ht="24" customHeight="1" s="28">
       <c r="A16" s="29" t="inlineStr">
         <is>
@@ -6153,6 +6209,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -6182,7 +6239,7 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>subir las pólizas de fianza del contrato (cumplimiento, vicios ocultos, anticipo) con sus metadatos: vigencia, afianzadora y monto afianzado</t>
+          <t>subir las pólizas de fianza del contrato (cumplimiento, vicios ocultos, anticipo) con sus metadatos (vigencia, afianzadora y monto), recibir alertas anticipadas de vencimiento y mantener el historial de fianzas y sus endosos por modificatorios</t>
         </is>
       </c>
       <c r="C7" s="31" t="n"/>
@@ -6202,6 +6259,7 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -6228,10 +6286,8 @@
       </c>
     </row>
     <row r="12" ht="32.1" customHeight="1" s="28">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A12" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
@@ -6246,14 +6302,12 @@
       </c>
     </row>
     <row r="13" ht="32.1" customHeight="1" s="28">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A13" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>El sistema emite alerta cuando faltan N días configurables para el vencimiento.</t>
+          <t>El sistema emite alerta cuando faltan 30, 15 y 5 días para el vencimiento (configurable).</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
@@ -6344,8 +6398,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -6371,7 +6425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" style="28" min="1" max="1"/>
@@ -6411,6 +6465,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -6440,7 +6495,7 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>registrar un convenio modificatorio del contrato (cambios al monto, plazo o conceptos) y aplicar las actualizaciones al catálogo, programa y fianzas, manteniendo el histórico de versiones</t>
+          <t>registrar un convenio modificatorio del contrato (cambios al monto, plazo o conceptos) y aplicar las actualizaciones al catálogo, programa y endosos de las fianzas, manteniendo el histórico de versiones conforme al art. 59 LOPSRM</t>
         </is>
       </c>
       <c r="C7" s="31" t="n"/>
@@ -6460,6 +6515,7 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -6486,14 +6542,12 @@
       </c>
     </row>
     <row r="12" ht="33" customHeight="1" s="28">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A12" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>Al autorizarse el modificatorio se generó una nueva versión del catálogo y del programa, sin alterar la versión anterior.</t>
+          <t>Al registrarse el modificatorio se genera una nueva versión del catálogo y del programa, sin alterar la versión anterior.</t>
         </is>
       </c>
       <c r="C12" s="26" t="n"/>
@@ -6504,14 +6558,12 @@
       </c>
     </row>
     <row r="13" ht="32.1" customHeight="1" s="28">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A13" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>El histórico de versiones registra fecha, autor y motivo del cambio para cada modificatorio.</t>
+          <t>El sistema indica si el modificatorio se rige por el art. 59 LOPSRM (modificatorio ordinario) o por el art. 59 Bis (ajuste de costos cuando se supera 50% del monto o 50% del plazo).</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
@@ -6521,35 +6573,34 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="29" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>El histórico de versiones registra fecha, autor y motivo del cambio, y los endosos correspondientes a las fianzas asociadas al modificatorio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" s="28"/>
+    <row r="16" ht="24" customHeight="1" s="28">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Complejidad</t>
-        </is>
-      </c>
-      <c r="B16" s="40" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="C16" s="31" t="n"/>
-      <c r="D16" s="26" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
-        </is>
-      </c>
-      <c r="B17" s="41" t="n">
-        <v>5</v>
+          <t>Complejidad</t>
+        </is>
+      </c>
+      <c r="B17" s="40" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
       </c>
       <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
@@ -6557,13 +6608,11 @@
     <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>Sprint propuesto</t>
-        </is>
-      </c>
-      <c r="B18" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
+          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
+        </is>
+      </c>
+      <c r="B18" s="41" t="n">
+        <v>5</v>
       </c>
       <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
@@ -6571,24 +6620,38 @@
     <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Sprint propuesto</t>
         </is>
       </c>
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>En desarrollo</t>
+          <t>Sprint 6</t>
         </is>
       </c>
       <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>En desarrollo</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -6614,7 +6677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" style="28" min="1" max="1"/>
@@ -6654,6 +6717,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -6683,7 +6747,7 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>consultar en una sola vista todos los elementos vigentes del contrato (configuración, catálogo, programa, fianzas, elementos jurídicos) con buscador</t>
+          <t>consultar en una sola vista los 5 bloques vigentes del contrato (configuración, catálogo, programa, fianzas y documentos jurídicos), con buscador combinable y descarga individual de documentos</t>
         </is>
       </c>
       <c r="C7" s="31" t="n"/>
@@ -6703,6 +6767,7 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -6729,14 +6794,12 @@
       </c>
     </row>
     <row r="12" ht="32.1" customHeight="1" s="28">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A12" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>El expediente muestra en una sola vista los 5 bloques: configuración, catálogo, programa, fianzas y documentos jurídicos.</t>
+          <t>El expediente muestra en una sola vista los 5 bloques del contrato: configuración, catálogo, programa, fianzas y documentos jurídicos.</t>
         </is>
       </c>
       <c r="C12" s="26" t="n"/>
@@ -6747,14 +6810,12 @@
       </c>
     </row>
     <row r="13" ht="32.1" customHeight="1" s="28">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A13" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>El buscador filtra los bloques por folio, contratista, objeto, periodo o tipo de documento.</t>
+          <t>El buscador filtra los bloques por folio, contratista, objeto, periodo o tipo de documento, con lógica Y.</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
@@ -6764,35 +6825,34 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="29" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cada documento del expediente puede descargarse individualmente desde su bloque.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" s="28"/>
+    <row r="16" ht="24" customHeight="1" s="28">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Complejidad</t>
-        </is>
-      </c>
-      <c r="B16" s="35" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="C16" s="31" t="n"/>
-      <c r="D16" s="26" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="28">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
-        </is>
-      </c>
-      <c r="B17" s="35" t="n">
-        <v>2</v>
+          <t>Complejidad</t>
+        </is>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
       </c>
       <c r="C17" s="31" t="n"/>
       <c r="D17" s="26" t="n"/>
@@ -6800,13 +6860,11 @@
     <row r="18" ht="24" customHeight="1" s="28">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>Sprint propuesto</t>
-        </is>
-      </c>
-      <c r="B18" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
+          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="n">
+        <v>2</v>
       </c>
       <c r="C18" s="31" t="n"/>
       <c r="D18" s="26" t="n"/>
@@ -6814,24 +6872,38 @@
     <row r="19" ht="24" customHeight="1" s="28">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Sprint propuesto</t>
         </is>
       </c>
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>En desarrollo</t>
+          <t>Sprint 4</t>
         </is>
       </c>
       <c r="C19" s="31" t="n"/>
       <c r="D19" s="26" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>En desarrollo</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -6897,7 +6969,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -6947,7 +7018,6 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -7082,8 +7152,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -7149,7 +7219,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -7199,7 +7268,6 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -7334,8 +7402,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -7401,7 +7469,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -7451,7 +7518,6 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -7509,7 +7575,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="24" customHeight="1" s="28">
       <c r="A15" s="29" t="inlineStr">
         <is>
@@ -7576,8 +7641,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>

--- a/docs/Historias_Usuario.xlsx
+++ b/docs/Historias_Usuario.xlsx
@@ -29,8 +29,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HU-19" sheetId="21" state="visible" r:id="rId21"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HU-20" sheetId="22" state="visible" r:id="rId22"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HU-21" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan_Iteraciones" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registro" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan_Iteraciones" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -698,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="9" customWidth="1" style="28" min="1" max="1"/>
@@ -1698,6 +1699,44 @@
       <c r="H31" s="5" t="inlineStr">
         <is>
           <t>Sprint 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="27.9" customHeight="1" s="28">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Registro</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Registro de usuario con aprobación</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Control de Accesos</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Usuario nuevo / Dependencia</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>Agregada tras la revisión</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1804,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -1815,7 +1853,6 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -1950,8 +1987,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -2017,7 +2054,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -2067,7 +2103,6 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -2202,8 +2237,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -2525,7 +2560,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -2575,7 +2609,6 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -2710,8 +2743,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -3033,7 +3066,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -3083,7 +3115,6 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -3218,8 +3249,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -3285,7 +3316,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -3335,7 +3365,6 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -3470,8 +3499,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -3537,7 +3566,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -3587,7 +3615,6 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -3661,7 +3688,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16" ht="24" customHeight="1" s="28">
       <c r="A16" s="29" t="inlineStr">
         <is>
@@ -3796,7 +3822,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -3846,7 +3871,6 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -3981,8 +4005,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -4048,7 +4072,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -4098,7 +4121,6 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -4233,8 +4255,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -4566,7 +4588,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -4616,7 +4637,6 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -4751,8 +4771,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -4818,7 +4838,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -4868,7 +4887,6 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -4926,7 +4944,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="24" customHeight="1" s="28">
       <c r="A15" s="29" t="inlineStr">
         <is>
@@ -4993,8 +5010,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -5060,7 +5077,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -5110,7 +5126,6 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -5184,7 +5199,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16" ht="24" customHeight="1" s="28">
       <c r="A16" s="29" t="inlineStr">
         <is>
@@ -5495,8 +5509,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -5522,6 +5536,270 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="16" customWidth="1" style="28" min="1" max="1"/>
+    <col width="50" customWidth="1" style="28" min="2" max="2"/>
+    <col width="25" customWidth="1" style="28" min="3" max="3"/>
+    <col width="18" customWidth="1" style="28" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>Registro · Registro de usuario con aprobación</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" s="28">
+      <c r="A2" s="32" t="inlineStr">
+        <is>
+          <t>Servicio implementado: Control de Accesos</t>
+        </is>
+      </c>
+      <c r="C2" s="32" t="inlineStr">
+        <is>
+          <t>Módulo: —</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1" s="28">
+      <c r="A3" s="32" t="inlineStr">
+        <is>
+          <t>Sprint sugerido: Agregada tras la revisión</t>
+        </is>
+      </c>
+      <c r="C3" s="32" t="inlineStr">
+        <is>
+          <t>Estado: Backlog</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" s="28">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>HISTORIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="27.9" customHeight="1" s="28">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>usuario nuevo</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="n"/>
+      <c r="D6" s="26" t="n"/>
+    </row>
+    <row r="7" ht="69" customHeight="1" s="28">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Deseo</t>
+        </is>
+      </c>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>registrarme en el sistema proporcionando mis datos</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="n"/>
+      <c r="D7" s="26" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="28">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>A fin de</t>
+        </is>
+      </c>
+      <c r="B8" s="34" t="inlineStr">
+        <is>
+          <t>solicitar acceso y que la dependencia valide mi identidad y asigne mi rol</t>
+        </is>
+      </c>
+      <c r="C8" s="31" t="n"/>
+      <c r="D8" s="26" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" s="28">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>CRITERIOS DE ACEPTACIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>Criterios de aceptación</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="33" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32.1" customHeight="1" s="28">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>El registro captura los datos del solicitante y crea la cuenta en estado pendiente, sin otorgar acceso.</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>☐ Sí   ☐ No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32.1" customHeight="1" s="28">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>El sistema impide el ingreso de cuentas no aprobadas e informa que están pendientes de autorización.</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>☐ Sí   ☐ No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32.1" customHeight="1" s="28">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>La dependencia revisa las solicitudes, asigna el rol y aprueba o rechaza; solo las cuentas aprobadas pueden ingresar.</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="n"/>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>☐ Sí   ☐ No</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="25" t="n"/>
+    </row>
+    <row r="16" ht="24" customHeight="1" s="28">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>METADATOS DE PLANEACIÓN (Scrum)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="28">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>Complejidad</t>
+        </is>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="28">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="n"/>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="28">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>Sprint propuesto</t>
+        </is>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Agregada tras la revisión</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="26" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" s="28">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Terminado</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="26" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="C3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
@@ -5894,7 +6172,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6209,7 +6487,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -6259,7 +6536,6 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -6398,8 +6674,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -6465,7 +6741,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -6515,7 +6790,6 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -6650,8 +6924,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -6717,7 +6991,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="28">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -6767,7 +7040,6 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="26" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="28">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -6902,8 +7174,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -7152,8 +7424,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -7402,8 +7674,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>
@@ -7641,8 +7913,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:D6"/>

--- a/docs/Historias_Usuario.xlsx
+++ b/docs/Historias_Usuario.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" tabRatio="600" firstSheet="8" activeTab="8" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="600" firstSheet="14" activeTab="23" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Índice" sheetId="1" state="visible" r:id="rId1"/>
@@ -30,8 +30,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HU-20" sheetId="22" state="visible" r:id="rId22"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HU-21" sheetId="23" state="visible" r:id="rId23"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registro" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan_Iteraciones" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Firmar" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan_Iteraciones" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -222,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -292,12 +293,7 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -305,26 +301,39 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -699,88 +708,88 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="9" customWidth="1" style="28" min="1" max="1"/>
-    <col width="42" customWidth="1" style="28" min="2" max="2"/>
-    <col width="14" customWidth="1" style="28" min="3" max="3"/>
-    <col width="12" customWidth="1" style="28" min="4" max="4"/>
-    <col width="22" customWidth="1" style="28" min="5" max="5"/>
-    <col width="14" customWidth="1" style="28" min="6" max="7"/>
-    <col width="12" customWidth="1" style="28" min="8" max="8"/>
+    <col width="9" customWidth="1" style="32" min="1" max="1"/>
+    <col width="42" customWidth="1" style="32" min="2" max="2"/>
+    <col width="14" customWidth="1" style="32" min="3" max="3"/>
+    <col width="12" customWidth="1" style="32" min="4" max="4"/>
+    <col width="22" customWidth="1" style="32" min="5" max="5"/>
+    <col width="14" customWidth="1" style="32" min="6" max="7"/>
+    <col width="12" customWidth="1" style="32" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="28">
-      <c r="A1" s="27" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="32">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>SIGECOP — Historias de Usuario</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="39.9" customHeight="1" s="28">
-      <c r="A2" s="37" t="inlineStr">
+    <row r="2" ht="39.9" customHeight="1" s="32">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>Sistema de Gestión Técnico-Administrativa de Contratos de Obra Pública. 22 historias siguiendo el formato dictado por el profesor.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1" s="28">
-      <c r="A4" s="36" t="inlineStr">
+    <row r="4" ht="24" customHeight="1" s="32">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>Total historias</t>
         </is>
       </c>
-      <c r="B4" s="26" t="n"/>
-      <c r="C4" s="36" t="inlineStr">
+      <c r="B4" s="30" t="n"/>
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>Total user points</t>
         </is>
       </c>
-      <c r="D4" s="26" t="n"/>
-      <c r="E4" s="36" t="inlineStr">
+      <c r="D4" s="30" t="n"/>
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t>Total sprints planeados</t>
         </is>
       </c>
-      <c r="F4" s="26" t="n"/>
-      <c r="G4" s="36" t="inlineStr">
+      <c r="F4" s="30" t="n"/>
+      <c r="G4" s="29" t="inlineStr">
         <is>
           <t>Velocidad promedio del equipo</t>
         </is>
       </c>
-      <c r="H4" s="26" t="n"/>
-    </row>
-    <row r="5" ht="32.1" customHeight="1" s="28">
-      <c r="A5" s="38" t="n">
+      <c r="H4" s="30" t="n"/>
+    </row>
+    <row r="5" ht="32.1" customHeight="1" s="32">
+      <c r="A5" s="33" t="n">
         <v>22</v>
       </c>
-      <c r="B5" s="26" t="n"/>
-      <c r="C5" s="38" t="n">
-        <v>85</v>
-      </c>
-      <c r="D5" s="26" t="n"/>
-      <c r="E5" s="38" t="inlineStr">
+      <c r="B5" s="30" t="n"/>
+      <c r="C5" s="33" t="n">
+        <v>87</v>
+      </c>
+      <c r="D5" s="30" t="n"/>
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t>1-9</t>
         </is>
       </c>
-      <c r="F5" s="26" t="n"/>
-      <c r="G5" s="38" t="inlineStr">
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="33" t="inlineStr">
         <is>
           <t>9.4 pts/sprint</t>
         </is>
       </c>
-      <c r="H5" s="26" t="n"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1" s="28">
-      <c r="A8" s="39" t="inlineStr">
+      <c r="H5" s="30" t="n"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" s="32">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>Tabla resumen de las 22 historias</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1" s="28">
+    <row r="9" ht="30" customHeight="1" s="32">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>HU_ID</t>
@@ -822,7 +831,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="27.9" customHeight="1" s="28">
+    <row r="10" ht="27.9" customHeight="1" s="32">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>HU-00</t>
@@ -862,7 +871,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="27.9" customHeight="1" s="28">
+    <row r="11" ht="27.9" customHeight="1" s="32">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>HU-01</t>
@@ -902,7 +911,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="27.9" customHeight="1" s="28">
+    <row r="12" ht="27.9" customHeight="1" s="32">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>HU-02</t>
@@ -942,7 +951,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="27.9" customHeight="1" s="28">
+    <row r="13" ht="27.9" customHeight="1" s="32">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>HU-03</t>
@@ -982,7 +991,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="27.9" customHeight="1" s="28">
+    <row r="14" ht="27.9" customHeight="1" s="32">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>HU-04</t>
@@ -1022,7 +1031,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="27.9" customHeight="1" s="28">
+    <row r="15" ht="27.9" customHeight="1" s="32">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>HU-05</t>
@@ -1062,7 +1071,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="27.9" customHeight="1" s="28">
+    <row r="16" ht="27.9" customHeight="1" s="32">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>HU-06</t>
@@ -1102,7 +1111,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="27.9" customHeight="1" s="28">
+    <row r="17" ht="27.9" customHeight="1" s="32">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t>HU-07</t>
@@ -1142,7 +1151,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="27.9" customHeight="1" s="28">
+    <row r="18" ht="27.9" customHeight="1" s="32">
       <c r="A18" s="3" t="inlineStr">
         <is>
           <t>HU-08</t>
@@ -1182,7 +1191,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="27.9" customHeight="1" s="28">
+    <row r="19" ht="27.9" customHeight="1" s="32">
       <c r="A19" s="3" t="inlineStr">
         <is>
           <t>HU-09</t>
@@ -1222,7 +1231,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="27.9" customHeight="1" s="28">
+    <row r="20" ht="27.9" customHeight="1" s="32">
       <c r="A20" s="3" t="inlineStr">
         <is>
           <t>HU-10</t>
@@ -1262,7 +1271,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="27.9" customHeight="1" s="28">
+    <row r="21" ht="27.9" customHeight="1" s="32">
       <c r="A21" s="3" t="inlineStr">
         <is>
           <t>HU-11</t>
@@ -1302,7 +1311,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="27.9" customHeight="1" s="28">
+    <row r="22" ht="27.9" customHeight="1" s="32">
       <c r="A22" s="3" t="inlineStr">
         <is>
           <t>HU-12</t>
@@ -1342,7 +1351,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="27.9" customHeight="1" s="28">
+    <row r="23" ht="27.9" customHeight="1" s="32">
       <c r="A23" s="3" t="inlineStr">
         <is>
           <t>HU-13</t>
@@ -1382,7 +1391,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="27.9" customHeight="1" s="28">
+    <row r="24" ht="27.9" customHeight="1" s="32">
       <c r="A24" s="3" t="inlineStr">
         <is>
           <t>HU-14</t>
@@ -1422,7 +1431,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="27.9" customHeight="1" s="28">
+    <row r="25" ht="27.9" customHeight="1" s="32">
       <c r="A25" s="3" t="inlineStr">
         <is>
           <t>HU-15</t>
@@ -1462,7 +1471,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="27.9" customHeight="1" s="28">
+    <row r="26" ht="27.9" customHeight="1" s="32">
       <c r="A26" s="3" t="inlineStr">
         <is>
           <t>HU-16</t>
@@ -1502,7 +1511,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="27.9" customHeight="1" s="28">
+    <row r="27" ht="27.9" customHeight="1" s="32">
       <c r="A27" s="3" t="inlineStr">
         <is>
           <t>HU-17</t>
@@ -1542,7 +1551,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="27.9" customHeight="1" s="28">
+    <row r="28" ht="27.9" customHeight="1" s="32">
       <c r="A28" s="3" t="inlineStr">
         <is>
           <t>HU-18</t>
@@ -1582,7 +1591,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="27.9" customHeight="1" s="28">
+    <row r="29" ht="27.9" customHeight="1" s="32">
       <c r="A29" s="3" t="inlineStr">
         <is>
           <t>HU-19</t>
@@ -1622,7 +1631,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="27.9" customHeight="1" s="28">
+    <row r="30" ht="27.9" customHeight="1" s="32">
       <c r="A30" s="3" t="inlineStr">
         <is>
           <t>HU-20</t>
@@ -1662,7 +1671,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="27.9" customHeight="1" s="28">
+    <row r="31" ht="27.9" customHeight="1" s="32">
       <c r="A31" s="3" t="inlineStr">
         <is>
           <t>HU-21</t>
@@ -1702,7 +1711,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="27.9" customHeight="1" s="28">
+    <row r="32" ht="27.9" customHeight="1" s="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Registro</t>
@@ -1737,6 +1746,46 @@
       <c r="H32" s="5" t="inlineStr">
         <is>
           <t>Agregada tras la revisión</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Por Firmar</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Firma de aperturas de bitácora pendientes</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>SRV-03-05</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>MOD-03</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Residente, superintendente o supervisión</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
         </is>
       </c>
     </row>
@@ -1767,143 +1816,143 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="28" min="1" max="1"/>
-    <col width="50" customWidth="1" style="28" min="2" max="2"/>
-    <col width="25" customWidth="1" style="28" min="3" max="3"/>
-    <col width="18" customWidth="1" style="28" min="4" max="4"/>
+    <col width="16" customWidth="1" style="32" min="1" max="1"/>
+    <col width="50" customWidth="1" style="32" min="2" max="2"/>
+    <col width="25" customWidth="1" style="32" min="3" max="3"/>
+    <col width="18" customWidth="1" style="32" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="27" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="32">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>HU-06 · Registro de trabajos terminados por periodo</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="32" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="32">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-02-02</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="43" t="inlineStr">
         <is>
           <t>Módulo: MOD-02</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="32" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="32">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>Sprint sugerido: 7</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="29" t="inlineStr">
+    <row r="5" ht="24" customHeight="1" s="32">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.9" customHeight="1" s="28">
+    <row r="6" ht="27.9" customHeight="1" s="32">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>contratista</t>
         </is>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="26" t="n"/>
-    </row>
-    <row r="7" ht="29.1" customHeight="1" s="28">
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="29.1" customHeight="1" s="32">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>registrar por periodo las cantidades terminadas por cada concepto del catálogo, vinculando cada registro a su nota de bitácora del periodo, viendo el avance acumulado contra lo contratado en vivo</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="26" t="n"/>
-    </row>
-    <row r="8" ht="27.9" customHeight="1" s="28">
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="30" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="32">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>alimentar la integración de la estimación con el avance real y dejar respaldo documental de cada cantidad reportada</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="26" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="30" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" s="32">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="28">
+    <row r="12" ht="32.1" customHeight="1" s="32">
       <c r="A12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>Cada cantidad capturada queda ligada al concepto del catálogo correspondiente y a una nota de bitácora del periodo (tipo entrega de obra o avance).</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n"/>
+      <c r="C12" s="30" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="28">
+    <row r="13" ht="32.1" customHeight="1" s="32">
       <c r="A13" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>El sistema acumula el avance ejecutado por concepto y muestra el porcentaje de avance contra lo contratado en vivo, periodo a periodo.</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n"/>
+      <c r="C13" s="30" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
@@ -1920,53 +1969,53 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="28"/>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="29" t="inlineStr">
+    <row r="15" ht="24" customHeight="1" s="32"/>
+    <row r="16" ht="24" customHeight="1" s="32">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" s="28">
+    <row r="17" ht="24" customHeight="1" s="32">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B17" s="42" t="inlineStr">
+      <c r="B17" s="46" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="28">
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="32">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B18" s="42" t="n">
+      <c r="B18" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="26" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="28">
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="32">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>Sprint 7</t>
         </is>
       </c>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="26" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="30" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
@@ -1974,13 +2023,13 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="26" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -2017,143 +2066,143 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="28" min="1" max="1"/>
-    <col width="50" customWidth="1" style="28" min="2" max="2"/>
-    <col width="25" customWidth="1" style="28" min="3" max="3"/>
-    <col width="18" customWidth="1" style="28" min="4" max="4"/>
+    <col width="16" customWidth="1" style="32" min="1" max="1"/>
+    <col width="50" customWidth="1" style="32" min="2" max="2"/>
+    <col width="25" customWidth="1" style="32" min="3" max="3"/>
+    <col width="18" customWidth="1" style="32" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="27" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="32">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>HU-07 · Configuración de alertas de atraso por concepto</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="32" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="32">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-02-03</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="43" t="inlineStr">
         <is>
           <t>Módulo: MOD-02</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="32" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="32">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>Sprint sugerido: 6</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="29" t="inlineStr">
+    <row r="5" ht="24" customHeight="1" s="32">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.9" customHeight="1" s="28">
+    <row r="6" ht="27.9" customHeight="1" s="32">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="26" t="n"/>
-    </row>
-    <row r="7" ht="29.1" customHeight="1" s="28">
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="29.1" customHeight="1" s="32">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>configurar qué conceptos del contrato quiero vigilar, el umbral de atraso a partir del cual quiero ser notificado y el canal de notificación (sistema o correo)</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="26" t="n"/>
-    </row>
-    <row r="8" ht="27.9" customHeight="1" s="28">
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="30" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="32">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>recibir alertas solo de lo que decidí vigilar, sin saturación de notificaciones</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="26" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="30" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" s="32">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="28">
+    <row r="12" ht="32.1" customHeight="1" s="32">
       <c r="A12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>Se pueden crear, pausar y eliminar alertas por concepto sin alterar las del resto.</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n"/>
+      <c r="C12" s="30" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="28">
+    <row r="13" ht="32.1" customHeight="1" s="32">
       <c r="A13" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>La alerta solo dispara cuando el avance real es menor al umbral configurado por el usuario.</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n"/>
+      <c r="C13" s="30" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
@@ -2170,53 +2219,53 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="28"/>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="29" t="inlineStr">
+    <row r="15" ht="24" customHeight="1" s="32"/>
+    <row r="16" ht="24" customHeight="1" s="32">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" s="28">
+    <row r="17" ht="24" customHeight="1" s="32">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B17" s="35" t="inlineStr">
+      <c r="B17" s="39" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="28">
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="32">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
+      <c r="B18" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="26" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="28">
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="32">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>Sprint 6</t>
         </is>
       </c>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="26" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="30" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
@@ -2224,13 +2273,13 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="26" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -2267,225 +2316,225 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="28" min="1" max="1"/>
-    <col width="50" customWidth="1" style="28" min="2" max="2"/>
-    <col width="25" customWidth="1" style="28" min="3" max="3"/>
-    <col width="18" customWidth="1" style="28" min="4" max="4"/>
+    <col width="16" customWidth="1" style="32" min="1" max="1"/>
+    <col width="50" customWidth="1" style="32" min="2" max="2"/>
+    <col width="25" customWidth="1" style="32" min="3" max="3"/>
+    <col width="18" customWidth="1" style="32" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="27" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="32">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>HU-09 · Emisión y respuesta de notas tipificadas con firma</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="32" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="32">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-03-02</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="43" t="inlineStr">
         <is>
           <t>Módulo: MOD-03</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="32" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="32">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>Sprint sugerido: 2</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="29" t="inlineStr">
+    <row r="5" ht="24" customHeight="1" s="32">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.9" customHeight="1" s="28">
+    <row r="6" ht="27.9" customHeight="1" s="32">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>residente, supervisión o contratista (según rol autorizado)</t>
         </is>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="26" t="n"/>
-    </row>
-    <row r="7" ht="30.9" customHeight="1" s="28">
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="30.9" customHeight="1" s="32">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>emitir notas en la bitácora del contrato —el residente autoriza y aprueba, el superintendente solicita y avisa, y la supervisión registra el avance—, conforme a los arts. 122 y 125 RLOPSRM, con folio correlativo automático y firma conjunta de los tres participantes</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="26" t="n"/>
-    </row>
-    <row r="8" ht="27.9" customHeight="1" s="28">
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="30" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="32">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>documentar formalmente los eventos del contrato de manera trazable e inmutable para auditoría</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="26" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="30" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" s="32">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="28">
+    <row r="12" ht="32.1" customHeight="1" s="32">
       <c r="A12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>Aparecen los tipos de nota que corresponden al rol del usuario, pudiendo incorporar también otro tipo de nota para eventos no tipificados.</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n"/>
+      <c r="C12" s="30" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="28">
+    <row r="13" ht="32.1" customHeight="1" s="32">
       <c r="A13" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>Una nota firmada queda inmutable; las correcciones se hacen generando una nota vinculada (formato «dice / debe decir»), sin alterar la original.</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n"/>
+      <c r="C13" s="30" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32.1" customHeight="1" s="28">
+    <row r="14" ht="32.1" customHeight="1" s="32">
       <c r="A14" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="40" t="inlineStr">
         <is>
           <t>Cada nota queda registrada con folio correlativo, fecha, firma de los tres participantes y vínculo opcional a nota previa.</t>
         </is>
       </c>
-      <c r="C14" s="26" t="n"/>
+      <c r="C14" s="30" t="n"/>
       <c r="D14" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="29" t="inlineStr">
+    <row r="16" ht="24" customHeight="1" s="32">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" s="28">
+    <row r="17" ht="24" customHeight="1" s="32">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B17" s="40" t="inlineStr">
+      <c r="B17" s="44" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="28">
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="32">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B18" s="40" t="n">
+      <c r="B18" s="44" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="26" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="28">
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="32">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="26" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" s="28">
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="30" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" s="32">
       <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="26" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -2523,143 +2572,143 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="28" min="1" max="1"/>
-    <col width="50" customWidth="1" style="28" min="2" max="2"/>
-    <col width="25" customWidth="1" style="28" min="3" max="3"/>
-    <col width="18" customWidth="1" style="28" min="4" max="4"/>
+    <col width="16" customWidth="1" style="32" min="1" max="1"/>
+    <col width="50" customWidth="1" style="32" min="2" max="2"/>
+    <col width="25" customWidth="1" style="32" min="3" max="3"/>
+    <col width="18" customWidth="1" style="32" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="27" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="32">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>HU-11 · Registro de minutas, agenda de visitas y consulta de acuerdos</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="32" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="32">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-03-04</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="43" t="inlineStr">
         <is>
           <t>Módulo: MOD-03</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="32" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="32">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>Sprint sugerido: 7</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="29" t="inlineStr">
+    <row r="5" ht="24" customHeight="1" s="32">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.9" customHeight="1" s="28">
+    <row r="6" ht="27.9" customHeight="1" s="32">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="26" t="n"/>
-    </row>
-    <row r="7" ht="27.9" customHeight="1" s="28">
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="27.9" customHeight="1" s="32">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>subir el PDF de las minutas de reuniones del contrato con sus metadatos, agendar visitas e inspecciones de campo, y consultar los acuerdos asentados, pudiendo adjuntar una minuta como referencia en una nota de bitácora</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="26" t="n"/>
-    </row>
-    <row r="8" ht="27.9" customHeight="1" s="28">
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="30" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="32">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>tener concentradas todas las reuniones, visitas y compromisos del contrato en un solo lugar para consulta</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="26" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="30" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" s="32">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="28">
+    <row r="12" ht="32.1" customHeight="1" s="32">
       <c r="A12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>Las minutas (con su PDF y metadatos) y las visitas registradas son visibles para los usuarios autorizados del contrato.</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n"/>
+      <c r="C12" s="30" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="28">
+    <row r="13" ht="32.1" customHeight="1" s="32">
       <c r="A13" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>Se pueden consultar los acuerdos y compromisos derivados, filtrados por contrato y periodo.</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n"/>
+      <c r="C13" s="30" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
@@ -2676,53 +2725,53 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="28"/>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="29" t="inlineStr">
+    <row r="15" ht="24" customHeight="1" s="32"/>
+    <row r="16" ht="24" customHeight="1" s="32">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" s="28">
+    <row r="17" ht="24" customHeight="1" s="32">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B17" s="42" t="inlineStr">
+      <c r="B17" s="46" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="28">
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="32">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B18" s="42" t="n">
+      <c r="B18" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="26" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="28">
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="32">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>Sprint 7</t>
         </is>
       </c>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="26" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="30" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
@@ -2730,13 +2779,13 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="26" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -2773,225 +2822,225 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="28" min="1" max="1"/>
-    <col width="50" customWidth="1" style="28" min="2" max="2"/>
-    <col width="25" customWidth="1" style="28" min="3" max="3"/>
-    <col width="18" customWidth="1" style="28" min="4" max="4"/>
+    <col width="16" customWidth="1" style="32" min="1" max="1"/>
+    <col width="50" customWidth="1" style="32" min="2" max="2"/>
+    <col width="25" customWidth="1" style="32" min="3" max="3"/>
+    <col width="18" customWidth="1" style="32" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="27" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="32">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>HU-12 · Apertura del periodo e integración de la estimación</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="32" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="32">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-04-01</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="43" t="inlineStr">
         <is>
           <t>Módulo: MOD-04</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="32" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="32">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>Sprint sugerido: 3</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="29" t="inlineStr">
+    <row r="5" ht="24" customHeight="1" s="32">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.9" customHeight="1" s="28">
+    <row r="6" ht="27.9" customHeight="1" s="32">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>contratista</t>
         </is>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="26" t="n"/>
-    </row>
-    <row r="7" ht="36" customHeight="1" s="28">
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="36" customHeight="1" s="32">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>abrir el periodo de estimación e integrar como un solo bloque la carátula (con anticipo amortizado, retenciones del 5 al millar y deductivas), los números generadores, el registro fotográfico, los soportes y las notas de bitácora del periodo seleccionadas desde el buscador de bitácora</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="26" t="n"/>
-    </row>
-    <row r="8" ht="27.9" customHeight="1" s="28">
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="30" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="32">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>presentar la estimación como un expediente completo conforme al art. 132 RLOPSRM para la revisión de supervisión y residencia</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="26" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="30" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" s="32">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="33" customHeight="1" s="28">
+    <row r="12" ht="33" customHeight="1" s="32">
       <c r="A12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>La estimación se guarda como una sola entidad que contiene carátula, generadores, registro fotográfico, soportes y notas vinculadas seleccionadas del buscador de bitácora.</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n"/>
+      <c r="C12" s="30" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="35.1" customHeight="1" s="28">
+    <row r="13" ht="35.1" customHeight="1" s="32">
       <c r="A13" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>La carátula calcula automáticamente anticipo amortizado, retenciones legales (5 al millar, art. 191 LFD) y deductivas por penalizaciones según el contrato.</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n"/>
+      <c r="C13" s="30" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32.1" customHeight="1" s="28">
+    <row r="14" ht="32.1" customHeight="1" s="32">
       <c r="A14" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="40" t="inlineStr">
         <is>
           <t>El sistema bloquea la integración cuando una cantidad por concepto excede la cantidad contratada en el catálogo (art. 118 RLOPSRM).</t>
         </is>
       </c>
-      <c r="C14" s="26" t="n"/>
+      <c r="C14" s="30" t="n"/>
       <c r="D14" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="29" t="inlineStr">
+    <row r="16" ht="24" customHeight="1" s="32">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" s="28">
+    <row r="17" ht="24" customHeight="1" s="32">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B17" s="40" t="inlineStr">
+      <c r="B17" s="44" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="28">
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="32">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B18" s="40" t="n">
+      <c r="B18" s="44" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="26" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="28">
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="32">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="26" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" s="28">
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="30" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" s="32">
       <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="26" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -3029,143 +3078,143 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="28" min="1" max="1"/>
-    <col width="50" customWidth="1" style="28" min="2" max="2"/>
-    <col width="25" customWidth="1" style="28" min="3" max="3"/>
-    <col width="18" customWidth="1" style="28" min="4" max="4"/>
+    <col width="16" customWidth="1" style="32" min="1" max="1"/>
+    <col width="50" customWidth="1" style="32" min="2" max="2"/>
+    <col width="25" customWidth="1" style="32" min="3" max="3"/>
+    <col width="18" customWidth="1" style="32" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="27" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="32">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>HU-13 · Envío de la estimación</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="32" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="32">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-04-02</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="43" t="inlineStr">
         <is>
           <t>Módulo: MOD-04</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="32" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="32">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>Sprint sugerido: 8</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="29" t="inlineStr">
+    <row r="5" ht="24" customHeight="1" s="32">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.9" customHeight="1" s="28">
+    <row r="6" ht="27.9" customHeight="1" s="32">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>contratista</t>
         </is>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="26" t="n"/>
-    </row>
-    <row r="7" ht="27.9" customHeight="1" s="28">
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="27.9" customHeight="1" s="32">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>enviar formalmente una estimación integrada para que arranque el plazo de revisión del art. 54 LOPSRM, dentro de los 6 días naturales del periodo de presentación</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="26" t="n"/>
-    </row>
-    <row r="8" ht="27.9" customHeight="1" s="28">
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="30" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="32">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>dejar evidencia del momento exacto de entrega y disparar el plazo de revisión de la supervisión y residencia</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="26" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="30" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" s="32">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="28">
+    <row r="12" ht="32.1" customHeight="1" s="32">
       <c r="A12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>Al enviar la estimación quedan registradas la fecha y hora exacta de recepción, y queda notificación formal a residencia y supervisión.</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n"/>
+      <c r="C12" s="30" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="28">
+    <row r="13" ht="32.1" customHeight="1" s="32">
       <c r="A13" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>El botón Enviar se deshabilita cuando se vencen los 6 días naturales del periodo de presentación (art. 54 LOPSRM).</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n"/>
+      <c r="C13" s="30" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
@@ -3182,53 +3231,53 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="28"/>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="29" t="inlineStr">
+    <row r="15" ht="24" customHeight="1" s="32"/>
+    <row r="16" ht="24" customHeight="1" s="32">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" s="28">
+    <row r="17" ht="24" customHeight="1" s="32">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B17" s="42" t="inlineStr">
+      <c r="B17" s="46" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="28">
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="32">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B18" s="42" t="n">
+      <c r="B18" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="26" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="28">
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="32">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>Sprint 8</t>
         </is>
       </c>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="26" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="30" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
@@ -3236,13 +3285,13 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="26" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -3279,143 +3328,143 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="28" min="1" max="1"/>
-    <col width="50" customWidth="1" style="28" min="2" max="2"/>
-    <col width="25" customWidth="1" style="28" min="3" max="3"/>
-    <col width="18" customWidth="1" style="28" min="4" max="4"/>
+    <col width="16" customWidth="1" style="32" min="1" max="1"/>
+    <col width="50" customWidth="1" style="32" min="2" max="2"/>
+    <col width="25" customWidth="1" style="32" min="3" max="3"/>
+    <col width="18" customWidth="1" style="32" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="27" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="32">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>HU-14 · Historial de estimaciones del contrato</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="32" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="32">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-04-03</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="43" t="inlineStr">
         <is>
           <t>Módulo: MOD-04</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="32" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="32">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>Sprint sugerido: 5</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="29" t="inlineStr">
+    <row r="5" ht="24" customHeight="1" s="32">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.9" customHeight="1" s="28">
+    <row r="6" ht="27.9" customHeight="1" s="32">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="26" t="n"/>
-    </row>
-    <row r="7" ht="29.1" customHeight="1" s="28">
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="29.1" customHeight="1" s="32">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>consultar todas las estimaciones del contrato a lo largo del tiempo con sus estados (aceptadas, rechazadas, en proceso) y filtros por periodo, pudiendo abrir cada una para ver su expediente</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="26" t="n"/>
-    </row>
-    <row r="8" ht="27.9" customHeight="1" s="28">
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="30" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="32">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>ver la trazabilidad completa del ciclo de cobro del contrato, incluyendo versiones rechazadas, conforme a los tipos de estimación reconocidos en el art. 130 RLOPSRM</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="26" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="30" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" s="32">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="28">
+    <row r="12" ht="32.1" customHeight="1" s="32">
       <c r="A12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>El historial muestra todas las estimaciones del contrato en orden cronológico, incluyendo las versiones rechazadas.</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n"/>
+      <c r="C12" s="30" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="28">
+    <row r="13" ht="32.1" customHeight="1" s="32">
       <c r="A13" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>Los filtros permiten consultar por periodo, estado o ambos combinados (lógica Y).</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n"/>
+      <c r="C13" s="30" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
@@ -3432,53 +3481,53 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="28"/>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="29" t="inlineStr">
+    <row r="15" ht="24" customHeight="1" s="32"/>
+    <row r="16" ht="24" customHeight="1" s="32">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" s="28">
+    <row r="17" ht="24" customHeight="1" s="32">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B17" s="35" t="inlineStr">
+      <c r="B17" s="39" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="28">
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="32">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
+      <c r="B18" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="26" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="28">
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="32">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="26" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="30" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
@@ -3486,13 +3535,13 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="26" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -3529,225 +3578,225 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="28" min="1" max="1"/>
-    <col width="50" customWidth="1" style="28" min="2" max="2"/>
-    <col width="25" customWidth="1" style="28" min="3" max="3"/>
-    <col width="18" customWidth="1" style="28" min="4" max="4"/>
+    <col width="16" customWidth="1" style="32" min="1" max="1"/>
+    <col width="50" customWidth="1" style="32" min="2" max="2"/>
+    <col width="25" customWidth="1" style="32" min="3" max="3"/>
+    <col width="18" customWidth="1" style="32" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="27" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="32">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>HU-15 · Recepción, revisión técnica y autorización de la estimación</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="32" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="32">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-05-01</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="43" t="inlineStr">
         <is>
           <t>Módulo: MOD-05</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="32" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="32">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>Sprint sugerido: 4</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="29" t="inlineStr">
+    <row r="5" ht="24" customHeight="1" s="32">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.9" customHeight="1" s="28">
+    <row r="6" ht="27.9" customHeight="1" s="32">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>supervisión y residencia (revisión secuencial)</t>
         </is>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="26" t="n"/>
-    </row>
-    <row r="7" ht="36.9" customHeight="1" s="28">
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="36.9" customHeight="1" s="32">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>revisar la estimación recibida sección por sección (carátula, números generadores, registro fotográfico, soportes, notas), registrar observaciones con tipo y severidad, turnar de supervisión a residencia y al final autorizar o rechazar</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="26" t="n"/>
-    </row>
-    <row r="8" ht="27.9" customHeight="1" s="28">
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="30" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="32">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>decidir sobre la estimación con evidencia completa, en ejercicio de la responsabilidad de la residencia sobre la revisión y aprobación (art. 53 LOPSRM), y dentro de los plazos de los arts. 54 LOPSRM y 133 RLOPSRM</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="26" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="30" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" s="32">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="33" customHeight="1" s="28">
+    <row r="12" ht="33" customHeight="1" s="32">
       <c r="A12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>La revisión permite ir sección por sección (carátula, generadores, registro fotográfico, soportes y notas) y registrar observaciones con tipo y severidad por concepto.</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n"/>
+      <c r="C12" s="30" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="28">
+    <row r="13" ht="32.1" customHeight="1" s="32">
       <c r="A13" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>La autorización queda condicionada al turnado secuencial: primero supervisión, luego residencia; residencia no puede resolver antes del turnado.</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n"/>
+      <c r="C13" s="30" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="33" customHeight="1" s="28">
+    <row r="14" ht="33" customHeight="1" s="32">
       <c r="A14" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="40" t="inlineStr">
         <is>
           <t>El sistema controla el plazo de 15 días naturales de revisión conforme al art. 54 LOPSRM mediante un semáforo basado en la fecha real de recepción.</t>
         </is>
       </c>
-      <c r="C14" s="26" t="n"/>
+      <c r="C14" s="30" t="n"/>
       <c r="D14" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="29" t="inlineStr">
+    <row r="16" ht="24" customHeight="1" s="32">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" s="28">
+    <row r="17" ht="24" customHeight="1" s="32">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B17" s="40" t="inlineStr">
+      <c r="B17" s="44" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="28">
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="32">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B18" s="40" t="n">
+      <c r="B18" s="44" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="26" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="28">
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="32">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="26" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" s="28">
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="30" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" s="32">
       <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="26" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -3785,143 +3834,143 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="28" min="1" max="1"/>
-    <col width="50" customWidth="1" style="28" min="2" max="2"/>
-    <col width="25" customWidth="1" style="28" min="3" max="3"/>
-    <col width="18" customWidth="1" style="28" min="4" max="4"/>
+    <col width="16" customWidth="1" style="32" min="1" max="1"/>
+    <col width="50" customWidth="1" style="32" min="2" max="2"/>
+    <col width="25" customWidth="1" style="32" min="3" max="3"/>
+    <col width="18" customWidth="1" style="32" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="27" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="32">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>HU-16 · Reingreso de estimación tras rechazo</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="32" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="32">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-05-02</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="43" t="inlineStr">
         <is>
           <t>Módulo: MOD-05</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="32" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="32">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>Sprint sugerido: 8</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="29" t="inlineStr">
+    <row r="5" ht="24" customHeight="1" s="32">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.9" customHeight="1" s="28">
+    <row r="6" ht="27.9" customHeight="1" s="32">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>contratista</t>
         </is>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="26" t="n"/>
-    </row>
-    <row r="7" ht="27.9" customHeight="1" s="28">
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="27.9" customHeight="1" s="32">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>presentar una nueva versión completa de la estimación del mismo periodo después de un rechazo, atendiendo las observaciones recibidas</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="26" t="n"/>
-    </row>
-    <row r="8" ht="27.9" customHeight="1" s="28">
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="30" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="32">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>que la estimación sea revisada nuevamente como un bloque completo sin perder trazabilidad de la versión anterior</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="26" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="30" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" s="32">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="28">
+    <row r="12" ht="32.1" customHeight="1" s="32">
       <c r="A12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>La nueva versión se trata como bloque completo independiente y la versión rechazada queda como histórico vinculado.</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n"/>
+      <c r="C12" s="30" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="28">
+    <row r="13" ht="32.1" customHeight="1" s="32">
       <c r="A13" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>El listado de observaciones de la versión rechazada está disponible para descarga en PDF o Excel.</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n"/>
+      <c r="C13" s="30" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
@@ -3938,53 +3987,53 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="28"/>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="29" t="inlineStr">
+    <row r="15" ht="24" customHeight="1" s="32"/>
+    <row r="16" ht="24" customHeight="1" s="32">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" s="28">
+    <row r="17" ht="24" customHeight="1" s="32">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B17" s="42" t="inlineStr">
+      <c r="B17" s="46" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="28">
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="32">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B18" s="42" t="n">
+      <c r="B18" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="26" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="28">
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="32">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>Sprint 8</t>
         </is>
       </c>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="26" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="30" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
@@ -3992,13 +4041,13 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="26" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -4035,143 +4084,143 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="28" min="1" max="1"/>
-    <col width="50" customWidth="1" style="28" min="2" max="2"/>
-    <col width="25" customWidth="1" style="28" min="3" max="3"/>
-    <col width="18" customWidth="1" style="28" min="4" max="4"/>
+    <col width="16" customWidth="1" style="32" min="1" max="1"/>
+    <col width="50" customWidth="1" style="32" min="2" max="2"/>
+    <col width="25" customWidth="1" style="32" min="3" max="3"/>
+    <col width="18" customWidth="1" style="32" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="27" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="32">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>HU-17 · Tablero de estimaciones aceptadas y en proceso</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="32" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="32">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-06-01</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="43" t="inlineStr">
         <is>
           <t>Módulo: MOD-06</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="32" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="32">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>Sprint sugerido: 8</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="29" t="inlineStr">
+    <row r="5" ht="24" customHeight="1" s="32">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.9" customHeight="1" s="28">
+    <row r="6" ht="27.9" customHeight="1" s="32">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="26" t="n"/>
-    </row>
-    <row r="7" ht="35.1" customHeight="1" s="28">
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="35.1" customHeight="1" s="32">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>ver en un tablero las estimaciones del contrato aceptadas y en proceso (presentada, en revisión, autorizada, en pago, pagada), con su línea de tiempo, indicadores y pendientes por solventar</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="26" t="n"/>
-    </row>
-    <row r="8" ht="27.9" customHeight="1" s="28">
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="30" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="32">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>saber qué estimación está en qué estado y qué requiere mi acción inmediata</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="26" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="30" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" s="32">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="28">
+    <row r="12" ht="32.1" customHeight="1" s="32">
       <c r="A12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>El tablero muestra solo estimaciones aceptadas y en proceso (no las rechazadas, que viven en el historial).</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n"/>
+      <c r="C12" s="30" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="28">
+    <row r="13" ht="32.1" customHeight="1" s="32">
       <c r="A13" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>Cada estimación muestra su línea de tiempo de estado, y el tablero da indicadores agregados del contrato (avance, montos, días en cada estado).</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n"/>
+      <c r="C13" s="30" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
@@ -4188,53 +4237,53 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="28"/>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="29" t="inlineStr">
+    <row r="15" ht="24" customHeight="1" s="32"/>
+    <row r="16" ht="24" customHeight="1" s="32">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" s="28">
+    <row r="17" ht="24" customHeight="1" s="32">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B17" s="42" t="inlineStr">
+      <c r="B17" s="46" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="28">
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="32">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B18" s="42" t="n">
+      <c r="B18" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="26" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="28">
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="32">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>Sprint 8</t>
         </is>
       </c>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="26" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="30" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
@@ -4242,13 +4291,13 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="26" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -4285,165 +4334,165 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="28" min="1" max="1"/>
-    <col width="50" customWidth="1" style="28" min="2" max="2"/>
-    <col width="25" customWidth="1" style="28" min="3" max="3"/>
-    <col width="18" customWidth="1" style="28" min="4" max="4"/>
+    <col width="16" customWidth="1" style="32" min="1" max="1"/>
+    <col width="50" customWidth="1" style="32" min="2" max="2"/>
+    <col width="25" customWidth="1" style="32" min="3" max="3"/>
+    <col width="18" customWidth="1" style="32" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="27" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="32">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>HU-00 · Inicio de sesión por rol</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="32" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="32">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Servicio implementado: —</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="43" t="inlineStr">
         <is>
           <t>Módulo: —</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="32" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="32">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>Sprint sugerido: 1</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="29" t="inlineStr">
+    <row r="5" ht="24" customHeight="1" s="32">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.9" customHeight="1" s="28">
+    <row r="6" ht="27.9" customHeight="1" s="32">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>usuario del sistema (residente, contratista, supervisión, dependencia o finanzas)</t>
         </is>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="26" t="n"/>
-    </row>
-    <row r="7" ht="69" customHeight="1" s="28">
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="69" customHeight="1" s="32">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>autenticarme con mi usuario y contraseña, sin tener que indicar mi rol explícitamente, para que el sistema reconozca internamente quién soy y me muestre únicamente las funciones que me corresponden</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="26" t="n"/>
-    </row>
-    <row r="8" ht="27.9" customHeight="1" s="28">
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="30" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="32">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>proteger la información del contrato y que cada acción registrada quede asociada al usuario que la ejecuta</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="26" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="30" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" s="32">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="28">
+    <row r="12" ht="32.1" customHeight="1" s="32">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>El sistema valida usuario y contraseña, bloquea el acceso cuando son inválidos y no permite continuar si los campos usuario o contraseña están vacíos.</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n"/>
+      <c r="C12" s="30" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="28">
+    <row r="13" ht="32.1" customHeight="1" s="32">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>El sistema deduce el rol del usuario a partir de su identificador, sin que este lo seleccione, y muestra únicamente las pantallas y opciones que corresponden a ese rol.</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n"/>
+      <c r="C13" s="30" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32.1" customHeight="1" s="28">
+    <row r="14" ht="32.1" customHeight="1" s="32">
       <c r="A14" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="40" t="inlineStr">
         <is>
           <t>Cada acción registrada por el usuario queda asociada a su nombre y fecha/hora en el sistema.</t>
         </is>
       </c>
-      <c r="C14" s="26" t="n"/>
+      <c r="C14" s="30" t="n"/>
       <c r="D14" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
@@ -4452,68 +4501,68 @@
     </row>
     <row r="15">
       <c r="A15" s="13" t="n"/>
-      <c r="B15" s="25" t="n"/>
-    </row>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="29" t="inlineStr">
+      <c r="B15" s="40" t="n"/>
+    </row>
+    <row r="16" ht="24" customHeight="1" s="32">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" s="28">
+    <row r="17" ht="24" customHeight="1" s="32">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B17" s="35" t="inlineStr">
+      <c r="B17" s="39" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="28">
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="32">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
+      <c r="B18" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="26" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="28">
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="32">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="26" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" s="28">
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="30" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" s="32">
       <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>Terminado</t>
         </is>
       </c>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="26" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -4551,143 +4600,143 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="28" min="1" max="1"/>
-    <col width="50" customWidth="1" style="28" min="2" max="2"/>
-    <col width="25" customWidth="1" style="28" min="3" max="3"/>
-    <col width="18" customWidth="1" style="28" min="4" max="4"/>
+    <col width="16" customWidth="1" style="32" min="1" max="1"/>
+    <col width="50" customWidth="1" style="32" min="2" max="2"/>
+    <col width="25" customWidth="1" style="32" min="3" max="3"/>
+    <col width="18" customWidth="1" style="32" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="27" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="32">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>HU-18 · Vista ejecutiva del portafolio con semáforos</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="32" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="32">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-06-02</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="43" t="inlineStr">
         <is>
           <t>Módulo: MOD-06</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="32" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="32">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>Sprint sugerido: 9</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="29" t="inlineStr">
+    <row r="5" ht="24" customHeight="1" s="32">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.9" customHeight="1" s="28">
+    <row r="6" ht="27.9" customHeight="1" s="32">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>dependencia</t>
         </is>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="26" t="n"/>
-    </row>
-    <row r="7" ht="32.1" customHeight="1" s="28">
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="32.1" customHeight="1" s="32">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>ver mis contratos asignados como una lista con semáforo de tres colores (verde, ámbar, rojo) según avance físico, atrasos y pendientes, con drill-down al detalle del contrato</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="26" t="n"/>
-    </row>
-    <row r="8" ht="27.9" customHeight="1" s="28">
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="30" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="32">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>tomar decisiones ejecutivas sobre cuáles contratos requieren mi atención</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="26" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="30" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" s="32">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="28">
+    <row r="12" ht="32.1" customHeight="1" s="32">
       <c r="A12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>Cada contrato del portafolio muestra un semáforo de color calculado a partir de tres factores: avance físico vs programado, atrasos en plazos legales y pendientes sin atender.</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n"/>
+      <c r="C12" s="30" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="28">
+    <row r="13" ht="32.1" customHeight="1" s="32">
       <c r="A13" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>Al hacer doble clic sobre un contrato se abre su detalle con indicadores físicos, financieros, atrasos y penalizaciones.</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n"/>
+      <c r="C13" s="30" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
@@ -4704,53 +4753,53 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="28"/>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="29" t="inlineStr">
+    <row r="15" ht="24" customHeight="1" s="32"/>
+    <row r="16" ht="24" customHeight="1" s="32">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" s="28">
+    <row r="17" ht="24" customHeight="1" s="32">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B17" s="42" t="inlineStr">
+      <c r="B17" s="46" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="28">
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="32">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B18" s="41" t="n">
+      <c r="B18" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="26" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="28">
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="32">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>Sprint 9</t>
         </is>
       </c>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="26" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="30" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
@@ -4758,13 +4807,13 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="26" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -4801,209 +4850,209 @@
   <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="28" min="1" max="1"/>
-    <col width="50" customWidth="1" style="28" min="2" max="2"/>
-    <col width="25" customWidth="1" style="28" min="3" max="3"/>
-    <col width="18" customWidth="1" style="28" min="4" max="4"/>
+    <col width="16" customWidth="1" style="32" min="1" max="1"/>
+    <col width="50" customWidth="1" style="32" min="2" max="2"/>
+    <col width="25" customWidth="1" style="32" min="3" max="3"/>
+    <col width="18" customWidth="1" style="32" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="27" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="32">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>HU-19 · Exportación de los 7 reportes definidos del contrato</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="32" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="32">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-06-03</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="43" t="inlineStr">
         <is>
           <t>Módulo: MOD-06</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="32" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="32">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>Sprint sugerido: 9</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="29" t="inlineStr">
+    <row r="5" ht="24" customHeight="1" s="32">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.9" customHeight="1" s="28">
+    <row r="6" ht="27.9" customHeight="1" s="32">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="26" t="n"/>
-    </row>
-    <row r="7" ht="35.1" customHeight="1" s="28">
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="35.1" customHeight="1" s="32">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>descargar cualquiera de los 7 reportes definidos del contrato (avance físico, financiero, estimaciones, observaciones, bitácora, modificatorios, penalizaciones) en formato PDF o Excel según el reporte</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="26" t="n"/>
-    </row>
-    <row r="8" ht="27.9" customHeight="1" s="28">
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="30" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="32">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>llevar la información del sistema a oficios, presentaciones o expedientes de auditoría</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="26" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="30" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" s="32">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="28">
+    <row r="12" ht="32.1" customHeight="1" s="32">
       <c r="A12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>Cada uno de los 7 reportes definidos genera un archivo descargable en el formato establecido (PDF, Excel o ambos según el reporte).</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n"/>
+      <c r="C12" s="30" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="33" customHeight="1" s="28">
+    <row r="13" ht="33" customHeight="1" s="32">
       <c r="A13" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>El usuario puede seleccionar el periodo (mensual, trimestral, acumulado) sin alterar el contenido predefinido del reporte.</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n"/>
+      <c r="C13" s="30" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="29" t="inlineStr">
+    <row r="15" ht="24" customHeight="1" s="32">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="28">
+    <row r="16" ht="24" customHeight="1" s="32">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B16" s="42" t="inlineStr">
+      <c r="B16" s="46" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C16" s="31" t="n"/>
-      <c r="D16" s="26" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" s="28">
+      <c r="C16" s="38" t="n"/>
+      <c r="D16" s="30" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="32">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B17" s="41" t="n">
+      <c r="B17" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="28">
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="32">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="30" t="inlineStr">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>Sprint 9</t>
         </is>
       </c>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="26" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="28">
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="32">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="26" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -5040,225 +5089,225 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="28" min="1" max="1"/>
-    <col width="50" customWidth="1" style="28" min="2" max="2"/>
-    <col width="25" customWidth="1" style="28" min="3" max="3"/>
-    <col width="18" customWidth="1" style="28" min="4" max="4"/>
+    <col width="16" customWidth="1" style="32" min="1" max="1"/>
+    <col width="50" customWidth="1" style="32" min="2" max="2"/>
+    <col width="25" customWidth="1" style="32" min="3" max="3"/>
+    <col width="18" customWidth="1" style="32" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="27" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="32">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>HU-20 · Tránsito a pago: carga de soportes y verificación de suficiencia presupuestal</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="32" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="32">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-07-01</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="43" t="inlineStr">
         <is>
           <t>Módulo: MOD-07</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="32" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="32">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>Sprint sugerido: 5</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="29" t="inlineStr">
+    <row r="5" ht="24" customHeight="1" s="32">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.9" customHeight="1" s="28">
+    <row r="6" ht="27.9" customHeight="1" s="32">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>contratista y finanzas</t>
         </is>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="26" t="n"/>
-    </row>
-    <row r="7" ht="45" customHeight="1" s="28">
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="45" customHeight="1" s="32">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>que al autorizarse una estimación el sistema verifique la suficiencia presupuestal (art. 24 LOPSRM), genere la instrucción de pago, permita cargar los soportes (factura, CFDI y fianza de cumplimiento cuando el contrato lo exija) y notifique a Finanzas con el plazo de 20 días naturales del art. 54 LOPSRM</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="26" t="n"/>
-    </row>
-    <row r="8" ht="27.9" customHeight="1" s="28">
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="30" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="32">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>no perder el plazo de pago y dejar evidencia de la suficiencia presupuestal verificada, considerando que el incumplimiento del plazo de pago genera gastos financieros a cargo de la dependencia (art. 55 LOPSRM)</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="26" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="30" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" s="32">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="28">
+    <row r="12" ht="32.1" customHeight="1" s="32">
       <c r="A12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>El sistema verifica suficiencia presupuestal contra el techo anual y bloquea la generación de la instrucción de pago si el monto excede lo disponible (art. 24 LOPSRM).</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n"/>
+      <c r="C12" s="30" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="33.9" customHeight="1" s="28">
+    <row r="13" ht="33.9" customHeight="1" s="32">
       <c r="A13" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>Un semáforo muestra el avance del plazo de 20 días naturales para pago (art. 54 LOPSRM), basado en la fecha de autorización, y avisa al entrar en amarillo.</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n"/>
+      <c r="C13" s="30" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="36.9" customHeight="1" s="28">
+    <row r="14" ht="36.9" customHeight="1" s="32">
       <c r="A14" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="40" t="inlineStr">
         <is>
           <t>La instrucción de pago solo puede generarse cuando todos los soportes obligatorios (factura, CFDI, estado de fianza de cumplimiento cuando el contrato lo exija) están cargados.</t>
         </is>
       </c>
-      <c r="C14" s="26" t="n"/>
+      <c r="C14" s="30" t="n"/>
       <c r="D14" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="29" t="inlineStr">
+    <row r="16" ht="24" customHeight="1" s="32">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" s="28">
+    <row r="17" ht="24" customHeight="1" s="32">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B17" s="40" t="inlineStr">
+      <c r="B17" s="44" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="28">
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="32">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B18" s="40" t="n">
+      <c r="B18" s="44" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="26" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="28">
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="32">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="26" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" s="28">
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="30" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" s="32">
       <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="26" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -5296,213 +5345,213 @@
   <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="28" min="1" max="1"/>
-    <col width="50" customWidth="1" style="28" min="2" max="2"/>
-    <col width="25" customWidth="1" style="28" min="3" max="3"/>
-    <col width="18" customWidth="1" style="28" min="4" max="4"/>
+    <col width="16" customWidth="1" style="32" min="1" max="1"/>
+    <col width="50" customWidth="1" style="32" min="2" max="2"/>
+    <col width="25" customWidth="1" style="32" min="3" max="3"/>
+    <col width="18" customWidth="1" style="32" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="27" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="32">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>HU-21 · Registro del pago efectuado</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="32" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="32">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-07-02</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="43" t="inlineStr">
         <is>
           <t>Módulo: MOD-07</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="32" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="32">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>Sprint sugerido: 2</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="29" t="inlineStr">
+    <row r="5" ht="24" customHeight="1" s="32">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.9" customHeight="1" s="28">
+    <row r="6" ht="27.9" customHeight="1" s="32">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>finanzas</t>
         </is>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="26" t="n"/>
-    </row>
-    <row r="7" ht="27.9" customHeight="1" s="28">
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="27.9" customHeight="1" s="32">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>registrar en el sistema el pago realizado de una estimación: fecha, importe, referencia bancaria y observaciones</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="26" t="n"/>
-    </row>
-    <row r="8" ht="27.9" customHeight="1" s="28">
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="30" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="32">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>cerrar el ciclo de la estimación y actualizar el avance financiero del contrato</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="26" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="30" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" s="32">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="28">
+    <row r="12" ht="32.1" customHeight="1" s="32">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>El registro del pago marca la estimación como pagada y actualiza el avance financiero del contrato.</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n"/>
+      <c r="C12" s="30" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="28">
+    <row r="13" ht="32.1" customHeight="1" s="32">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>se encuentran todos o se encuentran los siguientes datos: fecha, importe, referencia bancaria y usuario que realizó el registro.</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n"/>
+      <c r="C13" s="30" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="29" t="inlineStr">
+    <row r="15" ht="24" customHeight="1" s="32">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="28">
+    <row r="16" ht="24" customHeight="1" s="32">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B16" s="35" t="inlineStr">
+      <c r="B16" s="39" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="C16" s="31" t="n"/>
-      <c r="D16" s="26" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" s="28">
+      <c r="C16" s="38" t="n"/>
+      <c r="D16" s="30" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="32">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
+      <c r="B17" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="28">
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="32">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="30" t="inlineStr">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="26" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="28">
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="32">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="26" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -5539,165 +5588,163 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="28" min="1" max="1"/>
-    <col width="50" customWidth="1" style="28" min="2" max="2"/>
-    <col width="25" customWidth="1" style="28" min="3" max="3"/>
-    <col width="18" customWidth="1" style="28" min="4" max="4"/>
+    <col width="16" customWidth="1" style="32" min="1" max="1"/>
+    <col width="50" customWidth="1" style="32" min="2" max="2"/>
+    <col width="25" customWidth="1" style="32" min="3" max="3"/>
+    <col width="18" customWidth="1" style="32" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="27" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="32">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>Registro · Registro de usuario con aprobación</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="32" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="32">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Servicio implementado: Control de Accesos</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="43" t="inlineStr">
         <is>
           <t>Módulo: —</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="32" t="inlineStr">
-        <is>
-          <t>Sprint sugerido: Agregada tras la revisión</t>
-        </is>
-      </c>
-      <c r="C3" s="32" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="32">
+      <c r="A3" s="43" t="n"/>
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="29" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="32">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.9" customHeight="1" s="28">
+    <row r="6" ht="27.9" customHeight="1" s="32">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>usuario nuevo</t>
         </is>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="26" t="n"/>
-    </row>
-    <row r="7" ht="69" customHeight="1" s="28">
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="69" customHeight="1" s="32">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>registrarme en el sistema proporcionando mis datos</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="26" t="n"/>
-    </row>
-    <row r="8" ht="27.9" customHeight="1" s="28">
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="30" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="32">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>solicitar acceso y que la dependencia valide mi identidad y asigne mi rol</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="26" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="30" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="24" customHeight="1" s="32">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="28">
+    <row r="12" ht="32.1" customHeight="1" s="32">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
-        <is>
-          <t>El registro captura los datos del solicitante y crea la cuenta en estado pendiente, sin otorgar acceso.</t>
-        </is>
-      </c>
-      <c r="C12" s="26" t="n"/>
+      <c r="B12" s="40" t="inlineStr">
+        <is>
+          <t>El registro captura los datos del solicitante —incluido el rol que solicita— y crea la cuenta en estado pendiente, sin otorgar acceso ni el rol solicitado de forma automática.</t>
+        </is>
+      </c>
+      <c r="C12" s="30" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="28">
+    <row r="13" ht="32.1" customHeight="1" s="32">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>El sistema impide el ingreso de cuentas no aprobadas e informa que están pendientes de autorización.</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n"/>
+      <c r="C13" s="30" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32.1" customHeight="1" s="28">
+    <row r="14" ht="32.1" customHeight="1" s="32">
       <c r="A14" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B14" s="25" t="inlineStr">
-        <is>
-          <t>La dependencia revisa las solicitudes, asigna el rol y aprueba o rechaza; solo las cuentas aprobadas pueden ingresar.</t>
-        </is>
-      </c>
-      <c r="C14" s="26" t="n"/>
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t>La dependencia revisa las solicitudes y asigna el rol efectivo (que puede diferir del solicitado), aprueba o rechaza, y queda registrado quién aprobó y cuándo (aprobado_por / aprobado_en); solo las cuentas aprobadas pueden ingresar.</t>
+        </is>
+      </c>
+      <c r="C14" s="30" t="n"/>
       <c r="D14" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
@@ -5706,66 +5753,66 @@
     </row>
     <row r="15">
       <c r="A15" s="13" t="n"/>
-      <c r="B15" s="25" t="n"/>
-    </row>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="29" t="inlineStr">
+      <c r="B15" s="40" t="n"/>
+    </row>
+    <row r="16" ht="24" customHeight="1" s="32">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" s="28">
+    <row r="17" ht="24" customHeight="1" s="32">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B17" s="35" t="inlineStr">
+      <c r="B17" s="39" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="28">
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="32">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n"/>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="26" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="28">
+      <c r="B18" s="39" t="n"/>
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="32">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>Agregada tras la revisión</t>
         </is>
       </c>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="26" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" s="28">
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="30" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" s="32">
       <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>Terminado</t>
         </is>
       </c>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="26" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -5800,32 +5847,300 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="16" customWidth="1" style="32" min="1" max="1"/>
+    <col width="50" customWidth="1" style="32" min="2" max="2"/>
+    <col width="25" customWidth="1" style="32" min="3" max="3"/>
+    <col width="18" customWidth="1" style="32" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" s="32">
+      <c r="A1" s="34" t="inlineStr">
+        <is>
+          <t>Por Firmar · Firma de aperturas de bitácora pendientes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" s="32">
+      <c r="A2" s="43" t="inlineStr">
+        <is>
+          <t>Servicio implementado: SRV-03-05</t>
+        </is>
+      </c>
+      <c r="C2" s="43" t="inlineStr">
+        <is>
+          <t>Módulo: MOD-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1" s="32">
+      <c r="A3" s="43" t="inlineStr">
+        <is>
+          <t>Sprint sugerido: 1</t>
+        </is>
+      </c>
+      <c r="C3" s="43" t="inlineStr">
+        <is>
+          <t>Estado: Backlog</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="32">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>HISTORIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="27.9" customHeight="1" s="32">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="B6" s="37" t="inlineStr">
+        <is>
+          <t>firmante autorizado (residente, superintendente o supervisión)</t>
+        </is>
+      </c>
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="69" customHeight="1" s="32">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Deseo</t>
+        </is>
+      </c>
+      <c r="B7" s="37" t="inlineStr">
+        <is>
+          <t>ver las aperturas de bitácora pendientes de mi firma y firmar desde mi propia cuenta</t>
+        </is>
+      </c>
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="30" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="32">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>A fin de</t>
+        </is>
+      </c>
+      <c r="B8" s="37" t="inlineStr">
+        <is>
+          <t>que mi firma quede registrada de forma auténtica (con mi identidad y fecha/hora) y la apertura avance hasta quedar completa</t>
+        </is>
+      </c>
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="30" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="24" customHeight="1" s="32">
+      <c r="A10" s="36" t="inlineStr">
+        <is>
+          <t>CRITERIOS DE ACEPTACIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B11" s="42" t="inlineStr">
+        <is>
+          <t>Criterios de aceptación</t>
+        </is>
+      </c>
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="42" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32.1" customHeight="1" s="32">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B12" s="40" t="inlineStr">
+        <is>
+          <t>En una bandeja "Por firmar", cada firmante ve únicamente las aperturas que requieren su firma y que aún no ha firmado.</t>
+        </is>
+      </c>
+      <c r="C12" s="30" t="n"/>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>☐ Sí   ☐ No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32.1" customHeight="1" s="32">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B13" s="40" t="inlineStr">
+        <is>
+          <t>Al firmar, la firma queda registrada con la identidad del firmante y la fecha/hora; ningún usuario puede firmar por otro.</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="n"/>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>☐ Sí   ☐ No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32.1" customHeight="1" s="32">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t>Cuando todos los firmantes autorizados han firmado, la apertura queda marcada como completa.</t>
+        </is>
+      </c>
+      <c r="C14" s="30" t="n"/>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>☐ Sí   ☐ No</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="40" t="n"/>
+    </row>
+    <row r="16" ht="24" customHeight="1" s="32">
+      <c r="A16" s="36" t="inlineStr">
+        <is>
+          <t>METADATOS DE PLANEACIÓN (Scrum)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="32">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>Complejidad</t>
+        </is>
+      </c>
+      <c r="B17" s="39" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="32">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
+        </is>
+      </c>
+      <c r="B18" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="32">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>Sprint propuesto</t>
+        </is>
+      </c>
+      <c r="B19" s="41" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="30" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" s="32">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B20" s="41" t="inlineStr">
+        <is>
+          <t>Terminado</t>
+        </is>
+      </c>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="30" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="C3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="12" customWidth="1" style="28" min="1" max="1"/>
-    <col width="50" customWidth="1" style="28" min="2" max="2"/>
-    <col width="12" customWidth="1" style="28" min="3" max="3"/>
-    <col width="22" customWidth="1" style="28" min="4" max="4"/>
-    <col width="32" customWidth="1" style="28" min="5" max="5"/>
-    <col width="40" customWidth="1" style="28" min="6" max="6"/>
+    <col width="12" customWidth="1" style="32" min="1" max="1"/>
+    <col width="50" customWidth="1" style="32" min="2" max="2"/>
+    <col width="12" customWidth="1" style="32" min="3" max="3"/>
+    <col width="22" customWidth="1" style="32" min="4" max="4"/>
+    <col width="32" customWidth="1" style="32" min="5" max="5"/>
+    <col width="40" customWidth="1" style="32" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="28">
-      <c r="A1" s="27" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="32">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>Plan de iteraciones (Sprints)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="50.1" customHeight="1" s="28">
-      <c r="A2" s="37" t="inlineStr">
+    <row r="2" ht="50.1" customHeight="1" s="32">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>Distribución de las 22 historias en 9 sprints. Velocidad objetivo: 9 puntos por sprint (3 integrantes × 3 días útiles × 1 punto por día-persona). Las historias complejas (8 user points): HU-09 emisión de notas, HU-12 integración de estimación, HU-15 revisión de estimación y HU-20 tránsito a pago, todas ubicadas en sprints 2-5 para mitigar el riesgo de retraso. Ningún sprint excede 10 puntos. Promedio: 9.4 pts/sprint.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32.1" customHeight="1" s="28">
+    <row r="4" ht="32.1" customHeight="1" s="32">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Sprint</t>
@@ -5857,21 +6172,22 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="66" customHeight="1" s="28">
-      <c r="A5" s="36" t="inlineStr">
+    <row r="5" ht="66" customHeight="1" s="32">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>• HU-00 Inicio de sesión por rol (1)
 • HU-01 Alta de contratos (5)
-• HU-08 Apertura formal de la bitácora del contrato (2)</t>
-        </is>
-      </c>
-      <c r="C5" s="40" t="n">
-        <v>8</v>
+• HU-08 Apertura formal de la bitácora del contrato (2)
+• Por Firmar Firma de aperturas de bitácora pendientes (2)</t>
+        </is>
+      </c>
+      <c r="C5" s="44" t="n">
+        <v>10</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -5889,19 +6205,19 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1" s="28">
-      <c r="A6" s="36" t="inlineStr">
+    <row r="6" ht="60" customHeight="1" s="32">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>• HU-09 Emisión y respuesta de notas tipificadas con firma (8)
 • HU-21 Registro del pago efectuado (2)</t>
         </is>
       </c>
-      <c r="C6" s="41" t="n">
+      <c r="C6" s="45" t="n">
         <v>10</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -5920,19 +6236,19 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1" s="28">
-      <c r="A7" s="36" t="inlineStr">
+    <row r="7" ht="60" customHeight="1" s="32">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>• HU-10 Consulta y búsqueda de notas de bitácora (2)
 • HU-12 Apertura del periodo e integración de la estimación (8)</t>
         </is>
       </c>
-      <c r="C7" s="41" t="n">
+      <c r="C7" s="45" t="n">
         <v>10</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -5951,19 +6267,19 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1" s="28">
-      <c r="A8" s="36" t="inlineStr">
+    <row r="8" ht="60" customHeight="1" s="32">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>• HU-04 Consulta integrada del expediente contractual (2)
 • HU-15 Recepción, revisión técnica y autorización de la estimación (8)</t>
         </is>
       </c>
-      <c r="C8" s="41" t="n">
+      <c r="C8" s="45" t="n">
         <v>10</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -5982,19 +6298,19 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1" s="28">
-      <c r="A9" s="36" t="inlineStr">
+    <row r="9" ht="60" customHeight="1" s="32">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>• HU-14 Historial de estimaciones del contrato (2)
 • HU-20 Tránsito a pago: carga de soportes y verificación de suficiencia presupuestal (8)</t>
         </is>
       </c>
-      <c r="C9" s="41" t="n">
+      <c r="C9" s="45" t="n">
         <v>10</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -6013,20 +6329,20 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="66" customHeight="1" s="28">
-      <c r="A10" s="36" t="inlineStr">
+    <row r="10" ht="66" customHeight="1" s="32">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>Sprint 6</t>
         </is>
       </c>
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>• HU-02 Registro de fianzas y garantías (2)
 • HU-03 Trámite y aplicación de convenios modificatorios (5)
 • HU-07 Configuración de alertas de atraso por concepto (2)</t>
         </is>
       </c>
-      <c r="C10" s="40" t="n">
+      <c r="C10" s="44" t="n">
         <v>9</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -6045,13 +6361,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="66" customHeight="1" s="28">
-      <c r="A11" s="36" t="inlineStr">
+    <row r="11" ht="66" customHeight="1" s="32">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>Sprint 7</t>
         </is>
       </c>
-      <c r="B11" s="34" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>• HU-05 Visualización del programa y curva de avance (3)
 • HU-06 Registro de trabajos terminados por periodo (3)
@@ -6077,20 +6393,20 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="66" customHeight="1" s="28">
-      <c r="A12" s="36" t="inlineStr">
+    <row r="12" ht="66" customHeight="1" s="32">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>Sprint 8</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>• HU-13 Envío de la estimación (3)
 • HU-16 Reingreso de estimación tras rechazo (3)
 • HU-17 Tablero de estimaciones aceptadas y en proceso (3)</t>
         </is>
       </c>
-      <c r="C12" s="41" t="n">
+      <c r="C12" s="45" t="n">
         <v>9</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -6109,19 +6425,19 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1" s="28">
-      <c r="A13" s="36" t="inlineStr">
+    <row r="13" ht="60" customHeight="1" s="32">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>Sprint 9</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>• HU-18 Vista ejecutiva del portafolio con semáforos (5)
 • HU-19 Exportación de los 7 reportes definidos del contrato (5)</t>
         </is>
       </c>
-      <c r="C13" s="41" t="n">
+      <c r="C13" s="45" t="n">
         <v>10</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -6152,7 +6468,7 @@
         </is>
       </c>
       <c r="C14" s="20" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D14" s="22" t="n"/>
       <c r="E14" s="22" t="n"/>
@@ -6172,7 +6488,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6194,225 +6510,227 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="28" min="1" max="1"/>
-    <col width="50" customWidth="1" style="28" min="2" max="2"/>
-    <col width="25" customWidth="1" style="28" min="3" max="3"/>
-    <col width="18" customWidth="1" style="28" min="4" max="4"/>
+    <col width="16" customWidth="1" style="32" min="1" max="1"/>
+    <col width="50" customWidth="1" style="32" min="2" max="2"/>
+    <col width="25" customWidth="1" style="32" min="3" max="3"/>
+    <col width="18" customWidth="1" style="32" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="27" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="32">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>HU-01 · Alta de contratos</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="32" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="32">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-01-01</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="43" t="inlineStr">
         <is>
           <t>Módulo: MOD-01</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="32" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="32">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>Sprint sugerido: 1</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="29" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="32">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.9" customHeight="1" s="28">
+    <row r="6" ht="27.9" customHeight="1" s="32">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="26" t="n"/>
-    </row>
-    <row r="7" ht="98.40000000000001" customHeight="1" s="28">
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="98.40000000000001" customHeight="1" s="32">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
-        <is>
-          <t>dar de alta un contrato nuevo capturando en un solo flujo: datos generales (folio, partes, monto, plazos, modalidad de pago), catálogo de conceptos (clave, descripción, unidad, precio, cantidad), programa de obra mes a mes, elementos jurídicos separados por dependencia y contratista, garantías (anticipo, cumplimiento y vicios ocultos), plan de amortización del anticipo, penalizaciones aplicables (incluida la retención del 5 al millar, art. 191 LFD) y el PDF firmado del contrato como respaldo</t>
-        </is>
-      </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="26" t="n"/>
-    </row>
-    <row r="8" ht="27.9" customHeight="1" s="28">
+      <c r="B7" s="37" t="inlineStr">
+        <is>
+          <t>dar de alta un contrato nuevo capturando en un solo flujo: datos generales (folio, partes, monto, plazos, modalidad de pago), el equipo del contrato (residente, superintendente y supervisión, ligados a sus cuentas), catálogo de conceptos (clave, descripción, unidad, precio, cantidad), programa de obra mes a mes, elementos jurídicos separados por dependencia y contratista, garantías (anticipo, cumplimiento y vicios ocultos), plan de amortización del anticipo, penalizaciones aplicables (incluida la retención del 5 al millar, art. 191 LFD) y el PDF firmado del contrato como respaldo; además, el sistema informa los umbrales de autorización del anticipo (art. 50 fr. IV LOPSRM y art. 139 RLOPSRM)</t>
+        </is>
+      </c>
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="30" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="32">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>tener el soporte documental del contrato en línea, disponible para los actores autorizados</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="26" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="30" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="24" customHeight="1" s="32">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="61.2" customHeight="1" s="28">
+    <row r="12" ht="61.2" customHeight="1" s="32">
       <c r="A12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="25" t="inlineStr">
-        <is>
-          <t>Existe un contrato con folio único que contiene, en una sola entidad, los siguientes bloques: datos generales, catálogo de conceptos, programa de obra, elementos jurídicos (dependencia y contratista por separado), garantías (anticipo, cumplimiento, vicios ocultos), plan de amortización, penalizaciones y PDF firmado.</t>
-        </is>
-      </c>
-      <c r="C12" s="26" t="n"/>
+      <c r="B12" s="40" t="inlineStr">
+        <is>
+          <t>Existe un contrato con folio único que contiene, en una sola entidad, los siguientes bloques: datos generales, equipo del contrato (residente, superintendente y supervisión) ligado a cuentas del sistema, catálogo de conceptos, programa de obra, elementos jurídicos (dependencia y contratista por separado), garantías (anticipo, cumplimiento, vicios ocultos), plan de amortización, penalizaciones y PDF firmado.</t>
+        </is>
+      </c>
+      <c r="C12" s="30" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="28">
+    <row r="13" ht="32.1" customHeight="1" s="32">
       <c r="A13" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="25" t="inlineStr">
-        <is>
-          <t>El sistema no permite guardar el contrato hasta que todos los campos obligatorios estén llenos y el folio sea único.</t>
-        </is>
-      </c>
-      <c r="C13" s="26" t="n"/>
+      <c r="B13" s="40" t="inlineStr">
+        <is>
+          <t>El sistema no permite guardar el contrato hasta que todos los campos obligatorios estén llenos, el folio sea único y se cumplan las reglas de validación: la suma del catálogo es igual al monto (subtotal sin IVA), cada concepto tiene cantidad y precio unitario mayores a 0, la fecha de término se deriva del plazo y la fecha de inicio, las actividades del programa caen dentro del plazo, y toda garantía capturada incluye su monto.</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32.1" customHeight="1" s="28">
+    <row r="14" ht="32.1" customHeight="1" s="32">
       <c r="A14" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="25" t="inlineStr">
-        <is>
-          <t>El sistema contempla el PDF firmado como parte del expediente del contrato, ligado cuando se cargue, consultable por los actores autorizados.</t>
-        </is>
-      </c>
-      <c r="C14" s="26" t="n"/>
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t>El sistema contempla el PDF firmado como parte del expediente del contrato, ligado cuando se cargue, inmutable una vez cargado (no se reemplaza), y consultable por los actores autorizados.</t>
+        </is>
+      </c>
+      <c r="C14" s="30" t="n"/>
       <c r="D14" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="29" t="inlineStr">
+    <row r="16" ht="24" customHeight="1" s="32">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" s="28">
+    <row r="17" ht="24" customHeight="1" s="32">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B17" s="40" t="inlineStr">
+      <c r="B17" s="44" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="28">
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="32">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B18" s="41" t="n">
+      <c r="B18" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="26" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="28">
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="32">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="26" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" s="28">
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="30" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" s="32">
       <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>Terminado</t>
         </is>
       </c>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="26" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -6450,154 +6768,154 @@
   <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="28" min="1" max="1"/>
-    <col width="50" customWidth="1" style="28" min="2" max="2"/>
-    <col width="25" customWidth="1" style="28" min="3" max="3"/>
-    <col width="18" customWidth="1" style="28" min="4" max="4"/>
+    <col width="16" customWidth="1" style="32" min="1" max="1"/>
+    <col width="50" customWidth="1" style="32" min="2" max="2"/>
+    <col width="25" customWidth="1" style="32" min="3" max="3"/>
+    <col width="18" customWidth="1" style="32" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="27" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="32">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>HU-02 · Registro de fianzas y garantías</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="32" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="32">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-01-02</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="43" t="inlineStr">
         <is>
           <t>Módulo: MOD-01</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="32" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="32">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>Sprint sugerido: 6</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="29" t="inlineStr">
+    <row r="5" ht="24" customHeight="1" s="32">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.9" customHeight="1" s="28">
+    <row r="6" ht="27.9" customHeight="1" s="32">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>dependencia</t>
         </is>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="26" t="n"/>
-    </row>
-    <row r="7" ht="29.1" customHeight="1" s="28">
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="29.1" customHeight="1" s="32">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>subir las pólizas de fianza del contrato (cumplimiento, vicios ocultos, anticipo) con sus metadatos (vigencia, afianzadora y monto), recibir alertas anticipadas de vencimiento y mantener el historial de fianzas y sus endosos por modificatorios</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="26" t="n"/>
-    </row>
-    <row r="8" ht="27.9" customHeight="1" s="28">
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="30" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="32">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>contar con el respaldo documental de las garantías del contrato y ser notificado cuando una póliza esté por vencer</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="26" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="30" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" s="32">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="28">
+    <row r="12" ht="32.1" customHeight="1" s="32">
       <c r="A12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>La póliza queda ligada al contrato con afianzadora, vigencia y monto registrados.</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n"/>
+      <c r="C12" s="30" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="28">
+    <row r="13" ht="32.1" customHeight="1" s="32">
       <c r="A13" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>El sistema emite alerta cuando faltan 30, 15 y 5 días para el vencimiento (configurable).</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n"/>
+      <c r="C13" s="30" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="27.6" customHeight="1" s="28">
+    <row r="14" ht="27.6" customHeight="1" s="32">
       <c r="A14" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="40" t="inlineStr">
         <is>
           <t>La póliza registrada puede consultarse en formato PDF desde el listado de fianzas del contrato.</t>
         </is>
@@ -6608,66 +6926,66 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="29" t="inlineStr">
+    <row r="15" ht="24" customHeight="1" s="32">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="28">
+    <row r="16" ht="24" customHeight="1" s="32">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B16" s="42" t="inlineStr">
+      <c r="B16" s="46" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C16" s="31" t="n"/>
-      <c r="D16" s="26" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" s="28">
+      <c r="C16" s="38" t="n"/>
+      <c r="D16" s="30" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="32">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
+      <c r="B17" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="28">
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="32">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="30" t="inlineStr">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>Sprint 6</t>
         </is>
       </c>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="26" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="28">
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="32">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="26" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -6704,143 +7022,143 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="28" min="1" max="1"/>
-    <col width="50" customWidth="1" style="28" min="2" max="2"/>
-    <col width="25" customWidth="1" style="28" min="3" max="3"/>
-    <col width="18" customWidth="1" style="28" min="4" max="4"/>
+    <col width="16" customWidth="1" style="32" min="1" max="1"/>
+    <col width="50" customWidth="1" style="32" min="2" max="2"/>
+    <col width="25" customWidth="1" style="32" min="3" max="3"/>
+    <col width="18" customWidth="1" style="32" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="27" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="32">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>HU-03 · Trámite y aplicación de convenios modificatorios</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="32" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="32">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-01-03</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="43" t="inlineStr">
         <is>
           <t>Módulo: MOD-01</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="32" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="32">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>Sprint sugerido: 6</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="29" t="inlineStr">
+    <row r="5" ht="24" customHeight="1" s="32">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.9" customHeight="1" s="28">
+    <row r="6" ht="27.9" customHeight="1" s="32">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>dependencia</t>
         </is>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="26" t="n"/>
-    </row>
-    <row r="7" ht="33" customHeight="1" s="28">
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="33" customHeight="1" s="32">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>registrar un convenio modificatorio del contrato (cambios al monto, plazo o conceptos) y aplicar las actualizaciones al catálogo, programa y endosos de las fianzas, manteniendo el histórico de versiones conforme al art. 59 LOPSRM</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="26" t="n"/>
-    </row>
-    <row r="8" ht="27.9" customHeight="1" s="28">
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="30" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="32">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>documentar formalmente los cambios al contrato conforme a los arts. 59 y 59 Bis LOPSRM (este último cuando la modificación supera el 50% del importe o del plazo) y poder consultar qué cambió, cuándo y por qué</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="26" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="30" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" s="32">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="33" customHeight="1" s="28">
+    <row r="12" ht="33" customHeight="1" s="32">
       <c r="A12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>Al registrarse el modificatorio se genera una nueva versión del catálogo y del programa, sin alterar la versión anterior.</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n"/>
+      <c r="C12" s="30" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="28">
+    <row r="13" ht="32.1" customHeight="1" s="32">
       <c r="A13" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>El sistema indica si el modificatorio se rige por el art. 59 LOPSRM (modificatorio ordinario) o por el art. 59 Bis (ajuste de costos cuando se supera 50% del monto o 50% del plazo).</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n"/>
+      <c r="C13" s="30" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
@@ -6857,53 +7175,53 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="28"/>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="29" t="inlineStr">
+    <row r="15" ht="24" customHeight="1" s="32"/>
+    <row r="16" ht="24" customHeight="1" s="32">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" s="28">
+    <row r="17" ht="24" customHeight="1" s="32">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B17" s="40" t="inlineStr">
+      <c r="B17" s="44" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="28">
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="32">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B18" s="41" t="n">
+      <c r="B18" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="26" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="28">
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="32">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>Sprint 6</t>
         </is>
       </c>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="26" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="30" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
@@ -6911,13 +7229,13 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="26" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -6954,143 +7272,145 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="28" min="1" max="1"/>
-    <col width="50" customWidth="1" style="28" min="2" max="2"/>
-    <col width="25" customWidth="1" style="28" min="3" max="3"/>
-    <col width="18" customWidth="1" style="28" min="4" max="4"/>
+    <col width="16" customWidth="1" style="32" min="1" max="1"/>
+    <col width="50" customWidth="1" style="32" min="2" max="2"/>
+    <col width="25" customWidth="1" style="32" min="3" max="3"/>
+    <col width="18" customWidth="1" style="32" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="27" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="32">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>HU-04 · Consulta integrada del expediente contractual</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="32" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="32">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-01-04</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="43" t="inlineStr">
         <is>
           <t>Módulo: MOD-01</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="32" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="32">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>Sprint sugerido: 4</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="29" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="32">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.9" customHeight="1" s="28">
+    <row r="6" ht="27.9" customHeight="1" s="32">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="26" t="n"/>
-    </row>
-    <row r="7" ht="29.1" customHeight="1" s="28">
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="29.1" customHeight="1" s="32">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>consultar en una sola vista los 5 bloques vigentes del contrato (configuración, catálogo, programa, fianzas y documentos jurídicos), con buscador combinable y descarga individual de documentos</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="26" t="n"/>
-    </row>
-    <row r="8" ht="27.9" customHeight="1" s="28">
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="30" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="32">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>obtener información del contrato sin tener que ir a cada módulo individualmente</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="26" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="30" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="24" customHeight="1" s="32">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="28">
+    <row r="12" ht="32.1" customHeight="1" s="32">
       <c r="A12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="25" t="inlineStr">
-        <is>
-          <t>El expediente muestra en una sola vista los 5 bloques del contrato: configuración, catálogo, programa, fianzas y documentos jurídicos.</t>
-        </is>
-      </c>
-      <c r="C12" s="26" t="n"/>
+      <c r="B12" s="40" t="inlineStr">
+        <is>
+          <t>El expediente muestra en una sola vista los 5 bloques del contrato: configuración, catálogo, programa, fianzas y documentos jurídicos; la consulta queda acotada a los actores que son parte del contrato.</t>
+        </is>
+      </c>
+      <c r="C12" s="30" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="28">
+    <row r="13" ht="32.1" customHeight="1" s="32">
       <c r="A13" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>El buscador filtra los bloques por folio, contratista, objeto, periodo o tipo de documento, con lógica Y.</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n"/>
+      <c r="C13" s="30" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
@@ -7107,53 +7427,53 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="28"/>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="29" t="inlineStr">
+    <row r="15" ht="24" customHeight="1" s="32"/>
+    <row r="16" ht="24" customHeight="1" s="32">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" s="28">
+    <row r="17" ht="24" customHeight="1" s="32">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B17" s="35" t="inlineStr">
+      <c r="B17" s="39" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="28">
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="32">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
+      <c r="B18" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="26" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="28">
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="32">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="26" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="30" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
@@ -7161,13 +7481,13 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="26" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -7204,143 +7524,143 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="28" min="1" max="1"/>
-    <col width="50" customWidth="1" style="28" min="2" max="2"/>
-    <col width="25" customWidth="1" style="28" min="3" max="3"/>
-    <col width="18" customWidth="1" style="28" min="4" max="4"/>
+    <col width="16" customWidth="1" style="32" min="1" max="1"/>
+    <col width="50" customWidth="1" style="32" min="2" max="2"/>
+    <col width="25" customWidth="1" style="32" min="3" max="3"/>
+    <col width="18" customWidth="1" style="32" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="27" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="32">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>HU-05 · Visualización del programa y curva de avance</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="32" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="32">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-02-01</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="43" t="inlineStr">
         <is>
           <t>Módulo: MOD-02</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="32" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="32">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>Sprint sugerido: 7</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="29" t="inlineStr">
+    <row r="5" ht="24" customHeight="1" s="32">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.9" customHeight="1" s="28">
+    <row r="6" ht="27.9" customHeight="1" s="32">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="26" t="n"/>
-    </row>
-    <row r="7" ht="27.9" customHeight="1" s="28">
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="27.9" customHeight="1" s="32">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>visualizar el programa de obra (catálogo de conceptos y su calendario tipo Gantt, marcando lo ejecutado) y las curvas de avance (programado vs ejecutado vs financiero), con filtros por concepto y periodo</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="26" t="n"/>
-    </row>
-    <row r="8" ht="27.9" customHeight="1" s="28">
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="30" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="32">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>identificar desviaciones entre lo planeado, lo ejecutado y lo cobrado para tomar decisiones a tiempo</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="26" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="30" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" s="32">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="28">
+    <row r="12" ht="32.1" customHeight="1" s="32">
       <c r="A12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>La vista muestra el programa de obra como matriz concepto × periodo (tipo Gantt), con el catálogo de conceptos y un código de color que distingue lo ejecutado de lo no ejecutado.</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n"/>
+      <c r="C12" s="30" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="28">
+    <row r="13" ht="32.1" customHeight="1" s="32">
       <c r="A13" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>La vista grafica las tres curvas (programado, ejecutado, financiero) y los filtros por concepto y periodo recalculan tanto la matriz como las curvas.</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n"/>
+      <c r="C13" s="30" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
@@ -7357,53 +7677,53 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="28"/>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="29" t="inlineStr">
+    <row r="15" ht="24" customHeight="1" s="32"/>
+    <row r="16" ht="24" customHeight="1" s="32">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" s="28">
+    <row r="17" ht="24" customHeight="1" s="32">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B17" s="42" t="inlineStr">
+      <c r="B17" s="46" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="28">
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="32">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B18" s="42" t="n">
+      <c r="B18" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="26" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="28">
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="32">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>Sprint 7</t>
         </is>
       </c>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="26" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="30" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
@@ -7411,13 +7731,13 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="26" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -7454,143 +7774,145 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="28" min="1" max="1"/>
-    <col width="50" customWidth="1" style="28" min="2" max="2"/>
-    <col width="25" customWidth="1" style="28" min="3" max="3"/>
-    <col width="18" customWidth="1" style="28" min="4" max="4"/>
+    <col width="16" customWidth="1" style="32" min="1" max="1"/>
+    <col width="50" customWidth="1" style="32" min="2" max="2"/>
+    <col width="25" customWidth="1" style="32" min="3" max="3"/>
+    <col width="18" customWidth="1" style="32" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="27" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="32">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>HU-08 · Apertura formal de la bitácora del contrato</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="32" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="32">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-03-01</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="43" t="inlineStr">
         <is>
           <t>Módulo: MOD-03</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="32" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="32">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>Sprint sugerido: 1</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="29" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="32">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.9" customHeight="1" s="28">
+    <row r="6" ht="27.9" customHeight="1" s="32">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="26" t="n"/>
-    </row>
-    <row r="7" ht="30" customHeight="1" s="28">
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1" s="32">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
-        <is>
-          <t>aperturar la bitácora electrónica del contrato en la fecha de entrega del sitio de los trabajos, ligando a las tres partes (dependencia, supervisión y contratista) con sus representantes autorizados a firmar, y registrando la primera nota con los datos obligatorios</t>
-        </is>
-      </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="26" t="n"/>
-    </row>
-    <row r="8" ht="27.9" customHeight="1" s="28">
+      <c r="B7" s="37" t="inlineStr">
+        <is>
+          <t>aperturar la bitácora electrónica del contrato en la fecha de entrega del sitio de los trabajos, ligando a los representantes autorizados de cada parte (residente, superintendente y supervisión cuando exista) a partir de sus cuentas en el sistema, y registrando la primera nota con los datos obligatorios.</t>
+        </is>
+      </c>
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="30" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="32">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>habilitar el registro formal de eventos del contrato conforme al art. 46 último párrafo y al art. 52 Bis LOPSRM (bitácora electrónica obligatoria), reglamentados por el art. 122 RLOPSRM</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="26" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="30" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="24" customHeight="1" s="32">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="28">
+    <row r="12" ht="32.1" customHeight="1" s="32">
       <c r="A12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="25" t="inlineStr">
-        <is>
-          <t>Existe una bitácora única por contrato con las tres partes ligadas y sus firmantes autorizados (residente, supervisor externo si existe, superintendente).</t>
-        </is>
-      </c>
-      <c r="C12" s="26" t="n"/>
+      <c r="B12" s="40" t="inlineStr">
+        <is>
+          <t>Existe una bitácora única por contrato, con los representantes autorizados ligados a sus cuentas en el sistema: residente, superintendente y supervisión (esta última cuando exista). No se capturan nombres libres; los firmantes provienen del equipo asignado al contrato.</t>
+        </is>
+      </c>
+      <c r="C12" s="30" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="28">
+    <row r="13" ht="32.1" customHeight="1" s="32">
       <c r="A13" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="25" t="inlineStr">
-        <is>
-          <t>La fecha y hora de apertura (fecha de entrega del sitio) queda registrada como evento formal inalterable, con la firma conjunta de los tres autorizados.</t>
-        </is>
-      </c>
-      <c r="C13" s="26" t="n"/>
+      <c r="B13" s="40" t="inlineStr">
+        <is>
+          <t>La fecha y hora de apertura (fecha de entrega del sitio) queda registrada como evento formal inalterable. Cada autorizado firma desde su propia cuenta; la apertura queda completa cuando todos han firmado.</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
@@ -7607,53 +7929,53 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="28"/>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="A16" s="29" t="inlineStr">
+    <row r="15" ht="24" customHeight="1" s="32"/>
+    <row r="16" ht="24" customHeight="1" s="32">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" s="28">
+    <row r="17" ht="24" customHeight="1" s="32">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B17" s="35" t="inlineStr">
+      <c r="B17" s="39" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="28">
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="32">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
+      <c r="B18" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="26" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="28">
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="32">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="26" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="30" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
@@ -7661,13 +7983,13 @@
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
-        <is>
-          <t>En desarrollo</t>
-        </is>
-      </c>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="26" t="n"/>
+      <c r="B20" s="41" t="inlineStr">
+        <is>
+          <t>Terminado</t>
+        </is>
+      </c>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -7704,209 +8026,209 @@
   <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" style="28" min="1" max="1"/>
-    <col width="50" customWidth="1" style="28" min="2" max="2"/>
-    <col width="25" customWidth="1" style="28" min="3" max="3"/>
-    <col width="18" customWidth="1" style="28" min="4" max="4"/>
+    <col width="16" customWidth="1" style="32" min="1" max="1"/>
+    <col width="50" customWidth="1" style="32" min="2" max="2"/>
+    <col width="25" customWidth="1" style="32" min="3" max="3"/>
+    <col width="18" customWidth="1" style="32" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="28">
-      <c r="A1" s="27" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="32">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>HU-10 · Consulta y búsqueda de notas de bitácora</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="28">
-      <c r="A2" s="32" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="32">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Servicio implementado: SRV-03-03</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="43" t="inlineStr">
         <is>
           <t>Módulo: MOD-03</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="28">
-      <c r="A3" s="32" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="32">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>Sprint sugerido: 3</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>Estado: Backlog</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="28">
-      <c r="A5" s="29" t="inlineStr">
+    <row r="5" ht="24" customHeight="1" s="32">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>HISTORIA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.9" customHeight="1" s="28">
+    <row r="6" ht="27.9" customHeight="1" s="32">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>residente</t>
         </is>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="26" t="n"/>
-    </row>
-    <row r="7" ht="27.9" customHeight="1" s="28">
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="27.9" customHeight="1" s="32">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Deseo</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>buscar notas de la bitácora del contrato combinando los filtros tipo, rango de fechas, firmante, vínculo y palabra clave, todos aplicados con lógica Y (AND), y exportar las notas seleccionadas en formato Excel</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="26" t="n"/>
-    </row>
-    <row r="8" ht="27.9" customHeight="1" s="28">
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="30" t="n"/>
+    </row>
+    <row r="8" ht="27.9" customHeight="1" s="32">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A fin de</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>encontrar rápido la nota que necesito y poder referenciarla en estimaciones o reportes</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="26" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="30" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" s="32">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>Criterios de aceptación</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.1" customHeight="1" s="28">
+    <row r="12" ht="32.1" customHeight="1" s="32">
       <c r="A12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>La búsqueda devuelve solo las notas que cumplen simultáneamente todos los filtros aplicados (tipo, fecha, firmante, vínculo y palabra clave).</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n"/>
+      <c r="C12" s="30" t="n"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" s="28">
+    <row r="13" ht="32.1" customHeight="1" s="32">
       <c r="A13" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>Se pueden seleccionar varias notas del resultado y exportarlas en formato Excel.</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n"/>
+      <c r="C13" s="30" t="n"/>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>☐ Sí   ☐ No</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="28">
-      <c r="A15" s="29" t="inlineStr">
+    <row r="15" ht="24" customHeight="1" s="32">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>METADATOS DE PLANEACIÓN (Scrum)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="28">
+    <row r="16" ht="24" customHeight="1" s="32">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Complejidad</t>
         </is>
       </c>
-      <c r="B16" s="35" t="inlineStr">
+      <c r="B16" s="39" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="C16" s="31" t="n"/>
-      <c r="D16" s="26" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" s="28">
+      <c r="C16" s="38" t="n"/>
+      <c r="D16" s="30" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="32">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>User points (Fibonacci 1, 2, 3, 5, 8)</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
+      <c r="B17" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="28">
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="32">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Sprint propuesto</t>
         </is>
       </c>
-      <c r="B18" s="30" t="inlineStr">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="26" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="28">
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="32">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>En desarrollo</t>
         </is>
       </c>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="26" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
